--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78846104-3D74-4972-B123-94272BFE4BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D93170D-8994-426E-8834-C90E9E6D7D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="594">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1820,6 +1820,15 @@
   </si>
   <si>
     <t>Local Charges in june 9821/3 = 3273.66</t>
+  </si>
+  <si>
+    <t>INV 00091993 2633.78 NZ$ @2.15 CTF Newzealand</t>
+  </si>
+  <si>
+    <t>Collection and delivery Commision Abdul Khan</t>
+  </si>
+  <si>
+    <t>Dubai Office Exp in june 14952.5/3 = 4984.16</t>
   </si>
 </sst>
 </file>
@@ -1969,7 +1978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2047,6 +2056,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2062,377 +2072,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7AF396E0-14CD-4B92-AB27-039AE1E776EB}"/>
   </cellStyles>
-  <dxfs count="90">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="53">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -22176,7 +21816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6BDDCE-7628-4239-A22E-AFC54CBF13AA}">
-  <dimension ref="A1:L232"/>
+  <dimension ref="A1:L230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -27386,19 +27026,19 @@
         <v>3069.44</v>
       </c>
       <c r="G131" s="13">
-        <f t="shared" ref="G131:G194" si="4">F131/11</f>
+        <f t="shared" ref="G131:G191" si="4">F131/11</f>
         <v>279.04000000000002</v>
       </c>
       <c r="H131" s="13">
-        <f t="shared" ref="H131:H194" si="5">F131-G131</f>
+        <f t="shared" ref="H131:H191" si="5">F131-G131</f>
         <v>2790.4</v>
       </c>
       <c r="I131" s="13">
-        <f t="shared" ref="I131:I194" si="6">E131-H131</f>
+        <f t="shared" ref="I131:I191" si="6">E131-H131</f>
         <v>1234.5999999999999</v>
       </c>
       <c r="J131" s="14">
-        <f t="shared" ref="J131:J194" si="7">(E131-H131)/H131</f>
+        <f t="shared" ref="J131:J191" si="7">(E131-H131)/H131</f>
         <v>0.44244552752293576</v>
       </c>
       <c r="K131" s="10" t="s">
@@ -29768,38 +29408,38 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>15</v>
+        <v>552</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>547</v>
+        <v>17</v>
       </c>
       <c r="E191" s="10">
-        <v>1400</v>
+        <v>11600</v>
       </c>
       <c r="F191" s="10">
-        <v>1108.27</v>
+        <v>10527.57</v>
       </c>
       <c r="G191" s="13">
         <f t="shared" si="4"/>
-        <v>100.75181818181818</v>
+        <v>957.05181818181813</v>
       </c>
       <c r="H191" s="13">
         <f t="shared" si="5"/>
-        <v>1007.5181818181818</v>
+        <v>9570.5181818181809</v>
       </c>
       <c r="I191" s="13">
         <f t="shared" si="6"/>
-        <v>392.4818181818182</v>
+        <v>2029.4818181818191</v>
       </c>
       <c r="J191" s="14">
         <f t="shared" si="7"/>
-        <v>0.38955308724408316</v>
+        <v>0.21205558357721691</v>
       </c>
       <c r="K191" s="10" t="s">
         <v>18</v>
@@ -29808,38 +29448,38 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="15">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C192" s="23" t="s">
-        <v>548</v>
+        <v>276</v>
+      </c>
+      <c r="C192" s="23">
+        <v>39784450551</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>547</v>
+        <v>17</v>
       </c>
       <c r="E192" s="10">
-        <v>1400</v>
+        <v>4175</v>
       </c>
       <c r="F192" s="10">
-        <v>932.94</v>
+        <v>3143.18</v>
       </c>
       <c r="G192" s="13">
-        <f t="shared" si="4"/>
-        <v>84.812727272727273</v>
+        <f>F192/11</f>
+        <v>285.74363636363637</v>
       </c>
       <c r="H192" s="13">
-        <f t="shared" si="5"/>
-        <v>848.12727272727284</v>
+        <f>F192-G192</f>
+        <v>2857.4363636363632</v>
       </c>
       <c r="I192" s="13">
-        <f t="shared" si="6"/>
-        <v>551.87272727272716</v>
+        <f>E192-H192</f>
+        <v>1317.5636363636368</v>
       </c>
       <c r="J192" s="14">
-        <f t="shared" si="7"/>
-        <v>0.65069565030977317</v>
+        <f>(E192-H192)/H192</f>
+        <v>0.4610999051915578</v>
       </c>
       <c r="K192" s="10" t="s">
         <v>18</v>
@@ -29848,38 +29488,38 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="E193" s="10">
-        <v>1400</v>
+        <v>2070</v>
       </c>
       <c r="F193" s="10">
-        <v>1108.27</v>
+        <v>1527.53</v>
       </c>
       <c r="G193" s="13">
-        <f t="shared" si="4"/>
-        <v>100.75181818181818</v>
+        <f>F193/11</f>
+        <v>138.86636363636364</v>
       </c>
       <c r="H193" s="13">
-        <f t="shared" si="5"/>
-        <v>1007.5181818181818</v>
+        <f>F193-G193</f>
+        <v>1388.6636363636362</v>
       </c>
       <c r="I193" s="13">
-        <f t="shared" si="6"/>
-        <v>392.4818181818182</v>
+        <f>E193-H193</f>
+        <v>681.33636363636379</v>
       </c>
       <c r="J193" s="14">
-        <f t="shared" si="7"/>
-        <v>0.38955308724408316</v>
+        <f>(E193-H193)/H193</f>
+        <v>0.49064175499008217</v>
       </c>
       <c r="K193" s="10" t="s">
         <v>18</v>
@@ -29891,35 +29531,35 @@
         <v>46202</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>552</v>
+        <v>145</v>
       </c>
       <c r="C194" s="23" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>17</v>
+        <v>561</v>
       </c>
       <c r="E194" s="10">
-        <v>11600</v>
+        <v>2070</v>
       </c>
       <c r="F194" s="10">
-        <v>10527.57</v>
+        <v>1527.53</v>
       </c>
       <c r="G194" s="13">
-        <f t="shared" si="4"/>
-        <v>957.05181818181813</v>
+        <f>F194/11</f>
+        <v>138.86636363636364</v>
       </c>
       <c r="H194" s="13">
-        <f t="shared" si="5"/>
-        <v>9570.5181818181809</v>
+        <f>F194-G194</f>
+        <v>1388.6636363636362</v>
       </c>
       <c r="I194" s="13">
-        <f t="shared" si="6"/>
-        <v>2029.4818181818191</v>
+        <f>E194-H194</f>
+        <v>681.33636363636379</v>
       </c>
       <c r="J194" s="14">
-        <f t="shared" si="7"/>
-        <v>0.21205558357721691</v>
+        <f>(E194-H194)/H194</f>
+        <v>0.49064175499008217</v>
       </c>
       <c r="K194" s="10" t="s">
         <v>18</v>
@@ -29928,38 +29568,38 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="15">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>276</v>
       </c>
       <c r="C195" s="23">
-        <v>39784450551</v>
+        <v>19670053861</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E195" s="10">
-        <v>4175</v>
+        <v>4000</v>
       </c>
       <c r="F195" s="10">
-        <v>3143.18</v>
+        <v>3115</v>
       </c>
       <c r="G195" s="13">
         <f>F195/11</f>
-        <v>285.74363636363637</v>
+        <v>283.18181818181819</v>
       </c>
       <c r="H195" s="13">
         <f>F195-G195</f>
-        <v>2857.4363636363632</v>
+        <v>2831.818181818182</v>
       </c>
       <c r="I195" s="13">
         <f>E195-H195</f>
-        <v>1317.5636363636368</v>
+        <v>1168.181818181818</v>
       </c>
       <c r="J195" s="14">
         <f>(E195-H195)/H195</f>
-        <v>0.4610999051915578</v>
+        <v>0.41252006420545739</v>
       </c>
       <c r="K195" s="10" t="s">
         <v>18</v>
@@ -29968,38 +29608,38 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="15">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C196" s="23" t="s">
-        <v>560</v>
+        <v>276</v>
+      </c>
+      <c r="C196" s="23">
+        <v>29151959754</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>561</v>
+        <v>17</v>
       </c>
       <c r="E196" s="10">
-        <v>2070</v>
+        <v>4000</v>
       </c>
       <c r="F196" s="10">
-        <v>1527.53</v>
+        <v>3115</v>
       </c>
       <c r="G196" s="13">
         <f>F196/11</f>
-        <v>138.86636363636364</v>
+        <v>283.18181818181819</v>
       </c>
       <c r="H196" s="13">
         <f>F196-G196</f>
-        <v>1388.6636363636362</v>
+        <v>2831.818181818182</v>
       </c>
       <c r="I196" s="13">
         <f>E196-H196</f>
-        <v>681.33636363636379</v>
+        <v>1168.181818181818</v>
       </c>
       <c r="J196" s="14">
         <f>(E196-H196)/H196</f>
-        <v>0.49064175499008217</v>
+        <v>0.41252006420545739</v>
       </c>
       <c r="K196" s="10" t="s">
         <v>18</v>
@@ -30008,38 +29648,38 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="15">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C197" s="23" t="s">
-        <v>562</v>
+        <v>276</v>
+      </c>
+      <c r="C197" s="23">
+        <v>29690452568</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>561</v>
+        <v>17</v>
       </c>
       <c r="E197" s="10">
-        <v>2070</v>
+        <v>4000</v>
       </c>
       <c r="F197" s="10">
-        <v>1527.53</v>
+        <v>3115</v>
       </c>
       <c r="G197" s="13">
         <f>F197/11</f>
-        <v>138.86636363636364</v>
+        <v>283.18181818181819</v>
       </c>
       <c r="H197" s="13">
         <f>F197-G197</f>
-        <v>1388.6636363636362</v>
+        <v>2831.818181818182</v>
       </c>
       <c r="I197" s="13">
         <f>E197-H197</f>
-        <v>681.33636363636379</v>
+        <v>1168.181818181818</v>
       </c>
       <c r="J197" s="14">
         <f>(E197-H197)/H197</f>
-        <v>0.49064175499008217</v>
+        <v>0.41252006420545739</v>
       </c>
       <c r="K197" s="10" t="s">
         <v>18</v>
@@ -30054,7 +29694,7 @@
         <v>276</v>
       </c>
       <c r="C198" s="23">
-        <v>19670053861</v>
+        <v>41511018445</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>17</v>
@@ -30094,7 +29734,7 @@
         <v>276</v>
       </c>
       <c r="C199" s="23">
-        <v>29151959754</v>
+        <v>41539033418</v>
       </c>
       <c r="D199" s="10" t="s">
         <v>17</v>
@@ -30134,7 +29774,7 @@
         <v>276</v>
       </c>
       <c r="C200" s="23">
-        <v>29690452568</v>
+        <v>41614067465</v>
       </c>
       <c r="D200" s="10" t="s">
         <v>17</v>
@@ -30174,7 +29814,7 @@
         <v>276</v>
       </c>
       <c r="C201" s="23">
-        <v>41511018445</v>
+        <v>41745009481</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>17</v>
@@ -30214,7 +29854,7 @@
         <v>276</v>
       </c>
       <c r="C202" s="23">
-        <v>41539033418</v>
+        <v>51559056134</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>17</v>
@@ -30254,7 +29894,7 @@
         <v>276</v>
       </c>
       <c r="C203" s="23">
-        <v>41614067465</v>
+        <v>61670053428</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>17</v>
@@ -30294,7 +29934,7 @@
         <v>276</v>
       </c>
       <c r="C204" s="23">
-        <v>41745009481</v>
+        <v>61699071496</v>
       </c>
       <c r="D204" s="10" t="s">
         <v>17</v>
@@ -30334,7 +29974,7 @@
         <v>276</v>
       </c>
       <c r="C205" s="23">
-        <v>51559056134</v>
+        <v>69548862359</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>17</v>
@@ -30374,7 +30014,7 @@
         <v>276</v>
       </c>
       <c r="C206" s="23">
-        <v>61670053428</v>
+        <v>79645154464</v>
       </c>
       <c r="D206" s="10" t="s">
         <v>17</v>
@@ -30414,7 +30054,7 @@
         <v>276</v>
       </c>
       <c r="C207" s="23">
-        <v>61699071496</v>
+        <v>89048444551</v>
       </c>
       <c r="D207" s="10" t="s">
         <v>17</v>
@@ -30447,320 +30087,208 @@
       <c r="L207" s="10"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="15">
-        <v>46203</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="C208" s="23">
-        <v>69548862359</v>
-      </c>
-      <c r="D208" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E208" s="10">
-        <v>4000</v>
-      </c>
-      <c r="F208" s="10">
-        <v>3115</v>
-      </c>
-      <c r="G208" s="13">
-        <f>F208/11</f>
-        <v>283.18181818181819</v>
-      </c>
-      <c r="H208" s="13">
-        <f>F208-G208</f>
-        <v>2831.818181818182</v>
-      </c>
-      <c r="I208" s="13">
-        <f>E208-H208</f>
-        <v>1168.181818181818</v>
-      </c>
-      <c r="J208" s="14">
-        <f>(E208-H208)/H208</f>
-        <v>0.41252006420545739</v>
-      </c>
-      <c r="K208" s="10" t="s">
-        <v>18</v>
-      </c>
+      <c r="E208" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="F208" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G208" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="H208" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="J208" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="K208" s="10"/>
       <c r="L208" s="10"/>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="15">
-        <v>46203</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="C209" s="23">
-        <v>79645154464</v>
-      </c>
-      <c r="D209" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E209" s="10">
-        <v>4000</v>
-      </c>
-      <c r="F209" s="10">
-        <v>3115</v>
-      </c>
-      <c r="G209" s="13">
-        <f>F209/11</f>
-        <v>283.18181818181819</v>
-      </c>
-      <c r="H209" s="13">
-        <f>F209-G209</f>
-        <v>2831.818181818182</v>
-      </c>
-      <c r="I209" s="13">
-        <f>E209-H209</f>
-        <v>1168.181818181818</v>
-      </c>
-      <c r="J209" s="14">
-        <f>(E209-H209)/H209</f>
-        <v>0.41252006420545739</v>
-      </c>
-      <c r="K209" s="10" t="s">
-        <v>18</v>
-      </c>
+    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E209" s="7">
+        <f>SUM(E2:E208)</f>
+        <v>653134.99</v>
+      </c>
+      <c r="F209" s="7">
+        <f>SUM(F2:F208)</f>
+        <v>557419.34</v>
+      </c>
+      <c r="G209" s="8">
+        <f>SUM(G2:G208)</f>
+        <v>50674.485454545407</v>
+      </c>
+      <c r="H209" s="8">
+        <f>SUM(H2:H208)</f>
+        <v>506744.85454545484</v>
+      </c>
+      <c r="I209" s="8">
+        <f>SUM(I2:I208)</f>
+        <v>146390.13545454555</v>
+      </c>
+      <c r="J209" s="9">
+        <f>AVERAGE(J2:J208)</f>
+        <v>0.34090331528920426</v>
+      </c>
+      <c r="K209" s="10"/>
       <c r="L209" s="10"/>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="15">
-        <v>46203</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="C210" s="23">
-        <v>89048444551</v>
-      </c>
-      <c r="D210" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E210" s="10">
-        <v>4000</v>
-      </c>
-      <c r="F210" s="10">
-        <v>3115</v>
-      </c>
-      <c r="G210" s="13">
-        <f>F210/11</f>
-        <v>283.18181818181819</v>
-      </c>
-      <c r="H210" s="13">
-        <f>F210-G210</f>
-        <v>2831.818181818182</v>
-      </c>
-      <c r="I210" s="13">
-        <f>E210-H210</f>
-        <v>1168.181818181818</v>
-      </c>
-      <c r="J210" s="14">
-        <f>(E210-H210)/H210</f>
-        <v>0.41252006420545739</v>
-      </c>
-      <c r="K210" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L210" s="10"/>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E211" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="F211" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G211" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="H211" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="I211" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="J211" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="K211" s="10"/>
-      <c r="L211" s="10"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E212" s="7">
-        <f>SUM(E2:E211)</f>
-        <v>657334.99</v>
-      </c>
-      <c r="F212" s="7">
-        <f>SUM(F2:F211)</f>
-        <v>560568.82000000007</v>
-      </c>
-      <c r="G212" s="8">
-        <f>SUM(G2:G211)</f>
-        <v>50960.801818181768</v>
-      </c>
-      <c r="H212" s="8">
-        <f>SUM(H2:H211)</f>
-        <v>509608.01818181848</v>
-      </c>
-      <c r="I212" s="8">
-        <f>SUM(I2:I211)</f>
-        <v>147726.97181818192</v>
-      </c>
-      <c r="J212" s="9">
-        <f>AVERAGE(J2:J211)</f>
-        <v>0.34285112332236367</v>
-      </c>
-      <c r="K212" s="10"/>
-      <c r="L212" s="10"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B216" s="41" t="s">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B213" s="42" t="s">
         <v>583</v>
       </c>
+      <c r="C213" s="21">
+        <v>10691.07</v>
+      </c>
+    </row>
+    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B214" s="43" t="s">
+        <v>584</v>
+      </c>
+      <c r="C214" s="21">
+        <v>15682.45</v>
+      </c>
+    </row>
+    <row r="215" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B215" s="43" t="s">
+        <v>585</v>
+      </c>
+      <c r="C215" s="21">
+        <v>11863.87</v>
+      </c>
+    </row>
+    <row r="216" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B216" s="43" t="s">
+        <v>590</v>
+      </c>
       <c r="C216" s="21">
-        <v>10691.07</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B217" s="42" t="s">
-        <v>584</v>
+        <v>3273.66</v>
+      </c>
+    </row>
+    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B217" s="43" t="s">
+        <v>586</v>
       </c>
       <c r="C217" s="21">
-        <v>15682.45</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B218" s="42" t="s">
-        <v>585</v>
+        <v>15154.99</v>
+      </c>
+    </row>
+    <row r="218" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B218" s="43" t="s">
+        <v>576</v>
       </c>
       <c r="C218" s="21">
-        <v>11863.87</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B219" s="42" t="s">
-        <v>590</v>
-      </c>
-      <c r="C219" s="21">
-        <v>3273.66</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B220" s="42" t="s">
-        <v>586</v>
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B219" s="43" t="s">
+        <v>587</v>
+      </c>
+      <c r="C219" s="32">
+        <v>12303.19</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B220" s="43" t="s">
+        <v>577</v>
       </c>
       <c r="C220" s="21">
-        <v>15154.99</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B221" s="42" t="s">
-        <v>576</v>
+        <v>6337.5</v>
+      </c>
+    </row>
+    <row r="221" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B221" s="43" t="s">
+        <v>578</v>
       </c>
       <c r="C221" s="21">
-        <v>10140</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B222" s="42" t="s">
-        <v>587</v>
-      </c>
-      <c r="C222" s="32">
-        <v>12303.19</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B223" s="42" t="s">
-        <v>577</v>
+        <v>3727.36</v>
+      </c>
+    </row>
+    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B222" s="43" t="s">
+        <v>579</v>
+      </c>
+      <c r="C222" s="21">
+        <v>3727.37</v>
+      </c>
+    </row>
+    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B223" s="43" t="s">
+        <v>580</v>
       </c>
       <c r="C223" s="21">
-        <v>6337.5</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B224" s="42" t="s">
-        <v>578</v>
+        <v>1013.5</v>
+      </c>
+    </row>
+    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B224" s="43" t="s">
+        <v>581</v>
       </c>
       <c r="C224" s="21">
-        <v>3727.36</v>
+        <v>320</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="42" t="s">
-        <v>579</v>
+      <c r="B225" s="43" t="s">
+        <v>582</v>
       </c>
       <c r="C225" s="21">
-        <v>3727.37</v>
+        <v>256</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="42" t="s">
-        <v>580</v>
+      <c r="B226" s="10" t="s">
+        <v>593</v>
       </c>
       <c r="C226" s="21">
-        <v>1013.5</v>
+        <v>4984.16</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="42" t="s">
-        <v>581</v>
-      </c>
-      <c r="C227" s="21">
-        <v>320</v>
-      </c>
+      <c r="B227" s="10"/>
+      <c r="C227" s="21"/>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="42" t="s">
-        <v>582</v>
-      </c>
-      <c r="C228" s="21">
-        <v>256</v>
+      <c r="B228" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C228" s="5">
+        <f>SUM(C213:C227)</f>
+        <v>99475.12000000001</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B229" s="10"/>
       <c r="C229" s="21"/>
     </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B230" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="C230" s="5">
-        <f>SUM(C216:C229)</f>
-        <v>94490.96</v>
-      </c>
-    </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B231" s="10"/>
-      <c r="C231" s="21"/>
-    </row>
-    <row r="232" spans="2:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="B232" s="43" t="s">
+    <row r="230" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B230" s="44" t="s">
         <v>589</v>
       </c>
-      <c r="C232" s="44">
-        <f>I212-C230</f>
-        <v>53236.011818181913</v>
+      <c r="C230" s="45">
+        <f>I209-C228</f>
+        <v>46915.015454545544</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C222">
+  <conditionalFormatting sqref="C219">
     <cfRule type="duplicateValues" dxfId="47" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C222">
+  <conditionalFormatting sqref="C219">
     <cfRule type="duplicateValues" dxfId="46" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C231 C1:C229 C233:C1048576">
+  <conditionalFormatting sqref="C229 C1:C227 C231:C1048576">
     <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C210">
-    <cfRule type="duplicateValues" dxfId="44" priority="39"/>
+  <conditionalFormatting sqref="C218:C222">
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C221:C225">
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+  <conditionalFormatting sqref="C2:C207">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30768,11 +30296,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B5EA52-4A09-4771-8155-97F59FDF1D1A}">
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
     <col min="3" max="3" width="35" style="22" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
@@ -34144,13 +33672,40 @@
       <c r="K87" s="10"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="42" t="s">
+      <c r="B94" s="43" t="s">
         <v>590</v>
+      </c>
+      <c r="C94" s="22">
+        <v>3273.66</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B95" s="41" t="s">
+        <v>591</v>
+      </c>
+      <c r="C95" s="22">
+        <v>5662.62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B96" s="41" t="s">
+        <v>592</v>
+      </c>
+      <c r="C96" s="22">
+        <v>5613.5</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>593</v>
+      </c>
+      <c r="C97" s="22">
+        <v>4984.16</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C85">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35910,12 +35465,15 @@
       <c r="C60" s="33"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="42" t="s">
+      <c r="B61" s="43" t="s">
         <v>590</v>
       </c>
       <c r="C61" s="33"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>593</v>
+      </c>
       <c r="C62" s="33"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -36073,13 +35631,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C53">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C113">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44453,7 +44011,7 @@
       <c r="J262" s="10"/>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B268" s="42" t="s">
+      <c r="B268" s="43" t="s">
         <v>590</v>
       </c>
     </row>
@@ -44678,10 +44236,10 @@
     <sortCondition ref="I2:I260"/>
   </sortState>
   <conditionalFormatting sqref="C2:C260">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46342,115 +45900,115 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C103">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C44 C46:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D93170D-8994-426E-8834-C90E9E6D7D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F283EFE7-8798-47E2-9B73-044008C87A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="595">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1829,6 +1829,9 @@
   </si>
   <si>
     <t>Dubai Office Exp in june 14952.5/3 = 4984.16</t>
+  </si>
+  <si>
+    <t>Dxb &amp; Khi Salary Exp in june  21135.44/3 = 7045.14</t>
   </si>
 </sst>
 </file>
@@ -1978,7 +1981,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2061,6 +2064,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -21816,7 +21820,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6BDDCE-7628-4239-A22E-AFC54CBF13AA}">
-  <dimension ref="A1:L230"/>
+  <dimension ref="A1:L231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -30177,118 +30181,126 @@
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B218" s="43" t="s">
-        <v>576</v>
+      <c r="B218" s="44" t="s">
+        <v>594</v>
       </c>
       <c r="C218" s="21">
-        <v>10140</v>
+        <v>7045.14</v>
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B219" s="43" t="s">
-        <v>587</v>
-      </c>
-      <c r="C219" s="32">
-        <v>12303.19</v>
+        <v>576</v>
+      </c>
+      <c r="C219" s="21">
+        <v>10140</v>
       </c>
     </row>
     <row r="220" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B220" s="43" t="s">
-        <v>577</v>
-      </c>
-      <c r="C220" s="21">
-        <v>6337.5</v>
+        <v>587</v>
+      </c>
+      <c r="C220" s="32">
+        <v>12303.19</v>
       </c>
     </row>
     <row r="221" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B221" s="43" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C221" s="21">
-        <v>3727.36</v>
+        <v>6337.5</v>
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B222" s="43" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C222" s="21">
-        <v>3727.37</v>
+        <v>3727.36</v>
       </c>
     </row>
     <row r="223" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B223" s="43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C223" s="21">
-        <v>1013.5</v>
+        <v>3727.37</v>
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B224" s="43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C224" s="21">
-        <v>320</v>
+        <v>1013.5</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B225" s="43" t="s">
+        <v>581</v>
+      </c>
+      <c r="C225" s="21">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B226" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="C225" s="21">
+      <c r="C226" s="21">
         <v>256</v>
       </c>
     </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="10" t="s">
+    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B227" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="C226" s="21">
+      <c r="C227" s="21">
         <v>4984.16</v>
       </c>
     </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="10"/>
-      <c r="C227" s="21"/>
-    </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="10"/>
+      <c r="C228" s="21"/>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B229" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="C228" s="5">
-        <f>SUM(C213:C227)</f>
-        <v>99475.12000000001</v>
-      </c>
-    </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B229" s="10"/>
-      <c r="C229" s="21"/>
-    </row>
-    <row r="230" spans="2:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="B230" s="44" t="s">
+      <c r="C229" s="5">
+        <f>SUM(C213:C228)</f>
+        <v>106520.26</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B230" s="10"/>
+      <c r="C230" s="21"/>
+    </row>
+    <row r="231" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B231" s="45" t="s">
         <v>589</v>
       </c>
-      <c r="C230" s="45">
-        <f>I209-C228</f>
-        <v>46915.015454545544</v>
+      <c r="C231" s="46">
+        <f>I209-C229</f>
+        <v>39869.875454545559</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C219">
+  <conditionalFormatting sqref="C220">
     <cfRule type="duplicateValues" dxfId="47" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C219">
+  <conditionalFormatting sqref="C220">
     <cfRule type="duplicateValues" dxfId="46" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C229 C1:C227 C231:C1048576">
+  <conditionalFormatting sqref="C230 C1:C228 C232:C1048576">
     <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C218:C222">
+  <conditionalFormatting sqref="C219:C223">
     <cfRule type="duplicateValues" dxfId="44" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C207">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30296,7 +30308,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B5EA52-4A09-4771-8155-97F59FDF1D1A}">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="22" customWidth="1"/>
@@ -33703,9 +33715,17 @@
         <v>4984.16</v>
       </c>
     </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="C98" s="22">
+        <v>7045.14</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C85">
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33717,7 +33737,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="21.7109375" style="22" customWidth="1"/>
     <col min="4" max="4" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
@@ -35477,6 +35497,9 @@
       <c r="C62" s="33"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="44" t="s">
+        <v>594</v>
+      </c>
       <c r="C63" s="34"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -35631,13 +35654,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C53">
-    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C113">
-    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44236,10 +44259,10 @@
     <sortCondition ref="I2:I260"/>
   </sortState>
   <conditionalFormatting sqref="C2:C260">
-    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45900,115 +45923,115 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C103">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C44 C46:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F283EFE7-8798-47E2-9B73-044008C87A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE7CDBB-3BEF-469B-B34A-9101739440E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5189" uniqueCount="598">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1832,6 +1832,15 @@
   </si>
   <si>
     <t>Dxb &amp; Khi Salary Exp in june  21135.44/3 = 7045.14</t>
+  </si>
+  <si>
+    <t>Carry Exp</t>
+  </si>
+  <si>
+    <t>408 Shop Exp</t>
+  </si>
+  <si>
+    <t>Karachi Office Exp</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +1990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2060,6 +2069,9 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -30141,7 +30153,7 @@
       <c r="L209" s="10"/>
     </row>
     <row r="213" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B213" s="42" t="s">
+      <c r="B213" s="43" t="s">
         <v>583</v>
       </c>
       <c r="C213" s="21">
@@ -30149,7 +30161,7 @@
       </c>
     </row>
     <row r="214" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B214" s="43" t="s">
+      <c r="B214" s="44" t="s">
         <v>584</v>
       </c>
       <c r="C214" s="21">
@@ -30157,7 +30169,7 @@
       </c>
     </row>
     <row r="215" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B215" s="43" t="s">
+      <c r="B215" s="44" t="s">
         <v>585</v>
       </c>
       <c r="C215" s="21">
@@ -30165,7 +30177,7 @@
       </c>
     </row>
     <row r="216" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B216" s="43" t="s">
+      <c r="B216" s="44" t="s">
         <v>590</v>
       </c>
       <c r="C216" s="21">
@@ -30173,7 +30185,7 @@
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B217" s="43" t="s">
+      <c r="B217" s="44" t="s">
         <v>586</v>
       </c>
       <c r="C217" s="21">
@@ -30181,7 +30193,7 @@
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B218" s="44" t="s">
+      <c r="B218" s="45" t="s">
         <v>594</v>
       </c>
       <c r="C218" s="21">
@@ -30189,7 +30201,7 @@
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B219" s="43" t="s">
+      <c r="B219" s="44" t="s">
         <v>576</v>
       </c>
       <c r="C219" s="21">
@@ -30197,7 +30209,7 @@
       </c>
     </row>
     <row r="220" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B220" s="43" t="s">
+      <c r="B220" s="44" t="s">
         <v>587</v>
       </c>
       <c r="C220" s="32">
@@ -30205,7 +30217,7 @@
       </c>
     </row>
     <row r="221" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B221" s="43" t="s">
+      <c r="B221" s="44" t="s">
         <v>577</v>
       </c>
       <c r="C221" s="21">
@@ -30213,7 +30225,7 @@
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B222" s="43" t="s">
+      <c r="B222" s="44" t="s">
         <v>578</v>
       </c>
       <c r="C222" s="21">
@@ -30221,7 +30233,7 @@
       </c>
     </row>
     <row r="223" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B223" s="43" t="s">
+      <c r="B223" s="44" t="s">
         <v>579</v>
       </c>
       <c r="C223" s="21">
@@ -30229,7 +30241,7 @@
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B224" s="43" t="s">
+      <c r="B224" s="44" t="s">
         <v>580</v>
       </c>
       <c r="C224" s="21">
@@ -30237,7 +30249,7 @@
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="43" t="s">
+      <c r="B225" s="44" t="s">
         <v>581</v>
       </c>
       <c r="C225" s="21">
@@ -30245,7 +30257,7 @@
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="43" t="s">
+      <c r="B226" s="44" t="s">
         <v>582</v>
       </c>
       <c r="C226" s="21">
@@ -30278,10 +30290,10 @@
       <c r="C230" s="21"/>
     </row>
     <row r="231" spans="2:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="B231" s="45" t="s">
+      <c r="B231" s="46" t="s">
         <v>589</v>
       </c>
-      <c r="C231" s="46">
+      <c r="C231" s="47">
         <f>I209-C229</f>
         <v>39869.875454545559</v>
       </c>
@@ -33684,7 +33696,7 @@
       <c r="K87" s="10"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="43" t="s">
+      <c r="B94" s="44" t="s">
         <v>590</v>
       </c>
       <c r="C94" s="22">
@@ -33716,7 +33728,7 @@
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="44" t="s">
+      <c r="B98" s="45" t="s">
         <v>594</v>
       </c>
       <c r="C98" s="22">
@@ -35485,7 +35497,7 @@
       <c r="C60" s="33"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="43" t="s">
+      <c r="B61" s="44" t="s">
         <v>590</v>
       </c>
       <c r="C61" s="33"/>
@@ -35497,7 +35509,7 @@
       <c r="C62" s="33"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="44" t="s">
+      <c r="B63" s="45" t="s">
         <v>594</v>
       </c>
       <c r="C63" s="34"/>
@@ -44034,7 +44046,7 @@
       <c r="J262" s="10"/>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B268" s="43" t="s">
+      <c r="B268" s="44" t="s">
         <v>590</v>
       </c>
     </row>
@@ -45759,49 +45771,64 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C50" s="33"/>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C51" s="33"/>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C52" s="33"/>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="34"/>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="33"/>
-    </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>595</v>
+      </c>
+      <c r="C53" s="34">
+        <v>8151.89</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>596</v>
+      </c>
+      <c r="C54" s="42">
+        <v>1062.01</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>597</v>
+      </c>
+      <c r="C55" s="42">
+        <v>7677</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C56" s="33"/>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C57" s="33"/>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C58" s="33"/>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C59" s="33"/>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C60" s="33"/>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C61" s="33"/>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C62" s="34"/>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C63" s="33"/>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C64" s="33"/>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.25">

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE7CDBB-3BEF-469B-B34A-9101739440E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219AAD04-B4E6-427C-9FEF-ED731BA8819D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5189" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4801" uniqueCount="598">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -2088,47 +2088,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7AF396E0-14CD-4B92-AB27-039AE1E776EB}"/>
   </cellStyles>
-  <dxfs count="53">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="49">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -21904,19 +21864,19 @@
         <v>1013.35</v>
       </c>
       <c r="G2" s="13">
-        <f>F2/11</f>
+        <f t="shared" ref="G2:G33" si="0">F2/11</f>
         <v>92.122727272727275</v>
       </c>
       <c r="H2" s="13">
-        <f>F2-G2</f>
+        <f t="shared" ref="H2:H33" si="1">F2-G2</f>
         <v>921.22727272727275</v>
       </c>
       <c r="I2" s="13">
-        <f>E2-H2</f>
+        <f t="shared" ref="I2:I33" si="2">E2-H2</f>
         <v>338.77272727272725</v>
       </c>
       <c r="J2" s="14">
-        <f>(E2-H2)/H2</f>
+        <f t="shared" ref="J2:J33" si="3">(E2-H2)/H2</f>
         <v>0.36774066216016182</v>
       </c>
       <c r="K2" s="10" t="s">
@@ -21944,19 +21904,19 @@
         <v>1013.35</v>
       </c>
       <c r="G3" s="13">
-        <f>F3/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H3" s="13">
-        <f>F3-G3</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I3" s="13">
-        <f>E3-H3</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J3" s="14">
-        <f>(E3-H3)/H3</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K3" s="10" t="s">
@@ -21984,19 +21944,19 @@
         <v>1013.35</v>
       </c>
       <c r="G4" s="13">
-        <f>F4/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H4" s="13">
-        <f>F4-G4</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I4" s="13">
-        <f>E4-H4</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J4" s="14">
-        <f>(E4-H4)/H4</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K4" s="10" t="s">
@@ -22024,19 +21984,19 @@
         <v>1013.35</v>
       </c>
       <c r="G5" s="13">
-        <f>F5/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H5" s="13">
-        <f>F5-G5</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I5" s="13">
-        <f>E5-H5</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J5" s="14">
-        <f>(E5-H5)/H5</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K5" s="10" t="s">
@@ -22064,19 +22024,19 @@
         <v>1013.35</v>
       </c>
       <c r="G6" s="13">
-        <f>F6/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H6" s="13">
-        <f>F6-G6</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I6" s="13">
-        <f>E6-H6</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J6" s="14">
-        <f>(E6-H6)/H6</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K6" s="10" t="s">
@@ -22104,19 +22064,19 @@
         <v>1013.35</v>
       </c>
       <c r="G7" s="13">
-        <f>F7/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H7" s="13">
-        <f>F7-G7</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I7" s="13">
-        <f>E7-H7</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J7" s="14">
-        <f>(E7-H7)/H7</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K7" s="10" t="s">
@@ -22144,19 +22104,19 @@
         <v>1013.35</v>
       </c>
       <c r="G8" s="13">
-        <f>F8/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H8" s="13">
-        <f>F8-G8</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I8" s="13">
-        <f>E8-H8</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J8" s="14">
-        <f>(E8-H8)/H8</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K8" s="10" t="s">
@@ -22184,19 +22144,19 @@
         <v>1013.35</v>
       </c>
       <c r="G9" s="13">
-        <f>F9/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H9" s="13">
-        <f>F9-G9</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I9" s="13">
-        <f>E9-H9</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J9" s="14">
-        <f>(E9-H9)/H9</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K9" s="10" t="s">
@@ -22224,19 +22184,19 @@
         <v>1013.35</v>
       </c>
       <c r="G10" s="13">
-        <f>F10/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H10" s="13">
-        <f>F10-G10</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I10" s="13">
-        <f>E10-H10</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J10" s="14">
-        <f>(E10-H10)/H10</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K10" s="10" t="s">
@@ -22264,19 +22224,19 @@
         <v>1013.35</v>
       </c>
       <c r="G11" s="13">
-        <f>F11/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H11" s="13">
-        <f>F11-G11</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I11" s="13">
-        <f>E11-H11</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J11" s="14">
-        <f>(E11-H11)/H11</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K11" s="10" t="s">
@@ -22304,19 +22264,19 @@
         <v>1013.35</v>
       </c>
       <c r="G12" s="13">
-        <f>F12/11</f>
+        <f t="shared" si="0"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H12" s="13">
-        <f>F12-G12</f>
+        <f t="shared" si="1"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I12" s="13">
-        <f>E12-H12</f>
+        <f t="shared" si="2"/>
         <v>338.77272727272725</v>
       </c>
       <c r="J12" s="14">
-        <f>(E12-H12)/H12</f>
+        <f t="shared" si="3"/>
         <v>0.36774066216016182</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -22342,19 +22302,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G13" s="13">
-        <f>F13/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H13" s="13">
-        <f>F13-G13</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I13" s="13">
-        <f>E13-H13</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J13" s="14">
-        <f>(E13-H13)/H13</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K13" s="10" t="s">
@@ -22380,19 +22340,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G14" s="13">
-        <f>F14/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H14" s="13">
-        <f>F14-G14</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I14" s="13">
-        <f>E14-H14</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J14" s="14">
-        <f>(E14-H14)/H14</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K14" s="10" t="s">
@@ -22418,19 +22378,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G15" s="13">
-        <f>F15/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H15" s="13">
-        <f>F15-G15</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I15" s="13">
-        <f>E15-H15</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J15" s="14">
-        <f>(E15-H15)/H15</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K15" s="10" t="s">
@@ -22456,19 +22416,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G16" s="13">
-        <f>F16/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H16" s="13">
-        <f>F16-G16</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I16" s="13">
-        <f>E16-H16</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J16" s="14">
-        <f>(E16-H16)/H16</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K16" s="10" t="s">
@@ -22494,19 +22454,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G17" s="13">
-        <f>F17/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H17" s="13">
-        <f>F17-G17</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I17" s="13">
-        <f>E17-H17</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J17" s="14">
-        <f>(E17-H17)/H17</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K17" s="10" t="s">
@@ -22532,19 +22492,19 @@
         <v>1158.3900000000001</v>
       </c>
       <c r="G18" s="13">
-        <f>F18/11</f>
+        <f t="shared" si="0"/>
         <v>105.30818181818182</v>
       </c>
       <c r="H18" s="13">
-        <f>F18-G18</f>
+        <f t="shared" si="1"/>
         <v>1053.0818181818183</v>
       </c>
       <c r="I18" s="13">
-        <f>E18-H18</f>
+        <f t="shared" si="2"/>
         <v>706.91818181818167</v>
       </c>
       <c r="J18" s="14">
-        <f>(E18-H18)/H18</f>
+        <f t="shared" si="3"/>
         <v>0.67128514576265308</v>
       </c>
       <c r="K18" s="10" t="s">
@@ -22570,19 +22530,19 @@
         <v>1513.37</v>
       </c>
       <c r="G19" s="13">
-        <f>F19/11</f>
+        <f t="shared" si="0"/>
         <v>137.57909090909089</v>
       </c>
       <c r="H19" s="13">
-        <f>F19-G19</f>
+        <f t="shared" si="1"/>
         <v>1375.7909090909091</v>
       </c>
       <c r="I19" s="13">
-        <f>E19-H19</f>
+        <f t="shared" si="2"/>
         <v>657.53909090909087</v>
       </c>
       <c r="J19" s="14">
-        <f>(E19-H19)/H19</f>
+        <f t="shared" si="3"/>
         <v>0.47793533636850205</v>
       </c>
       <c r="K19" s="10" t="s">
@@ -22608,19 +22568,19 @@
         <v>1513.37</v>
       </c>
       <c r="G20" s="13">
-        <f>F20/11</f>
+        <f t="shared" si="0"/>
         <v>137.57909090909089</v>
       </c>
       <c r="H20" s="13">
-        <f>F20-G20</f>
+        <f t="shared" si="1"/>
         <v>1375.7909090909091</v>
       </c>
       <c r="I20" s="13">
-        <f>E20-H20</f>
+        <f t="shared" si="2"/>
         <v>657.53909090909087</v>
       </c>
       <c r="J20" s="14">
-        <f>(E20-H20)/H20</f>
+        <f t="shared" si="3"/>
         <v>0.47793533636850205</v>
       </c>
       <c r="K20" s="10" t="s">
@@ -22646,19 +22606,19 @@
         <v>1513.37</v>
       </c>
       <c r="G21" s="13">
-        <f>F21/11</f>
+        <f t="shared" si="0"/>
         <v>137.57909090909089</v>
       </c>
       <c r="H21" s="13">
-        <f>F21-G21</f>
+        <f t="shared" si="1"/>
         <v>1375.7909090909091</v>
       </c>
       <c r="I21" s="13">
-        <f>E21-H21</f>
+        <f t="shared" si="2"/>
         <v>524.20909090909095</v>
       </c>
       <c r="J21" s="14">
-        <f>(E21-H21)/H21</f>
+        <f t="shared" si="3"/>
         <v>0.38102380779320327</v>
       </c>
       <c r="K21" s="10" t="s">
@@ -22684,19 +22644,19 @@
         <v>1513.37</v>
       </c>
       <c r="G22" s="13">
-        <f>F22/11</f>
+        <f t="shared" si="0"/>
         <v>137.57909090909089</v>
       </c>
       <c r="H22" s="13">
-        <f>F22-G22</f>
+        <f t="shared" si="1"/>
         <v>1375.7909090909091</v>
       </c>
       <c r="I22" s="13">
-        <f>E22-H22</f>
+        <f t="shared" si="2"/>
         <v>524.20909090909095</v>
       </c>
       <c r="J22" s="14">
-        <f>(E22-H22)/H22</f>
+        <f t="shared" si="3"/>
         <v>0.38102380779320327</v>
       </c>
       <c r="K22" s="10" t="s">
@@ -22722,19 +22682,19 @@
         <v>1513.37</v>
       </c>
       <c r="G23" s="13">
-        <f>F23/11</f>
+        <f t="shared" si="0"/>
         <v>137.57909090909089</v>
       </c>
       <c r="H23" s="13">
-        <f>F23-G23</f>
+        <f t="shared" si="1"/>
         <v>1375.7909090909091</v>
       </c>
       <c r="I23" s="13">
-        <f>E23-H23</f>
+        <f t="shared" si="2"/>
         <v>657.53909090909087</v>
       </c>
       <c r="J23" s="14">
-        <f>(E23-H23)/H23</f>
+        <f t="shared" si="3"/>
         <v>0.47793533636850205</v>
       </c>
       <c r="K23" s="10" t="s">
@@ -22762,19 +22722,19 @@
         <v>100</v>
       </c>
       <c r="G24" s="13">
-        <f>F24/11</f>
+        <f t="shared" si="0"/>
         <v>9.0909090909090917</v>
       </c>
       <c r="H24" s="13">
-        <f>F24-G24</f>
+        <f t="shared" si="1"/>
         <v>90.909090909090907</v>
       </c>
       <c r="I24" s="13">
-        <f>E24-H24</f>
+        <f t="shared" si="2"/>
         <v>59.090909090909093</v>
       </c>
       <c r="J24" s="14">
-        <f>(E24-H24)/H24</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="K24" s="10" t="s">
@@ -22802,19 +22762,19 @@
         <v>100</v>
       </c>
       <c r="G25" s="13">
-        <f>F25/11</f>
+        <f t="shared" si="0"/>
         <v>9.0909090909090917</v>
       </c>
       <c r="H25" s="13">
-        <f>F25-G25</f>
+        <f t="shared" si="1"/>
         <v>90.909090909090907</v>
       </c>
       <c r="I25" s="13">
-        <f>E25-H25</f>
+        <f t="shared" si="2"/>
         <v>59.090909090909093</v>
       </c>
       <c r="J25" s="14">
-        <f>(E25-H25)/H25</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="K25" s="10" t="s">
@@ -22842,19 +22802,19 @@
         <v>100</v>
       </c>
       <c r="G26" s="13">
-        <f>F26/11</f>
+        <f t="shared" si="0"/>
         <v>9.0909090909090917</v>
       </c>
       <c r="H26" s="13">
-        <f>F26-G26</f>
+        <f t="shared" si="1"/>
         <v>90.909090909090907</v>
       </c>
       <c r="I26" s="13">
-        <f>E26-H26</f>
+        <f t="shared" si="2"/>
         <v>59.090909090909093</v>
       </c>
       <c r="J26" s="14">
-        <f>(E26-H26)/H26</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="K26" s="10" t="s">
@@ -22882,19 +22842,19 @@
         <v>100</v>
       </c>
       <c r="G27" s="13">
-        <f>F27/11</f>
+        <f t="shared" si="0"/>
         <v>9.0909090909090917</v>
       </c>
       <c r="H27" s="13">
-        <f>F27-G27</f>
+        <f t="shared" si="1"/>
         <v>90.909090909090907</v>
       </c>
       <c r="I27" s="13">
-        <f>E27-H27</f>
+        <f t="shared" si="2"/>
         <v>59.090909090909093</v>
       </c>
       <c r="J27" s="14">
-        <f>(E27-H27)/H27</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="K27" s="10" t="s">
@@ -22920,19 +22880,19 @@
         <v>2082.41</v>
       </c>
       <c r="G28" s="18">
-        <f>F28/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H28" s="18">
-        <f>F28-G28</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I28" s="18">
-        <f>E28-H28</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J28" s="19">
-        <f>(E28-H28)/H28</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K28" s="17" t="s">
@@ -22960,19 +22920,19 @@
         <v>2082.41</v>
       </c>
       <c r="G29" s="18">
-        <f>F29/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H29" s="18">
-        <f>F29-G29</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I29" s="18">
-        <f>E29-H29</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J29" s="19">
-        <f>(E29-H29)/H29</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K29" s="17" t="s">
@@ -23000,19 +22960,19 @@
         <v>2082.41</v>
       </c>
       <c r="G30" s="18">
-        <f>F30/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H30" s="18">
-        <f>F30-G30</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I30" s="18">
-        <f>E30-H30</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J30" s="19">
-        <f>(E30-H30)/H30</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K30" s="17" t="s">
@@ -23040,19 +23000,19 @@
         <v>2082.41</v>
       </c>
       <c r="G31" s="18">
-        <f>F31/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H31" s="18">
-        <f>F31-G31</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I31" s="18">
-        <f>E31-H31</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J31" s="19">
-        <f>(E31-H31)/H31</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K31" s="17" t="s">
@@ -23080,19 +23040,19 @@
         <v>2082.41</v>
       </c>
       <c r="G32" s="18">
-        <f>F32/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H32" s="18">
-        <f>F32-G32</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I32" s="18">
-        <f>E32-H32</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J32" s="19">
-        <f>(E32-H32)/H32</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K32" s="17" t="s">
@@ -23120,19 +23080,19 @@
         <v>2082.41</v>
       </c>
       <c r="G33" s="18">
-        <f>F33/11</f>
+        <f t="shared" si="0"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H33" s="18">
-        <f>F33-G33</f>
+        <f t="shared" si="1"/>
         <v>1893.1</v>
       </c>
       <c r="I33" s="18">
-        <f>E33-H33</f>
+        <f t="shared" si="2"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J33" s="19">
-        <f>(E33-H33)/H33</f>
+        <f t="shared" si="3"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K33" s="17" t="s">
@@ -23160,19 +23120,19 @@
         <v>2082.41</v>
       </c>
       <c r="G34" s="18">
-        <f>F34/11</f>
+        <f t="shared" ref="G34:G65" si="4">F34/11</f>
         <v>189.30999999999997</v>
       </c>
       <c r="H34" s="18">
-        <f>F34-G34</f>
+        <f t="shared" ref="H34:H65" si="5">F34-G34</f>
         <v>1893.1</v>
       </c>
       <c r="I34" s="18">
-        <f>E34-H34</f>
+        <f t="shared" ref="I34:I65" si="6">E34-H34</f>
         <v>-193.09999999999991</v>
       </c>
       <c r="J34" s="19">
-        <f>(E34-H34)/H34</f>
+        <f t="shared" ref="J34:J66" si="7">(E34-H34)/H34</f>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K34" s="17" t="s">
@@ -23200,19 +23160,19 @@
         <v>2082.41</v>
       </c>
       <c r="G35" s="18">
-        <f>F35/11</f>
+        <f t="shared" si="4"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H35" s="18">
-        <f>F35-G35</f>
+        <f t="shared" si="5"/>
         <v>1893.1</v>
       </c>
       <c r="I35" s="18">
-        <f>E35-H35</f>
+        <f t="shared" si="6"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J35" s="19">
-        <f>(E35-H35)/H35</f>
+        <f t="shared" si="7"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K35" s="17" t="s">
@@ -23240,19 +23200,19 @@
         <v>2082.41</v>
       </c>
       <c r="G36" s="18">
-        <f>F36/11</f>
+        <f t="shared" si="4"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H36" s="18">
-        <f>F36-G36</f>
+        <f t="shared" si="5"/>
         <v>1893.1</v>
       </c>
       <c r="I36" s="18">
-        <f>E36-H36</f>
+        <f t="shared" si="6"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J36" s="19">
-        <f>(E36-H36)/H36</f>
+        <f t="shared" si="7"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K36" s="17" t="s">
@@ -23280,19 +23240,19 @@
         <v>2082.41</v>
       </c>
       <c r="G37" s="18">
-        <f>F37/11</f>
+        <f t="shared" si="4"/>
         <v>189.30999999999997</v>
       </c>
       <c r="H37" s="18">
-        <f>F37-G37</f>
+        <f t="shared" si="5"/>
         <v>1893.1</v>
       </c>
       <c r="I37" s="18">
-        <f>E37-H37</f>
+        <f t="shared" si="6"/>
         <v>-193.09999999999991</v>
       </c>
       <c r="J37" s="19">
-        <f>(E37-H37)/H37</f>
+        <f t="shared" si="7"/>
         <v>-0.10200200728963073</v>
       </c>
       <c r="K37" s="17" t="s">
@@ -23322,19 +23282,19 @@
         <v>4856.32</v>
       </c>
       <c r="G38" s="13">
-        <f>F38/11</f>
+        <f t="shared" si="4"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H38" s="13">
-        <f>F38-G38</f>
+        <f t="shared" si="5"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I38" s="13">
-        <f>E38-H38</f>
+        <f t="shared" si="6"/>
         <v>1235.1636363636362</v>
       </c>
       <c r="J38" s="14">
-        <f>(E38-H38)/H38</f>
+        <f t="shared" si="7"/>
         <v>0.27977563257775429</v>
       </c>
       <c r="K38" s="10" t="s">
@@ -23362,19 +23322,19 @@
         <v>4928.41</v>
       </c>
       <c r="G39" s="13">
-        <f>F39/11</f>
+        <f t="shared" si="4"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H39" s="13">
-        <f>F39-G39</f>
+        <f t="shared" si="5"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I39" s="13">
-        <f>E39-H39</f>
+        <f t="shared" si="6"/>
         <v>1119.6272727272726</v>
       </c>
       <c r="J39" s="14">
-        <f>(E39-H39)/H39</f>
+        <f t="shared" si="7"/>
         <v>0.24989601108673992</v>
       </c>
       <c r="K39" s="10" t="s">
@@ -23402,19 +23362,19 @@
         <v>4928.41</v>
       </c>
       <c r="G40" s="13">
-        <f>F40/11</f>
+        <f t="shared" si="4"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H40" s="13">
-        <f>F40-G40</f>
+        <f t="shared" si="5"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I40" s="13">
-        <f>E40-H40</f>
+        <f t="shared" si="6"/>
         <v>1119.6272727272726</v>
       </c>
       <c r="J40" s="14">
-        <f>(E40-H40)/H40</f>
+        <f t="shared" si="7"/>
         <v>0.24989601108673992</v>
       </c>
       <c r="K40" s="10" t="s">
@@ -23442,19 +23402,19 @@
         <v>4856.32</v>
       </c>
       <c r="G41" s="13">
-        <f>F41/11</f>
+        <f t="shared" si="4"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H41" s="13">
-        <f>F41-G41</f>
+        <f t="shared" si="5"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I41" s="13">
-        <f>E41-H41</f>
+        <f t="shared" si="6"/>
         <v>1235.1636363636362</v>
       </c>
       <c r="J41" s="14">
-        <f>(E41-H41)/H41</f>
+        <f t="shared" si="7"/>
         <v>0.27977563257775429</v>
       </c>
       <c r="K41" s="10" t="s">
@@ -23482,19 +23442,19 @@
         <v>928.34</v>
       </c>
       <c r="G42" s="13">
-        <f>F42/11</f>
+        <f t="shared" si="4"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H42" s="13">
-        <f>F42-G42</f>
+        <f t="shared" si="5"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I42" s="13">
-        <f>E42-H42</f>
+        <f t="shared" si="6"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J42" s="14">
-        <f>(E42-H42)/H42</f>
+        <f t="shared" si="7"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K42" s="10" t="s">
@@ -23522,19 +23482,19 @@
         <v>1013.35</v>
       </c>
       <c r="G43" s="13">
-        <f>F43/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H43" s="13">
-        <f>F43-G43</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I43" s="13">
-        <f>E43-H43</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J43" s="14">
-        <f>(E43-H43)/H43</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K43" s="10" t="s">
@@ -23562,19 +23522,19 @@
         <v>1013.35</v>
       </c>
       <c r="G44" s="13">
-        <f>F44/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H44" s="13">
-        <f>F44-G44</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I44" s="13">
-        <f>E44-H44</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J44" s="14">
-        <f>(E44-H44)/H44</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K44" s="10" t="s">
@@ -23602,19 +23562,19 @@
         <v>1018.84</v>
       </c>
       <c r="G45" s="13">
-        <f>F45/11</f>
+        <f t="shared" si="4"/>
         <v>92.621818181818185</v>
       </c>
       <c r="H45" s="13">
-        <f>F45-G45</f>
+        <f t="shared" si="5"/>
         <v>926.21818181818185</v>
       </c>
       <c r="I45" s="13">
-        <f>E45-H45</f>
+        <f t="shared" si="6"/>
         <v>408.78181818181815</v>
       </c>
       <c r="J45" s="14">
-        <f>(E45-H45)/H45</f>
+        <f t="shared" si="7"/>
         <v>0.44134505908680455</v>
       </c>
       <c r="K45" s="10" t="s">
@@ -23642,19 +23602,19 @@
         <v>928.34</v>
       </c>
       <c r="G46" s="13">
-        <f>F46/11</f>
+        <f t="shared" si="4"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H46" s="13">
-        <f>F46-G46</f>
+        <f t="shared" si="5"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I46" s="13">
-        <f>E46-H46</f>
+        <f t="shared" si="6"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J46" s="14">
-        <f>(E46-H46)/H46</f>
+        <f t="shared" si="7"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K46" s="10" t="s">
@@ -23682,19 +23642,19 @@
         <v>1013.35</v>
       </c>
       <c r="G47" s="13">
-        <f>F47/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H47" s="13">
-        <f>F47-G47</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I47" s="13">
-        <f>E47-H47</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J47" s="14">
-        <f>(E47-H47)/H47</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K47" s="10" t="s">
@@ -23722,19 +23682,19 @@
         <v>1013.35</v>
       </c>
       <c r="G48" s="13">
-        <f>F48/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H48" s="13">
-        <f>F48-G48</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I48" s="13">
-        <f>E48-H48</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J48" s="14">
-        <f>(E48-H48)/H48</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K48" s="10" t="s">
@@ -23762,19 +23722,19 @@
         <v>1108.27</v>
       </c>
       <c r="G49" s="13">
-        <f>F49/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H49" s="13">
-        <f>F49-G49</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I49" s="13">
-        <f>E49-H49</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J49" s="14">
-        <f>(E49-H49)/H49</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K49" s="10" t="s">
@@ -23802,19 +23762,19 @@
         <v>1013.35</v>
       </c>
       <c r="G50" s="13">
-        <f>F50/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H50" s="13">
-        <f>F50-G50</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I50" s="13">
-        <f>E50-H50</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J50" s="14">
-        <f>(E50-H50)/H50</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K50" s="10" t="s">
@@ -23842,19 +23802,19 @@
         <v>1108.27</v>
       </c>
       <c r="G51" s="13">
-        <f>F51/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H51" s="13">
-        <f>F51-G51</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I51" s="13">
-        <f>E51-H51</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J51" s="14">
-        <f>(E51-H51)/H51</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K51" s="10" t="s">
@@ -23882,19 +23842,19 @@
         <v>1013.35</v>
       </c>
       <c r="G52" s="13">
-        <f>F52/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H52" s="13">
-        <f>F52-G52</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I52" s="13">
-        <f>E52-H52</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J52" s="14">
-        <f>(E52-H52)/H52</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K52" s="10" t="s">
@@ -23922,19 +23882,19 @@
         <v>1108.27</v>
       </c>
       <c r="G53" s="13">
-        <f>F53/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H53" s="13">
-        <f>F53-G53</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I53" s="13">
-        <f>E53-H53</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J53" s="14">
-        <f>(E53-H53)/H53</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K53" s="10" t="s">
@@ -23962,19 +23922,19 @@
         <v>1013.35</v>
       </c>
       <c r="G54" s="13">
-        <f>F54/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H54" s="13">
-        <f>F54-G54</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I54" s="13">
-        <f>E54-H54</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J54" s="14">
-        <f>(E54-H54)/H54</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K54" s="10" t="s">
@@ -24002,19 +23962,19 @@
         <v>1108.27</v>
       </c>
       <c r="G55" s="13">
-        <f>F55/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H55" s="13">
-        <f>F55-G55</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I55" s="13">
-        <f>E55-H55</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J55" s="14">
-        <f>(E55-H55)/H55</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K55" s="10" t="s">
@@ -24042,19 +24002,19 @@
         <v>1013.35</v>
       </c>
       <c r="G56" s="13">
-        <f>F56/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H56" s="13">
-        <f>F56-G56</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I56" s="13">
-        <f>E56-H56</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J56" s="14">
-        <f>(E56-H56)/H56</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K56" s="10" t="s">
@@ -24082,19 +24042,19 @@
         <v>1108.27</v>
       </c>
       <c r="G57" s="13">
-        <f>F57/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H57" s="13">
-        <f>F57-G57</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I57" s="13">
-        <f>E57-H57</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J57" s="14">
-        <f>(E57-H57)/H57</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K57" s="10" t="s">
@@ -24122,19 +24082,19 @@
         <v>1108.27</v>
       </c>
       <c r="G58" s="13">
-        <f>F58/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H58" s="13">
-        <f>F58-G58</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I58" s="13">
-        <f>E58-H58</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J58" s="14">
-        <f>(E58-H58)/H58</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K58" s="10" t="s">
@@ -24162,19 +24122,19 @@
         <v>928.34</v>
       </c>
       <c r="G59" s="13">
-        <f>F59/11</f>
+        <f t="shared" si="4"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H59" s="13">
-        <f>F59-G59</f>
+        <f t="shared" si="5"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I59" s="13">
-        <f>E59-H59</f>
+        <f t="shared" si="6"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J59" s="14">
-        <f>(E59-H59)/H59</f>
+        <f t="shared" si="7"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K59" s="10" t="s">
@@ -24202,19 +24162,19 @@
         <v>1108.27</v>
       </c>
       <c r="G60" s="13">
-        <f>F60/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H60" s="13">
-        <f>F60-G60</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I60" s="13">
-        <f>E60-H60</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J60" s="14">
-        <f>(E60-H60)/H60</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K60" s="10" t="s">
@@ -24242,19 +24202,19 @@
         <v>1013.35</v>
       </c>
       <c r="G61" s="13">
-        <f>F61/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H61" s="13">
-        <f>F61-G61</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I61" s="13">
-        <f>E61-H61</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J61" s="14">
-        <f>(E61-H61)/H61</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K61" s="10" t="s">
@@ -24282,19 +24242,19 @@
         <v>928.34</v>
       </c>
       <c r="G62" s="13">
-        <f>F62/11</f>
+        <f t="shared" si="4"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H62" s="13">
-        <f>F62-G62</f>
+        <f t="shared" si="5"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I62" s="13">
-        <f>E62-H62</f>
+        <f t="shared" si="6"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J62" s="14">
-        <f>(E62-H62)/H62</f>
+        <f t="shared" si="7"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K62" s="10" t="s">
@@ -24322,19 +24282,19 @@
         <v>1108.27</v>
       </c>
       <c r="G63" s="13">
-        <f>F63/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H63" s="13">
-        <f>F63-G63</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I63" s="13">
-        <f>E63-H63</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J63" s="14">
-        <f>(E63-H63)/H63</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K63" s="10" t="s">
@@ -24362,19 +24322,19 @@
         <v>1108.27</v>
       </c>
       <c r="G64" s="13">
-        <f>F64/11</f>
+        <f t="shared" si="4"/>
         <v>100.75181818181818</v>
       </c>
       <c r="H64" s="13">
-        <f>F64-G64</f>
+        <f t="shared" si="5"/>
         <v>1007.5181818181818</v>
       </c>
       <c r="I64" s="13">
-        <f>E64-H64</f>
+        <f t="shared" si="6"/>
         <v>327.4818181818182</v>
       </c>
       <c r="J64" s="14">
-        <f>(E64-H64)/H64</f>
+        <f t="shared" si="7"/>
         <v>0.32503812247917929</v>
       </c>
       <c r="K64" s="10" t="s">
@@ -24402,19 +24362,19 @@
         <v>1013.35</v>
       </c>
       <c r="G65" s="13">
-        <f>F65/11</f>
+        <f t="shared" si="4"/>
         <v>92.122727272727275</v>
       </c>
       <c r="H65" s="13">
-        <f>F65-G65</f>
+        <f t="shared" si="5"/>
         <v>921.22727272727275</v>
       </c>
       <c r="I65" s="13">
-        <f>E65-H65</f>
+        <f t="shared" si="6"/>
         <v>413.77272727272725</v>
       </c>
       <c r="J65" s="14">
-        <f>(E65-H65)/H65</f>
+        <f t="shared" si="7"/>
         <v>0.44915379681255241</v>
       </c>
       <c r="K65" s="10" t="s">
@@ -24442,19 +24402,19 @@
         <v>928.34</v>
       </c>
       <c r="G66" s="13">
-        <f>F66/11</f>
+        <f t="shared" ref="G66:G97" si="8">F66/11</f>
         <v>84.394545454545451</v>
       </c>
       <c r="H66" s="13">
-        <f>F66-G66</f>
+        <f t="shared" ref="H66:H97" si="9">F66-G66</f>
         <v>843.9454545454546</v>
       </c>
       <c r="I66" s="13">
-        <f>E66-H66</f>
+        <f t="shared" ref="I66:I97" si="10">E66-H66</f>
         <v>491.0545454545454</v>
       </c>
       <c r="J66" s="14">
-        <f>(E66-H66)/H66</f>
+        <f t="shared" si="7"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K66" s="10" t="s">
@@ -24482,19 +24442,19 @@
         <v>1013.35</v>
       </c>
       <c r="G67" s="13">
-        <f t="shared" ref="G67:G130" si="0">F67/11</f>
+        <f t="shared" ref="G67:G130" si="11">F67/11</f>
         <v>92.122727272727275</v>
       </c>
       <c r="H67" s="13">
-        <f t="shared" ref="H67:H130" si="1">F67-G67</f>
+        <f t="shared" ref="H67:H130" si="12">F67-G67</f>
         <v>921.22727272727275</v>
       </c>
       <c r="I67" s="13">
-        <f t="shared" ref="I67:I130" si="2">E67-H67</f>
+        <f t="shared" ref="I67:I130" si="13">E67-H67</f>
         <v>413.77272727272725</v>
       </c>
       <c r="J67" s="14">
-        <f t="shared" ref="J67:J130" si="3">(E67-H67)/H67</f>
+        <f t="shared" ref="J67:J130" si="14">(E67-H67)/H67</f>
         <v>0.44915379681255241</v>
       </c>
       <c r="K67" s="10" t="s">
@@ -24522,19 +24482,19 @@
         <v>928.34</v>
       </c>
       <c r="G68" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H68" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I68" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J68" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K68" s="10" t="s">
@@ -24562,19 +24522,19 @@
         <v>1034</v>
       </c>
       <c r="G69" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H69" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I69" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J69" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K69" s="10" t="s">
@@ -24602,19 +24562,19 @@
         <v>1034</v>
       </c>
       <c r="G70" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H70" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I70" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J70" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K70" s="10" t="s">
@@ -24642,19 +24602,19 @@
         <v>1034</v>
       </c>
       <c r="G71" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H71" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I71" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J71" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K71" s="10" t="s">
@@ -24682,19 +24642,19 @@
         <v>923.17</v>
       </c>
       <c r="G72" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>83.924545454545452</v>
       </c>
       <c r="H72" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>839.24545454545455</v>
       </c>
       <c r="I72" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>495.75454545454545</v>
       </c>
       <c r="J72" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.59071460294420308</v>
       </c>
       <c r="K72" s="10" t="s">
@@ -24722,19 +24682,19 @@
         <v>923.17</v>
       </c>
       <c r="G73" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>83.924545454545452</v>
       </c>
       <c r="H73" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>839.24545454545455</v>
       </c>
       <c r="I73" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>495.75454545454545</v>
       </c>
       <c r="J73" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.59071460294420308</v>
       </c>
       <c r="K73" s="10" t="s">
@@ -24762,19 +24722,19 @@
         <v>1034</v>
       </c>
       <c r="G74" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H74" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I74" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J74" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K74" s="10" t="s">
@@ -24802,19 +24762,19 @@
         <v>1034</v>
       </c>
       <c r="G75" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H75" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I75" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J75" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K75" s="10" t="s">
@@ -24842,19 +24802,19 @@
         <v>1034</v>
       </c>
       <c r="G76" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H76" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I76" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J76" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K76" s="10" t="s">
@@ -24882,19 +24842,19 @@
         <v>1034</v>
       </c>
       <c r="G77" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H77" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I77" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J77" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K77" s="10" t="s">
@@ -24922,19 +24882,19 @@
         <v>1034</v>
       </c>
       <c r="G78" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H78" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I78" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J78" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K78" s="10" t="s">
@@ -24962,19 +24922,19 @@
         <v>1034</v>
       </c>
       <c r="G79" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H79" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I79" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J79" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K79" s="10" t="s">
@@ -25002,19 +24962,19 @@
         <v>928.34</v>
       </c>
       <c r="G80" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>84.394545454545451</v>
       </c>
       <c r="H80" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>843.9454545454546</v>
       </c>
       <c r="I80" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>491.0545454545454</v>
       </c>
       <c r="J80" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.58185578559579454</v>
       </c>
       <c r="K80" s="10" t="s">
@@ -25042,19 +25002,19 @@
         <v>1034</v>
       </c>
       <c r="G81" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H81" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I81" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J81" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K81" s="10" t="s">
@@ -25082,19 +25042,19 @@
         <v>1034</v>
       </c>
       <c r="G82" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H82" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I82" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J82" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K82" s="10" t="s">
@@ -25122,19 +25082,19 @@
         <v>1034</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H83" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I83" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J83" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K83" s="10" t="s">
@@ -25162,19 +25122,19 @@
         <v>923.17</v>
       </c>
       <c r="G84" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>83.924545454545452</v>
       </c>
       <c r="H84" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>839.24545454545455</v>
       </c>
       <c r="I84" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>495.75454545454545</v>
       </c>
       <c r="J84" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.59071460294420308</v>
       </c>
       <c r="K84" s="10" t="s">
@@ -25202,19 +25162,19 @@
         <v>1034</v>
       </c>
       <c r="G85" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H85" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I85" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J85" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K85" s="10" t="s">
@@ -25242,19 +25202,19 @@
         <v>1034</v>
       </c>
       <c r="G86" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H86" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I86" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J86" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K86" s="10" t="s">
@@ -25282,19 +25242,19 @@
         <v>1034</v>
       </c>
       <c r="G87" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H87" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I87" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J87" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K87" s="10" t="s">
@@ -25322,19 +25282,19 @@
         <v>1018.84</v>
       </c>
       <c r="G88" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>92.621818181818185</v>
       </c>
       <c r="H88" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>926.21818181818185</v>
       </c>
       <c r="I88" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>408.78181818181815</v>
       </c>
       <c r="J88" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.44134505908680455</v>
       </c>
       <c r="K88" s="10" t="s">
@@ -25362,19 +25322,19 @@
         <v>1031.77</v>
       </c>
       <c r="G89" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>93.797272727272727</v>
       </c>
       <c r="H89" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>937.9727272727273</v>
       </c>
       <c r="I89" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>397.0272727272727</v>
       </c>
       <c r="J89" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42328232067224281</v>
       </c>
       <c r="K89" s="10" t="s">
@@ -25402,19 +25362,19 @@
         <v>1034</v>
       </c>
       <c r="G90" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H90" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I90" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J90" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K90" s="10" t="s">
@@ -25442,19 +25402,19 @@
         <v>1034</v>
       </c>
       <c r="G91" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H91" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I91" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J91" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K91" s="10" t="s">
@@ -25482,19 +25442,19 @@
         <v>1031.77</v>
       </c>
       <c r="G92" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>93.797272727272727</v>
       </c>
       <c r="H92" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>937.9727272727273</v>
       </c>
       <c r="I92" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>397.0272727272727</v>
       </c>
       <c r="J92" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42328232067224281</v>
       </c>
       <c r="K92" s="10" t="s">
@@ -25522,19 +25482,19 @@
         <v>1034</v>
       </c>
       <c r="G93" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H93" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I93" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J93" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K93" s="10" t="s">
@@ -25562,19 +25522,19 @@
         <v>1034</v>
       </c>
       <c r="G94" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H94" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I94" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J94" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K94" s="10" t="s">
@@ -25602,19 +25562,19 @@
         <v>1034</v>
       </c>
       <c r="G95" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H95" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>940</v>
       </c>
       <c r="I95" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>395</v>
       </c>
       <c r="J95" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.42021276595744683</v>
       </c>
       <c r="K95" s="10" t="s">
@@ -25642,19 +25602,19 @@
         <v>1018.84</v>
       </c>
       <c r="G96" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>92.621818181818185</v>
       </c>
       <c r="H96" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>926.21818181818185</v>
       </c>
       <c r="I96" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>408.78181818181815</v>
       </c>
       <c r="J96" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.44134505908680455</v>
       </c>
       <c r="K96" s="10" t="s">
@@ -25682,19 +25642,19 @@
         <v>304.64</v>
       </c>
       <c r="G97" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H97" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I97" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J97" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K97" s="10" t="s">
@@ -25722,19 +25682,19 @@
         <v>289.41000000000003</v>
       </c>
       <c r="G98" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>26.310000000000002</v>
       </c>
       <c r="H98" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>263.10000000000002</v>
       </c>
       <c r="I98" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>76.899999999999977</v>
       </c>
       <c r="J98" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.29228430254656013</v>
       </c>
       <c r="K98" s="10" t="s">
@@ -25762,19 +25722,19 @@
         <v>304.64</v>
       </c>
       <c r="G99" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H99" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I99" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J99" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K99" s="10" t="s">
@@ -25802,19 +25762,19 @@
         <v>304.64</v>
       </c>
       <c r="G100" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H100" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I100" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J100" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K100" s="10" t="s">
@@ -25842,19 +25802,19 @@
         <v>304.64</v>
       </c>
       <c r="G101" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H101" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I101" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J101" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K101" s="10" t="s">
@@ -25882,19 +25842,19 @@
         <v>286.98</v>
       </c>
       <c r="G102" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>26.08909090909091</v>
       </c>
       <c r="H102" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>260.89090909090913</v>
       </c>
       <c r="I102" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>79.109090909090867</v>
       </c>
       <c r="J102" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.30322670569377635</v>
       </c>
       <c r="K102" s="10" t="s">
@@ -25922,19 +25882,19 @@
         <v>304.64</v>
       </c>
       <c r="G103" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H103" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I103" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J103" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K103" s="10" t="s">
@@ -25962,19 +25922,19 @@
         <v>304.64</v>
       </c>
       <c r="G104" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>27.694545454545452</v>
       </c>
       <c r="H104" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>276.94545454545454</v>
       </c>
       <c r="I104" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>63.054545454545462</v>
       </c>
       <c r="J104" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22767857142857145</v>
       </c>
       <c r="K104" s="10" t="s">
@@ -26002,19 +25962,19 @@
         <v>272.7</v>
       </c>
       <c r="G105" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>24.790909090909089</v>
       </c>
       <c r="H105" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>247.90909090909091</v>
       </c>
       <c r="I105" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>92.090909090909093</v>
       </c>
       <c r="J105" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.37147048038137148</v>
       </c>
       <c r="K105" s="10" t="s">
@@ -26042,19 +26002,19 @@
         <v>272.7</v>
       </c>
       <c r="G106" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>24.790909090909089</v>
       </c>
       <c r="H106" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>247.90909090909091</v>
       </c>
       <c r="I106" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>92.090909090909093</v>
       </c>
       <c r="J106" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.37147048038137148</v>
       </c>
       <c r="K106" s="10" t="s">
@@ -26082,19 +26042,19 @@
         <v>272.7</v>
       </c>
       <c r="G107" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>24.790909090909089</v>
       </c>
       <c r="H107" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>247.90909090909091</v>
       </c>
       <c r="I107" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>92.090909090909093</v>
       </c>
       <c r="J107" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.37147048038137148</v>
       </c>
       <c r="K107" s="10" t="s">
@@ -26122,19 +26082,19 @@
         <v>286.98</v>
       </c>
       <c r="G108" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>26.08909090909091</v>
       </c>
       <c r="H108" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>260.89090909090913</v>
       </c>
       <c r="I108" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>79.109090909090867</v>
       </c>
       <c r="J108" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.30322670569377635</v>
       </c>
       <c r="K108" s="10" t="s">
@@ -26162,19 +26122,19 @@
         <v>4856.32</v>
       </c>
       <c r="G109" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H109" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I109" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J109" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K109" s="10" t="s">
@@ -26202,19 +26162,19 @@
         <v>4926.7</v>
       </c>
       <c r="G110" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H110" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I110" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1121.181818181818</v>
       </c>
       <c r="J110" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.25032983538677001</v>
       </c>
       <c r="K110" s="10" t="s">
@@ -26242,19 +26202,19 @@
         <v>4856.32</v>
       </c>
       <c r="G111" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H111" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I111" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J111" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K111" s="10" t="s">
@@ -26282,19 +26242,19 @@
         <v>4856.32</v>
       </c>
       <c r="G112" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H112" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I112" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J112" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K112" s="10" t="s">
@@ -26322,19 +26282,19 @@
         <v>4926.7</v>
       </c>
       <c r="G113" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H113" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I113" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1121.181818181818</v>
       </c>
       <c r="J113" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.25032983538677001</v>
       </c>
       <c r="K113" s="10" t="s">
@@ -26362,19 +26322,19 @@
         <v>4856.32</v>
       </c>
       <c r="G114" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H114" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I114" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J114" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K114" s="10" t="s">
@@ -26402,19 +26362,19 @@
         <v>4856.32</v>
       </c>
       <c r="G115" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H115" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I115" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J115" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K115" s="10" t="s">
@@ -26442,19 +26402,19 @@
         <v>3371.04</v>
       </c>
       <c r="G116" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>306.4581818181818</v>
       </c>
       <c r="H116" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>3064.5818181818181</v>
       </c>
       <c r="I116" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1035.4181818181819</v>
       </c>
       <c r="J116" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.33786605913901946</v>
       </c>
       <c r="K116" s="10" t="s">
@@ -26482,19 +26442,19 @@
         <v>3374.02</v>
       </c>
       <c r="G117" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>306.72909090909093</v>
       </c>
       <c r="H117" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>3067.2909090909088</v>
       </c>
       <c r="I117" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1032.7090909090912</v>
       </c>
       <c r="J117" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.33668442984926006</v>
       </c>
       <c r="K117" s="10" t="s">
@@ -26522,19 +26482,19 @@
         <v>3371.04</v>
       </c>
       <c r="G118" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>306.4581818181818</v>
       </c>
       <c r="H118" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>3064.5818181818181</v>
       </c>
       <c r="I118" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1135.4181818181819</v>
       </c>
       <c r="J118" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.37049693863021504</v>
       </c>
       <c r="K118" s="10" t="s">
@@ -26562,19 +26522,19 @@
         <v>4928.41</v>
       </c>
       <c r="G119" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H119" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I119" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J119" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K119" s="10" t="s">
@@ -26602,19 +26562,19 @@
         <v>4856.32</v>
       </c>
       <c r="G120" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H120" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I120" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1185.1636363636362</v>
       </c>
       <c r="J120" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26845018450184499</v>
       </c>
       <c r="K120" s="10" t="s">
@@ -26642,19 +26602,19 @@
         <v>4928.41</v>
       </c>
       <c r="G121" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H121" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I121" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J121" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K121" s="10" t="s">
@@ -26682,19 +26642,19 @@
         <v>5373.44</v>
       </c>
       <c r="G122" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>488.4945454545454</v>
       </c>
       <c r="H122" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4884.9454545454546</v>
       </c>
       <c r="I122" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>615.0545454545454</v>
       </c>
       <c r="J122" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.12590817055740827</v>
       </c>
       <c r="K122" s="10" t="s">
@@ -26722,19 +26682,19 @@
         <v>4856.32</v>
       </c>
       <c r="G123" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H123" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I123" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1185.1636363636362</v>
       </c>
       <c r="J123" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.26845018450184499</v>
       </c>
       <c r="K123" s="10" t="s">
@@ -26762,19 +26722,19 @@
         <v>4928.41</v>
       </c>
       <c r="G124" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H124" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I124" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J124" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K124" s="10" t="s">
@@ -26802,19 +26762,19 @@
         <v>4928.41</v>
       </c>
       <c r="G125" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H125" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I125" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J125" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K125" s="10" t="s">
@@ -26842,19 +26802,19 @@
         <v>4928.41</v>
       </c>
       <c r="G126" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H126" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I126" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1119.6272727272726</v>
       </c>
       <c r="J126" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.24989601108673992</v>
       </c>
       <c r="K126" s="10" t="s">
@@ -26882,19 +26842,19 @@
         <v>4928.41</v>
       </c>
       <c r="G127" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H127" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I127" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1119.6272727272726</v>
       </c>
       <c r="J127" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.24989601108673992</v>
       </c>
       <c r="K127" s="10" t="s">
@@ -26922,19 +26882,19 @@
         <v>4928.41</v>
       </c>
       <c r="G128" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H128" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I128" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J128" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K128" s="10" t="s">
@@ -26962,19 +26922,19 @@
         <v>5162.2299999999996</v>
       </c>
       <c r="G129" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>469.29363636363632</v>
       </c>
       <c r="H129" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4692.9363636363632</v>
       </c>
       <c r="I129" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>807.06363636363676</v>
       </c>
       <c r="J129" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.17197412746041935</v>
       </c>
       <c r="K129" s="10" t="s">
@@ -27002,19 +26962,19 @@
         <v>4928.41</v>
       </c>
       <c r="G130" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H130" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I130" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>1019.6272727272726</v>
       </c>
       <c r="J130" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.22757643946019099</v>
       </c>
       <c r="K130" s="10" t="s">
@@ -27042,19 +27002,19 @@
         <v>3069.44</v>
       </c>
       <c r="G131" s="13">
-        <f t="shared" ref="G131:G191" si="4">F131/11</f>
+        <f t="shared" ref="G131:G191" si="15">F131/11</f>
         <v>279.04000000000002</v>
       </c>
       <c r="H131" s="13">
-        <f t="shared" ref="H131:H191" si="5">F131-G131</f>
+        <f t="shared" ref="H131:H191" si="16">F131-G131</f>
         <v>2790.4</v>
       </c>
       <c r="I131" s="13">
-        <f t="shared" ref="I131:I191" si="6">E131-H131</f>
+        <f t="shared" ref="I131:I191" si="17">E131-H131</f>
         <v>1234.5999999999999</v>
       </c>
       <c r="J131" s="14">
-        <f t="shared" ref="J131:J191" si="7">(E131-H131)/H131</f>
+        <f t="shared" ref="J131:J191" si="18">(E131-H131)/H131</f>
         <v>0.44244552752293576</v>
       </c>
       <c r="K131" s="10" t="s">
@@ -27082,19 +27042,19 @@
         <v>3143.18</v>
       </c>
       <c r="G132" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H132" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I132" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J132" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K132" s="10" t="s">
@@ -27122,19 +27082,19 @@
         <v>3069.44</v>
       </c>
       <c r="G133" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>279.04000000000002</v>
       </c>
       <c r="H133" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2790.4</v>
       </c>
       <c r="I133" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1234.5999999999999</v>
       </c>
       <c r="J133" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.44244552752293576</v>
       </c>
       <c r="K133" s="10" t="s">
@@ -27162,19 +27122,19 @@
         <v>3069.44</v>
       </c>
       <c r="G134" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>279.04000000000002</v>
       </c>
       <c r="H134" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2790.4</v>
       </c>
       <c r="I134" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1234.5999999999999</v>
       </c>
       <c r="J134" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.44244552752293576</v>
       </c>
       <c r="K134" s="10" t="s">
@@ -27202,19 +27162,19 @@
         <v>3143.18</v>
       </c>
       <c r="G135" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H135" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I135" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J135" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K135" s="10" t="s">
@@ -27242,19 +27202,19 @@
         <v>3069.44</v>
       </c>
       <c r="G136" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>279.04000000000002</v>
       </c>
       <c r="H136" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2790.4</v>
       </c>
       <c r="I136" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1234.5999999999999</v>
       </c>
       <c r="J136" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.44244552752293576</v>
       </c>
       <c r="K136" s="10" t="s">
@@ -27282,19 +27242,19 @@
         <v>3069.44</v>
       </c>
       <c r="G137" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>279.04000000000002</v>
       </c>
       <c r="H137" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2790.4</v>
       </c>
       <c r="I137" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1234.5999999999999</v>
       </c>
       <c r="J137" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.44244552752293576</v>
       </c>
       <c r="K137" s="10" t="s">
@@ -27322,19 +27282,19 @@
         <v>3143.18</v>
       </c>
       <c r="G138" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H138" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I138" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J138" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K138" s="10" t="s">
@@ -27362,19 +27322,19 @@
         <v>3143.18</v>
       </c>
       <c r="G139" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H139" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I139" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J139" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K139" s="10" t="s">
@@ -27402,19 +27362,19 @@
         <v>3069.44</v>
       </c>
       <c r="G140" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>279.04000000000002</v>
       </c>
       <c r="H140" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2790.4</v>
       </c>
       <c r="I140" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1234.5999999999999</v>
       </c>
       <c r="J140" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.44244552752293576</v>
       </c>
       <c r="K140" s="10" t="s">
@@ -27442,19 +27402,19 @@
         <v>3143.18</v>
       </c>
       <c r="G141" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H141" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I141" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J141" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K141" s="10" t="s">
@@ -27482,19 +27442,19 @@
         <v>3143.18</v>
       </c>
       <c r="G142" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>285.74363636363637</v>
       </c>
       <c r="H142" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>2857.4363636363632</v>
       </c>
       <c r="I142" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1167.5636363636368</v>
       </c>
       <c r="J142" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.40860529781940602</v>
       </c>
       <c r="K142" s="10" t="s">
@@ -27522,19 +27482,19 @@
         <v>928.27</v>
       </c>
       <c r="G143" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>84.38818181818182</v>
       </c>
       <c r="H143" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>843.88181818181818</v>
       </c>
       <c r="I143" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>506.11818181818182</v>
       </c>
       <c r="J143" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.59975007271591241</v>
       </c>
       <c r="K143" s="10" t="s">
@@ -27562,19 +27522,19 @@
         <v>4928.41</v>
       </c>
       <c r="G144" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H144" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I144" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J144" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K144" s="10" t="s">
@@ -27602,19 +27562,19 @@
         <v>4928.41</v>
       </c>
       <c r="G145" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H145" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I145" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J145" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K145" s="10" t="s">
@@ -27642,19 +27602,19 @@
         <v>4928.41</v>
       </c>
       <c r="G146" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H146" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I146" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J146" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K146" s="10" t="s">
@@ -27682,19 +27642,19 @@
         <v>4928.41</v>
       </c>
       <c r="G147" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H147" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I147" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J147" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K147" s="10" t="s">
@@ -27722,19 +27682,19 @@
         <v>4928.41</v>
       </c>
       <c r="G148" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H148" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I148" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J148" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K148" s="10" t="s">
@@ -27762,19 +27722,19 @@
         <v>4926.7</v>
       </c>
       <c r="G149" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H149" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I149" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J149" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K149" s="10" t="s">
@@ -27802,19 +27762,19 @@
         <v>4926.7</v>
       </c>
       <c r="G150" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H150" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I150" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J150" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K150" s="10" t="s">
@@ -27842,19 +27802,19 @@
         <v>4926.7</v>
       </c>
       <c r="G151" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H151" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I151" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J151" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K151" s="10" t="s">
@@ -27882,19 +27842,19 @@
         <v>4926.7</v>
       </c>
       <c r="G152" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H152" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I152" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1221.181818181818</v>
       </c>
       <c r="J152" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.27265715387581946</v>
       </c>
       <c r="K152" s="10" t="s">
@@ -27922,19 +27882,19 @@
         <v>4856.32</v>
       </c>
       <c r="G153" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H153" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I153" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J153" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K153" s="10" t="s">
@@ -27962,19 +27922,19 @@
         <v>4928.41</v>
       </c>
       <c r="G154" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H154" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I154" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J154" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K154" s="10" t="s">
@@ -28002,19 +27962,19 @@
         <v>4856.32</v>
       </c>
       <c r="G155" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H155" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I155" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1160.1636363636362</v>
       </c>
       <c r="J155" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.26278746046389029</v>
       </c>
       <c r="K155" s="10" t="s">
@@ -28042,19 +28002,19 @@
         <v>4856.32</v>
       </c>
       <c r="G156" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H156" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I156" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J156" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K156" s="10" t="s">
@@ -28082,19 +28042,19 @@
         <v>4926.7</v>
       </c>
       <c r="G157" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H157" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I157" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J157" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K157" s="10" t="s">
@@ -28122,19 +28082,19 @@
         <v>4928.41</v>
       </c>
       <c r="G158" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H158" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I158" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J158" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K158" s="10" t="s">
@@ -28162,19 +28122,19 @@
         <v>4928.41</v>
       </c>
       <c r="G159" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H159" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I159" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J159" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K159" s="10" t="s">
@@ -28202,19 +28162,19 @@
         <v>4926.7</v>
       </c>
       <c r="G160" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H160" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I160" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J160" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K160" s="10" t="s">
@@ -28242,19 +28202,19 @@
         <v>4926.7</v>
       </c>
       <c r="G161" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H161" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I161" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1261.181818181818</v>
       </c>
       <c r="J161" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.28158808127143925</v>
       </c>
       <c r="K161" s="10" t="s">
@@ -28282,19 +28242,19 @@
         <v>4856.32</v>
       </c>
       <c r="G162" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H162" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I162" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J162" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K162" s="10" t="s">
@@ -28322,19 +28282,19 @@
         <v>5014.1400000000003</v>
       </c>
       <c r="G163" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>455.83090909090913</v>
       </c>
       <c r="H163" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4558.3090909090915</v>
       </c>
       <c r="I163" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>991.69090909090846</v>
       </c>
       <c r="J163" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21755674951237883</v>
       </c>
       <c r="K163" s="10" t="s">
@@ -28362,19 +28322,19 @@
         <v>4926.7</v>
       </c>
       <c r="G164" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H164" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I164" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1261.181818181818</v>
       </c>
       <c r="J164" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.28158808127143925</v>
       </c>
       <c r="K164" s="10" t="s">
@@ -28402,19 +28362,19 @@
         <v>5014.1400000000003</v>
       </c>
       <c r="G165" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>455.83090909090913</v>
       </c>
       <c r="H165" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4558.3090909090915</v>
       </c>
       <c r="I165" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>991.69090909090846</v>
       </c>
       <c r="J165" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21755674951237883</v>
       </c>
       <c r="K165" s="10" t="s">
@@ -28442,19 +28402,19 @@
         <v>5014.1400000000003</v>
       </c>
       <c r="G166" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>455.83090909090913</v>
       </c>
       <c r="H166" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4558.3090909090915</v>
       </c>
       <c r="I166" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>991.69090909090846</v>
       </c>
       <c r="J166" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21755674951237883</v>
       </c>
       <c r="K166" s="10" t="s">
@@ -28482,19 +28442,19 @@
         <v>5014.1400000000003</v>
       </c>
       <c r="G167" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>455.83090909090913</v>
       </c>
       <c r="H167" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4558.3090909090915</v>
       </c>
       <c r="I167" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>991.69090909090846</v>
       </c>
       <c r="J167" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21755674951237883</v>
       </c>
       <c r="K167" s="10" t="s">
@@ -28522,19 +28482,19 @@
         <v>4856.32</v>
       </c>
       <c r="G168" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H168" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I168" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J168" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K168" s="10" t="s">
@@ -28562,19 +28522,19 @@
         <v>4928.41</v>
       </c>
       <c r="G169" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H169" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I169" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J169" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K169" s="10" t="s">
@@ -28602,19 +28562,19 @@
         <v>4928.41</v>
       </c>
       <c r="G170" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H170" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I170" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J170" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K170" s="10" t="s">
@@ -28642,19 +28602,19 @@
         <v>4856.32</v>
       </c>
       <c r="G171" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H171" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I171" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J171" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K171" s="10" t="s">
@@ -28682,19 +28642,19 @@
         <v>4928.41</v>
       </c>
       <c r="G172" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H172" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I172" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J172" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K172" s="10" t="s">
@@ -28722,19 +28682,19 @@
         <v>4926.7</v>
       </c>
       <c r="G173" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H173" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I173" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1261.181818181818</v>
       </c>
       <c r="J173" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.28158808127143925</v>
       </c>
       <c r="K173" s="10" t="s">
@@ -28762,19 +28722,19 @@
         <v>4928.41</v>
       </c>
       <c r="G174" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H174" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I174" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J174" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K174" s="10" t="s">
@@ -28802,19 +28762,19 @@
         <v>4926.7</v>
       </c>
       <c r="G175" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H175" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I175" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J175" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K175" s="10" t="s">
@@ -28842,19 +28802,19 @@
         <v>5373.44</v>
       </c>
       <c r="G176" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>488.4945454545454</v>
       </c>
       <c r="H176" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4884.9454545454546</v>
       </c>
       <c r="I176" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>665.0545454545454</v>
       </c>
       <c r="J176" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.13614369938065746</v>
       </c>
       <c r="K176" s="10" t="s">
@@ -28882,19 +28842,19 @@
         <v>4928.41</v>
       </c>
       <c r="G177" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H177" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I177" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J177" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K177" s="10" t="s">
@@ -28922,19 +28882,19 @@
         <v>5014.1400000000003</v>
       </c>
       <c r="G178" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>455.83090909090913</v>
       </c>
       <c r="H178" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4558.3090909090915</v>
       </c>
       <c r="I178" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>991.69090909090846</v>
       </c>
       <c r="J178" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21755674951237883</v>
       </c>
       <c r="K178" s="10" t="s">
@@ -28962,19 +28922,19 @@
         <v>4928.41</v>
       </c>
       <c r="G179" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H179" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I179" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1094.6272727272726</v>
       </c>
       <c r="J179" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.24431611818010268</v>
       </c>
       <c r="K179" s="10" t="s">
@@ -29002,19 +28962,19 @@
         <v>4928.41</v>
       </c>
       <c r="G180" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H180" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I180" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J180" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K180" s="10" t="s">
@@ -29042,19 +29002,19 @@
         <v>4928.41</v>
       </c>
       <c r="G181" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H181" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I181" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J181" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K181" s="10" t="s">
@@ -29082,19 +29042,19 @@
         <v>4926.7</v>
       </c>
       <c r="G182" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H182" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I182" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1071.181818181818</v>
       </c>
       <c r="J182" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23916617614224528</v>
       </c>
       <c r="K182" s="10" t="s">
@@ -29122,19 +29082,19 @@
         <v>4928.41</v>
       </c>
       <c r="G183" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H183" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I183" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J183" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K183" s="10" t="s">
@@ -29162,19 +29122,19 @@
         <v>4928.41</v>
       </c>
       <c r="G184" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H184" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I184" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J184" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K184" s="10" t="s">
@@ -29202,19 +29162,19 @@
         <v>4928.41</v>
       </c>
       <c r="G185" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H185" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I185" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J185" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K185" s="10" t="s">
@@ -29242,19 +29202,19 @@
         <v>4928.41</v>
       </c>
       <c r="G186" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H186" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I186" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J186" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K186" s="10" t="s">
@@ -29282,19 +29242,19 @@
         <v>4926.7</v>
       </c>
       <c r="G187" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>447.88181818181818</v>
       </c>
       <c r="H187" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4478.818181818182</v>
       </c>
       <c r="I187" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1221.181818181818</v>
       </c>
       <c r="J187" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.27265715387581946</v>
       </c>
       <c r="K187" s="10" t="s">
@@ -29322,19 +29282,19 @@
         <v>4928.41</v>
       </c>
       <c r="G188" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>448.03727272727269</v>
       </c>
       <c r="H188" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4480.3727272727274</v>
       </c>
       <c r="I188" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1069.6272727272726</v>
       </c>
       <c r="J188" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.23873622527346544</v>
       </c>
       <c r="K188" s="10" t="s">
@@ -29362,19 +29322,19 @@
         <v>4856.32</v>
       </c>
       <c r="G189" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H189" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I189" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J189" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K189" s="10" t="s">
@@ -29402,19 +29362,19 @@
         <v>4856.32</v>
       </c>
       <c r="G190" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>441.48363636363632</v>
       </c>
       <c r="H190" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4414.8363636363638</v>
       </c>
       <c r="I190" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1135.1636363636362</v>
       </c>
       <c r="J190" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25712473642593564</v>
       </c>
       <c r="K190" s="10" t="s">
@@ -29442,19 +29402,19 @@
         <v>10527.57</v>
       </c>
       <c r="G191" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>957.05181818181813</v>
       </c>
       <c r="H191" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>9570.5181818181809</v>
       </c>
       <c r="I191" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>2029.4818181818191</v>
       </c>
       <c r="J191" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.21205558357721691</v>
       </c>
       <c r="K191" s="10" t="s">
@@ -29482,19 +29442,19 @@
         <v>3143.18</v>
       </c>
       <c r="G192" s="13">
-        <f>F192/11</f>
+        <f t="shared" ref="G192:G207" si="19">F192/11</f>
         <v>285.74363636363637</v>
       </c>
       <c r="H192" s="13">
-        <f>F192-G192</f>
+        <f t="shared" ref="H192:H207" si="20">F192-G192</f>
         <v>2857.4363636363632</v>
       </c>
       <c r="I192" s="13">
-        <f>E192-H192</f>
+        <f t="shared" ref="I192:I207" si="21">E192-H192</f>
         <v>1317.5636363636368</v>
       </c>
       <c r="J192" s="14">
-        <f>(E192-H192)/H192</f>
+        <f t="shared" ref="J192:J207" si="22">(E192-H192)/H192</f>
         <v>0.4610999051915578</v>
       </c>
       <c r="K192" s="10" t="s">
@@ -29522,19 +29482,19 @@
         <v>1527.53</v>
       </c>
       <c r="G193" s="13">
-        <f>F193/11</f>
+        <f t="shared" si="19"/>
         <v>138.86636363636364</v>
       </c>
       <c r="H193" s="13">
-        <f>F193-G193</f>
+        <f t="shared" si="20"/>
         <v>1388.6636363636362</v>
       </c>
       <c r="I193" s="13">
-        <f>E193-H193</f>
+        <f t="shared" si="21"/>
         <v>681.33636363636379</v>
       </c>
       <c r="J193" s="14">
-        <f>(E193-H193)/H193</f>
+        <f t="shared" si="22"/>
         <v>0.49064175499008217</v>
       </c>
       <c r="K193" s="10" t="s">
@@ -29562,19 +29522,19 @@
         <v>1527.53</v>
       </c>
       <c r="G194" s="13">
-        <f>F194/11</f>
+        <f t="shared" si="19"/>
         <v>138.86636363636364</v>
       </c>
       <c r="H194" s="13">
-        <f>F194-G194</f>
+        <f t="shared" si="20"/>
         <v>1388.6636363636362</v>
       </c>
       <c r="I194" s="13">
-        <f>E194-H194</f>
+        <f t="shared" si="21"/>
         <v>681.33636363636379</v>
       </c>
       <c r="J194" s="14">
-        <f>(E194-H194)/H194</f>
+        <f t="shared" si="22"/>
         <v>0.49064175499008217</v>
       </c>
       <c r="K194" s="10" t="s">
@@ -29602,19 +29562,19 @@
         <v>3115</v>
       </c>
       <c r="G195" s="13">
-        <f>F195/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H195" s="13">
-        <f>F195-G195</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I195" s="13">
-        <f>E195-H195</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J195" s="14">
-        <f>(E195-H195)/H195</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K195" s="10" t="s">
@@ -29642,19 +29602,19 @@
         <v>3115</v>
       </c>
       <c r="G196" s="13">
-        <f>F196/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H196" s="13">
-        <f>F196-G196</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I196" s="13">
-        <f>E196-H196</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J196" s="14">
-        <f>(E196-H196)/H196</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K196" s="10" t="s">
@@ -29682,19 +29642,19 @@
         <v>3115</v>
       </c>
       <c r="G197" s="13">
-        <f>F197/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H197" s="13">
-        <f>F197-G197</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I197" s="13">
-        <f>E197-H197</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J197" s="14">
-        <f>(E197-H197)/H197</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K197" s="10" t="s">
@@ -29722,19 +29682,19 @@
         <v>3115</v>
       </c>
       <c r="G198" s="13">
-        <f>F198/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H198" s="13">
-        <f>F198-G198</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I198" s="13">
-        <f>E198-H198</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J198" s="14">
-        <f>(E198-H198)/H198</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K198" s="10" t="s">
@@ -29762,19 +29722,19 @@
         <v>3115</v>
       </c>
       <c r="G199" s="13">
-        <f>F199/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H199" s="13">
-        <f>F199-G199</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I199" s="13">
-        <f>E199-H199</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J199" s="14">
-        <f>(E199-H199)/H199</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K199" s="10" t="s">
@@ -29802,19 +29762,19 @@
         <v>3115</v>
       </c>
       <c r="G200" s="13">
-        <f>F200/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H200" s="13">
-        <f>F200-G200</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I200" s="13">
-        <f>E200-H200</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J200" s="14">
-        <f>(E200-H200)/H200</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K200" s="10" t="s">
@@ -29842,19 +29802,19 @@
         <v>3115</v>
       </c>
       <c r="G201" s="13">
-        <f>F201/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H201" s="13">
-        <f>F201-G201</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I201" s="13">
-        <f>E201-H201</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J201" s="14">
-        <f>(E201-H201)/H201</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K201" s="10" t="s">
@@ -29882,19 +29842,19 @@
         <v>3115</v>
       </c>
       <c r="G202" s="13">
-        <f>F202/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H202" s="13">
-        <f>F202-G202</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I202" s="13">
-        <f>E202-H202</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J202" s="14">
-        <f>(E202-H202)/H202</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K202" s="10" t="s">
@@ -29922,19 +29882,19 @@
         <v>3115</v>
       </c>
       <c r="G203" s="13">
-        <f>F203/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H203" s="13">
-        <f>F203-G203</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I203" s="13">
-        <f>E203-H203</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J203" s="14">
-        <f>(E203-H203)/H203</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K203" s="10" t="s">
@@ -29962,19 +29922,19 @@
         <v>3115</v>
       </c>
       <c r="G204" s="13">
-        <f>F204/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H204" s="13">
-        <f>F204-G204</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I204" s="13">
-        <f>E204-H204</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J204" s="14">
-        <f>(E204-H204)/H204</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K204" s="10" t="s">
@@ -30002,19 +29962,19 @@
         <v>3115</v>
       </c>
       <c r="G205" s="13">
-        <f>F205/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H205" s="13">
-        <f>F205-G205</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I205" s="13">
-        <f>E205-H205</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J205" s="14">
-        <f>(E205-H205)/H205</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K205" s="10" t="s">
@@ -30042,19 +30002,19 @@
         <v>3115</v>
       </c>
       <c r="G206" s="13">
-        <f>F206/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H206" s="13">
-        <f>F206-G206</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I206" s="13">
-        <f>E206-H206</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J206" s="14">
-        <f>(E206-H206)/H206</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K206" s="10" t="s">
@@ -30082,19 +30042,19 @@
         <v>3115</v>
       </c>
       <c r="G207" s="13">
-        <f>F207/11</f>
+        <f t="shared" si="19"/>
         <v>283.18181818181819</v>
       </c>
       <c r="H207" s="13">
-        <f>F207-G207</f>
+        <f t="shared" si="20"/>
         <v>2831.818181818182</v>
       </c>
       <c r="I207" s="13">
-        <f>E207-H207</f>
+        <f t="shared" si="21"/>
         <v>1168.181818181818</v>
       </c>
       <c r="J207" s="14">
-        <f>(E207-H207)/H207</f>
+        <f t="shared" si="22"/>
         <v>0.41252006420545739</v>
       </c>
       <c r="K207" s="10" t="s">
@@ -30299,20 +30259,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C220">
-    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
+  <conditionalFormatting sqref="C2:C207">
+    <cfRule type="duplicateValues" dxfId="47" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C219:C223">
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C220">
-    <cfRule type="duplicateValues" dxfId="46" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C230 C1:C228 C232:C1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C219:C223">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C207">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35665,14 +35623,14 @@
       <c r="C113" s="33"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C53">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C113">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35745,11 +35703,11 @@
         <v>2380</v>
       </c>
       <c r="G2" s="10">
-        <f>E2-F2</f>
+        <f t="shared" ref="G2:G33" si="0">E2-F2</f>
         <v>90</v>
       </c>
       <c r="H2" s="14">
-        <f>(E2-F2)/F2</f>
+        <f t="shared" ref="H2:H33" si="1">(E2-F2)/F2</f>
         <v>3.7815126050420166E-2</v>
       </c>
       <c r="I2" s="10" t="s">
@@ -35777,11 +35735,11 @@
         <v>2380</v>
       </c>
       <c r="G3" s="10">
-        <f>E3-F3</f>
+        <f t="shared" si="0"/>
         <v>470</v>
       </c>
       <c r="H3" s="14">
-        <f>(E3-F3)/F3</f>
+        <f t="shared" si="1"/>
         <v>0.19747899159663865</v>
       </c>
       <c r="I3" s="10" t="s">
@@ -35809,11 +35767,11 @@
         <v>2380</v>
       </c>
       <c r="G4" s="10">
-        <f>E4-F4</f>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="H4" s="14">
-        <f>(E4-F4)/F4</f>
+        <f t="shared" si="1"/>
         <v>5.4621848739495799E-2</v>
       </c>
       <c r="I4" s="10" t="s">
@@ -35841,11 +35799,11 @@
         <v>2380</v>
       </c>
       <c r="G5" s="10">
-        <f>E5-F5</f>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="H5" s="14">
-        <f>(E5-F5)/F5</f>
+        <f t="shared" si="1"/>
         <v>5.4621848739495799E-2</v>
       </c>
       <c r="I5" s="10" t="s">
@@ -35873,11 +35831,11 @@
         <v>2380</v>
       </c>
       <c r="G6" s="10">
-        <f>E6-F6</f>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="H6" s="14">
-        <f>(E6-F6)/F6</f>
+        <f t="shared" si="1"/>
         <v>5.4621848739495799E-2</v>
       </c>
       <c r="I6" s="10" t="s">
@@ -35905,11 +35863,11 @@
         <v>2450</v>
       </c>
       <c r="G7" s="10">
-        <f>E7-F7</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H7" s="14">
-        <f>(E7-F7)/F7</f>
+        <f t="shared" si="1"/>
         <v>8.1632653061224497E-3</v>
       </c>
       <c r="I7" s="10" t="s">
@@ -35937,11 +35895,11 @@
         <v>2450</v>
       </c>
       <c r="G8" s="10">
-        <f>E8-F8</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H8" s="14">
-        <f>(E8-F8)/F8</f>
+        <f t="shared" si="1"/>
         <v>8.1632653061224497E-3</v>
       </c>
       <c r="I8" s="10" t="s">
@@ -35969,11 +35927,11 @@
         <v>2450</v>
       </c>
       <c r="G9" s="10">
-        <f>E9-F9</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H9" s="14">
-        <f>(E9-F9)/F9</f>
+        <f t="shared" si="1"/>
         <v>8.1632653061224497E-3</v>
       </c>
       <c r="I9" s="10" t="s">
@@ -36001,11 +35959,11 @@
         <v>2450</v>
       </c>
       <c r="G10" s="10">
-        <f>E10-F10</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H10" s="14">
-        <f>(E10-F10)/F10</f>
+        <f t="shared" si="1"/>
         <v>8.1632653061224497E-3</v>
       </c>
       <c r="I10" s="10" t="s">
@@ -36033,11 +35991,11 @@
         <v>2450</v>
       </c>
       <c r="G11" s="10">
-        <f>E11-F11</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H11" s="14">
-        <f>(E11-F11)/F11</f>
+        <f t="shared" si="1"/>
         <v>8.1632653061224497E-3</v>
       </c>
       <c r="I11" s="10" t="s">
@@ -36065,11 +36023,11 @@
         <v>1800</v>
       </c>
       <c r="G12" s="10">
-        <f>E12-F12</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H12" s="14">
-        <f>(E12-F12)/F12</f>
+        <f t="shared" si="1"/>
         <v>5.5555555555555552E-2</v>
       </c>
       <c r="I12" s="10" t="s">
@@ -36097,11 +36055,11 @@
         <v>2380</v>
       </c>
       <c r="G13" s="10">
-        <f>E13-F13</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="H13" s="14">
-        <f>(E13-F13)/F13</f>
+        <f t="shared" si="1"/>
         <v>1.8907563025210083E-2</v>
       </c>
       <c r="I13" s="10" t="s">
@@ -36129,11 +36087,11 @@
         <v>2380</v>
       </c>
       <c r="G14" s="10">
-        <f>E14-F14</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="H14" s="14">
-        <f>(E14-F14)/F14</f>
+        <f t="shared" si="1"/>
         <v>1.8907563025210083E-2</v>
       </c>
       <c r="I14" s="10" t="s">
@@ -36161,11 +36119,11 @@
         <v>3750</v>
       </c>
       <c r="G15" s="10">
-        <f>E15-F15</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="H15" s="14">
-        <f>(E15-F15)/F15</f>
+        <f t="shared" si="1"/>
         <v>2.1333333333333333E-2</v>
       </c>
       <c r="I15" s="10" t="s">
@@ -36193,11 +36151,11 @@
         <v>1000</v>
       </c>
       <c r="G16" s="10">
-        <f>E16-F16</f>
+        <f t="shared" si="0"/>
         <v>2830</v>
       </c>
       <c r="H16" s="14">
-        <f>(E16-F16)/F16</f>
+        <f t="shared" si="1"/>
         <v>2.83</v>
       </c>
       <c r="I16" s="10" t="s">
@@ -36225,11 +36183,11 @@
         <v>3000</v>
       </c>
       <c r="G17" s="10">
-        <f>E17-F17</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H17" s="14">
-        <f>(E17-F17)/F17</f>
+        <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
       <c r="I17" s="10" t="s">
@@ -36257,11 +36215,11 @@
         <v>3000</v>
       </c>
       <c r="G18" s="10">
-        <f>E18-F18</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H18" s="14">
-        <f>(E18-F18)/F18</f>
+        <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
       <c r="I18" s="10" t="s">
@@ -36289,11 +36247,11 @@
         <v>1080</v>
       </c>
       <c r="G19" s="10">
-        <f>E19-F19</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="H19" s="14">
-        <f>(E19-F19)/F19</f>
+        <f t="shared" si="1"/>
         <v>0.18518518518518517</v>
       </c>
       <c r="I19" s="10" t="s">
@@ -36321,11 +36279,11 @@
         <v>2380</v>
       </c>
       <c r="G20" s="10">
-        <f>E20-F20</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="H20" s="14">
-        <f>(E20-F20)/F20</f>
+        <f t="shared" si="1"/>
         <v>1.8907563025210083E-2</v>
       </c>
       <c r="I20" s="10" t="s">
@@ -36353,11 +36311,11 @@
         <v>2400</v>
       </c>
       <c r="G21" s="17">
-        <f>E21-F21</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H21" s="19">
-        <f>(E21-F21)/F21</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I21" s="17" t="s">
@@ -36387,11 +36345,11 @@
         <v>2400</v>
       </c>
       <c r="G22" s="17">
-        <f>E22-F22</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H22" s="19">
-        <f>(E22-F22)/F22</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I22" s="17" t="s">
@@ -36421,11 +36379,11 @@
         <v>2400</v>
       </c>
       <c r="G23" s="17">
-        <f>E23-F23</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H23" s="19">
-        <f>(E23-F23)/F23</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I23" s="17" t="s">
@@ -36455,11 +36413,11 @@
         <v>2400</v>
       </c>
       <c r="G24" s="17">
-        <f>E24-F24</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H24" s="19">
-        <f>(E24-F24)/F24</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I24" s="17" t="s">
@@ -36489,11 +36447,11 @@
         <v>2400</v>
       </c>
       <c r="G25" s="17">
-        <f>E25-F25</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H25" s="19">
-        <f>(E25-F25)/F25</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I25" s="17" t="s">
@@ -36523,11 +36481,11 @@
         <v>2400</v>
       </c>
       <c r="G26" s="17">
-        <f>E26-F26</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H26" s="19">
-        <f>(E26-F26)/F26</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I26" s="17" t="s">
@@ -36557,11 +36515,11 @@
         <v>2400</v>
       </c>
       <c r="G27" s="17">
-        <f>E27-F27</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H27" s="19">
-        <f>(E27-F27)/F27</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I27" s="17" t="s">
@@ -36591,11 +36549,11 @@
         <v>2400</v>
       </c>
       <c r="G28" s="17">
-        <f>E28-F28</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H28" s="19">
-        <f>(E28-F28)/F28</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I28" s="17" t="s">
@@ -36625,11 +36583,11 @@
         <v>2400</v>
       </c>
       <c r="G29" s="17">
-        <f>E29-F29</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="H29" s="19">
-        <f>(E29-F29)/F29</f>
+        <f t="shared" si="1"/>
         <v>-2.0833333333333332E-2</v>
       </c>
       <c r="I29" s="17" t="s">
@@ -36659,11 +36617,11 @@
         <v>2450</v>
       </c>
       <c r="G30" s="17">
-        <f>E30-F30</f>
+        <f t="shared" si="0"/>
         <v>-100</v>
       </c>
       <c r="H30" s="19">
-        <f>(E30-F30)/F30</f>
+        <f t="shared" si="1"/>
         <v>-4.0816326530612242E-2</v>
       </c>
       <c r="I30" s="17" t="s">
@@ -36693,11 +36651,11 @@
         <v>3500</v>
       </c>
       <c r="G31" s="10">
-        <f>E31-F31</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H31" s="14">
-        <f>(E31-F31)/F31</f>
+        <f t="shared" si="1"/>
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I31" s="10" t="s">
@@ -36725,11 +36683,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G32" s="10">
-        <f>E32-F32</f>
+        <f t="shared" si="0"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H32" s="14">
-        <f>(E32-F32)/F32</f>
+        <f t="shared" si="1"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I32" s="10" t="s">
@@ -36757,11 +36715,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G33" s="10">
-        <f>E33-F33</f>
+        <f t="shared" si="0"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H33" s="14">
-        <f>(E33-F33)/F33</f>
+        <f t="shared" si="1"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I33" s="10" t="s">
@@ -36789,11 +36747,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G34" s="10">
-        <f>E34-F34</f>
+        <f t="shared" ref="G34:G65" si="2">E34-F34</f>
         <v>95.949999999999818</v>
       </c>
       <c r="H34" s="14">
-        <f>(E34-F34)/F34</f>
+        <f t="shared" ref="H34:H65" si="3">(E34-F34)/F34</f>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I34" s="10" t="s">
@@ -36821,11 +36779,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G35" s="10">
-        <f>E35-F35</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H35" s="14">
-        <f>(E35-F35)/F35</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I35" s="10" t="s">
@@ -36853,11 +36811,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G36" s="10">
-        <f>E36-F36</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H36" s="14">
-        <f>(E36-F36)/F36</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I36" s="10" t="s">
@@ -36885,11 +36843,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G37" s="10">
-        <f>E37-F37</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H37" s="14">
-        <f>(E37-F37)/F37</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I37" s="10" t="s">
@@ -36917,11 +36875,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G38" s="10">
-        <f>E38-F38</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H38" s="14">
-        <f>(E38-F38)/F38</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I38" s="10" t="s">
@@ -36949,11 +36907,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G39" s="10">
-        <f>E39-F39</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H39" s="14">
-        <f>(E39-F39)/F39</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I39" s="10" t="s">
@@ -36981,11 +36939,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G40" s="10">
-        <f>E40-F40</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H40" s="14">
-        <f>(E40-F40)/F40</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I40" s="10" t="s">
@@ -37013,11 +36971,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G41" s="10">
-        <f>E41-F41</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H41" s="14">
-        <f>(E41-F41)/F41</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I41" s="10" t="s">
@@ -37045,11 +37003,11 @@
         <v>2374.0500000000002</v>
       </c>
       <c r="G42" s="10">
-        <f>E42-F42</f>
+        <f t="shared" si="2"/>
         <v>95.949999999999818</v>
       </c>
       <c r="H42" s="14">
-        <f>(E42-F42)/F42</f>
+        <f t="shared" si="3"/>
         <v>4.0416166466586557E-2</v>
       </c>
       <c r="I42" s="10" t="s">
@@ -37077,11 +37035,11 @@
         <v>1999.2</v>
       </c>
       <c r="G43" s="10">
-        <f>E43-F43</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H43" s="14">
-        <f>(E43-F43)/F43</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I43" s="10" t="s">
@@ -37109,11 +37067,11 @@
         <v>1999.2</v>
       </c>
       <c r="G44" s="10">
-        <f>E44-F44</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H44" s="14">
-        <f>(E44-F44)/F44</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I44" s="10" t="s">
@@ -37141,11 +37099,11 @@
         <v>1999.2</v>
       </c>
       <c r="G45" s="10">
-        <f>E45-F45</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H45" s="14">
-        <f>(E45-F45)/F45</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I45" s="10" t="s">
@@ -37173,11 +37131,11 @@
         <v>1999.2</v>
       </c>
       <c r="G46" s="10">
-        <f>E46-F46</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H46" s="14">
-        <f>(E46-F46)/F46</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I46" s="10" t="s">
@@ -37205,11 +37163,11 @@
         <v>1999.2</v>
       </c>
       <c r="G47" s="10">
-        <f>E47-F47</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H47" s="14">
-        <f>(E47-F47)/F47</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I47" s="10" t="s">
@@ -37237,11 +37195,11 @@
         <v>1999.2</v>
       </c>
       <c r="G48" s="10">
-        <f>E48-F48</f>
+        <f t="shared" si="2"/>
         <v>35.799999999999955</v>
       </c>
       <c r="H48" s="14">
-        <f>(E48-F48)/F48</f>
+        <f t="shared" si="3"/>
         <v>1.7907162865146035E-2</v>
       </c>
       <c r="I48" s="10" t="s">
@@ -37269,11 +37227,11 @@
         <v>2856</v>
       </c>
       <c r="G49" s="10">
-        <f>E49-F49</f>
+        <f t="shared" si="2"/>
         <v>264</v>
       </c>
       <c r="H49" s="14">
-        <f>(E49-F49)/F49</f>
+        <f t="shared" si="3"/>
         <v>9.2436974789915971E-2</v>
       </c>
       <c r="I49" s="10" t="s">
@@ -37301,11 +37259,11 @@
         <v>3659.25</v>
       </c>
       <c r="G50" s="10">
-        <f>E50-F50</f>
+        <f t="shared" si="2"/>
         <v>40.75</v>
       </c>
       <c r="H50" s="14">
-        <f>(E50-F50)/F50</f>
+        <f t="shared" si="3"/>
         <v>1.1136161781785885E-2</v>
       </c>
       <c r="I50" s="10" t="s">
@@ -37333,11 +37291,11 @@
         <v>3659.25</v>
       </c>
       <c r="G51" s="10">
-        <f>E51-F51</f>
+        <f t="shared" si="2"/>
         <v>40.75</v>
       </c>
       <c r="H51" s="14">
-        <f>(E51-F51)/F51</f>
+        <f t="shared" si="3"/>
         <v>1.1136161781785885E-2</v>
       </c>
       <c r="I51" s="10" t="s">
@@ -37365,11 +37323,11 @@
         <v>3659.25</v>
       </c>
       <c r="G52" s="10">
-        <f>E52-F52</f>
+        <f t="shared" si="2"/>
         <v>40.75</v>
       </c>
       <c r="H52" s="14">
-        <f>(E52-F52)/F52</f>
+        <f t="shared" si="3"/>
         <v>1.1136161781785885E-2</v>
       </c>
       <c r="I52" s="10" t="s">
@@ -37397,11 +37355,11 @@
         <v>3677.1</v>
       </c>
       <c r="G53" s="10">
-        <f>E53-F53</f>
+        <f t="shared" si="2"/>
         <v>122.90000000000009</v>
       </c>
       <c r="H53" s="14">
-        <f>(E53-F53)/F53</f>
+        <f t="shared" si="3"/>
         <v>3.3423077969051723E-2</v>
       </c>
       <c r="I53" s="10" t="s">
@@ -37429,11 +37387,11 @@
         <v>3677.1</v>
       </c>
       <c r="G54" s="10">
-        <f>E54-F54</f>
+        <f t="shared" si="2"/>
         <v>122.90000000000009</v>
       </c>
       <c r="H54" s="14">
-        <f>(E54-F54)/F54</f>
+        <f t="shared" si="3"/>
         <v>3.3423077969051723E-2</v>
       </c>
       <c r="I54" s="10" t="s">
@@ -37461,11 +37419,11 @@
         <v>3659.25</v>
       </c>
       <c r="G55" s="10">
-        <f>E55-F55</f>
+        <f t="shared" si="2"/>
         <v>140.75</v>
       </c>
       <c r="H55" s="14">
-        <f>(E55-F55)/F55</f>
+        <f t="shared" si="3"/>
         <v>3.8464166154266587E-2</v>
       </c>
       <c r="I55" s="10" t="s">
@@ -37493,11 +37451,11 @@
         <v>3677.1</v>
       </c>
       <c r="G56" s="10">
-        <f>E56-F56</f>
+        <f t="shared" si="2"/>
         <v>122.90000000000009</v>
       </c>
       <c r="H56" s="14">
-        <f>(E56-F56)/F56</f>
+        <f t="shared" si="3"/>
         <v>3.3423077969051723E-2</v>
       </c>
       <c r="I56" s="10" t="s">
@@ -37525,11 +37483,11 @@
         <v>3659.25</v>
       </c>
       <c r="G57" s="10">
-        <f>E57-F57</f>
+        <f t="shared" si="2"/>
         <v>140.75</v>
       </c>
       <c r="H57" s="14">
-        <f>(E57-F57)/F57</f>
+        <f t="shared" si="3"/>
         <v>3.8464166154266587E-2</v>
       </c>
       <c r="I57" s="10" t="s">
@@ -37557,11 +37515,11 @@
         <v>3659.25</v>
       </c>
       <c r="G58" s="10">
-        <f>E58-F58</f>
+        <f t="shared" si="2"/>
         <v>140.75</v>
       </c>
       <c r="H58" s="14">
-        <f>(E58-F58)/F58</f>
+        <f t="shared" si="3"/>
         <v>3.8464166154266587E-2</v>
       </c>
       <c r="I58" s="10" t="s">
@@ -37589,11 +37547,11 @@
         <v>3677.1</v>
       </c>
       <c r="G59" s="10">
-        <f>E59-F59</f>
+        <f t="shared" si="2"/>
         <v>122.90000000000009</v>
       </c>
       <c r="H59" s="14">
-        <f>(E59-F59)/F59</f>
+        <f t="shared" si="3"/>
         <v>3.3423077969051723E-2</v>
       </c>
       <c r="I59" s="10" t="s">
@@ -37621,11 +37579,11 @@
         <v>3659.25</v>
       </c>
       <c r="G60" s="10">
-        <f>E60-F60</f>
+        <f t="shared" si="2"/>
         <v>140.75</v>
       </c>
       <c r="H60" s="14">
-        <f>(E60-F60)/F60</f>
+        <f t="shared" si="3"/>
         <v>3.8464166154266587E-2</v>
       </c>
       <c r="I60" s="10" t="s">
@@ -37653,11 +37611,11 @@
         <v>1249.5</v>
       </c>
       <c r="G61" s="10">
-        <f>E61-F61</f>
+        <f t="shared" si="2"/>
         <v>70.5</v>
       </c>
       <c r="H61" s="14">
-        <f>(E61-F61)/F61</f>
+        <f t="shared" si="3"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I61" s="10" t="s">
@@ -37685,11 +37643,11 @@
         <v>1249.5</v>
       </c>
       <c r="G62" s="10">
-        <f>E62-F62</f>
+        <f t="shared" si="2"/>
         <v>70.5</v>
       </c>
       <c r="H62" s="14">
-        <f>(E62-F62)/F62</f>
+        <f t="shared" si="3"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I62" s="10" t="s">
@@ -37717,11 +37675,11 @@
         <v>1249.5</v>
       </c>
       <c r="G63" s="10">
-        <f>E63-F63</f>
+        <f t="shared" si="2"/>
         <v>70.5</v>
       </c>
       <c r="H63" s="14">
-        <f>(E63-F63)/F63</f>
+        <f t="shared" si="3"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I63" s="10" t="s">
@@ -37749,11 +37707,11 @@
         <v>1249.5</v>
       </c>
       <c r="G64" s="10">
-        <f>E64-F64</f>
+        <f t="shared" si="2"/>
         <v>70.5</v>
       </c>
       <c r="H64" s="14">
-        <f>(E64-F64)/F64</f>
+        <f t="shared" si="3"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I64" s="10" t="s">
@@ -37781,11 +37739,11 @@
         <v>1249.5</v>
       </c>
       <c r="G65" s="10">
-        <f>E65-F65</f>
+        <f t="shared" si="2"/>
         <v>70.5</v>
       </c>
       <c r="H65" s="14">
-        <f>(E65-F65)/F65</f>
+        <f t="shared" si="3"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I65" s="10" t="s">
@@ -37813,11 +37771,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G66" s="10">
-        <f>E66-F66</f>
+        <f t="shared" ref="G66:G97" si="4">E66-F66</f>
         <v>141.90000000000009</v>
       </c>
       <c r="H66" s="14">
-        <f>(E66-F66)/F66</f>
+        <f t="shared" ref="H66:H97" si="5">(E66-F66)/F66</f>
         <v>0.12044817927170877</v>
       </c>
       <c r="I66" s="10" t="s">
@@ -37845,11 +37803,11 @@
         <v>1249.5</v>
       </c>
       <c r="G67" s="10">
-        <f>E67-F67</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H67" s="14">
-        <f>(E67-F67)/F67</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I67" s="10" t="s">
@@ -37877,11 +37835,11 @@
         <v>1249.5</v>
       </c>
       <c r="G68" s="10">
-        <f>E68-F68</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H68" s="14">
-        <f>(E68-F68)/F68</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I68" s="10" t="s">
@@ -37909,11 +37867,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G69" s="10">
-        <f>E69-F69</f>
+        <f t="shared" si="4"/>
         <v>141.90000000000009</v>
       </c>
       <c r="H69" s="14">
-        <f>(E69-F69)/F69</f>
+        <f t="shared" si="5"/>
         <v>0.12044817927170877</v>
       </c>
       <c r="I69" s="10" t="s">
@@ -37941,11 +37899,11 @@
         <v>1249.5</v>
       </c>
       <c r="G70" s="10">
-        <f>E70-F70</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H70" s="14">
-        <f>(E70-F70)/F70</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I70" s="10" t="s">
@@ -37973,11 +37931,11 @@
         <v>1249.5</v>
       </c>
       <c r="G71" s="10">
-        <f>E71-F71</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H71" s="14">
-        <f>(E71-F71)/F71</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I71" s="10" t="s">
@@ -38005,11 +37963,11 @@
         <v>1249.5</v>
       </c>
       <c r="G72" s="10">
-        <f>E72-F72</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H72" s="14">
-        <f>(E72-F72)/F72</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I72" s="10" t="s">
@@ -38037,11 +37995,11 @@
         <v>1249.5</v>
       </c>
       <c r="G73" s="10">
-        <f>E73-F73</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H73" s="14">
-        <f>(E73-F73)/F73</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I73" s="10" t="s">
@@ -38069,11 +38027,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G74" s="10">
-        <f>E74-F74</f>
+        <f t="shared" si="4"/>
         <v>141.90000000000009</v>
       </c>
       <c r="H74" s="14">
-        <f>(E74-F74)/F74</f>
+        <f t="shared" si="5"/>
         <v>0.12044817927170877</v>
       </c>
       <c r="I74" s="10" t="s">
@@ -38101,11 +38059,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G75" s="10">
-        <f>E75-F75</f>
+        <f t="shared" si="4"/>
         <v>141.90000000000009</v>
       </c>
       <c r="H75" s="14">
-        <f>(E75-F75)/F75</f>
+        <f t="shared" si="5"/>
         <v>0.12044817927170877</v>
       </c>
       <c r="I75" s="10" t="s">
@@ -38133,11 +38091,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G76" s="10">
-        <f>E76-F76</f>
+        <f t="shared" si="4"/>
         <v>141.90000000000009</v>
       </c>
       <c r="H76" s="14">
-        <f>(E76-F76)/F76</f>
+        <f t="shared" si="5"/>
         <v>0.12044817927170877</v>
       </c>
       <c r="I76" s="10" t="s">
@@ -38165,11 +38123,11 @@
         <v>1249.5</v>
       </c>
       <c r="G77" s="10">
-        <f>E77-F77</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H77" s="14">
-        <f>(E77-F77)/F77</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I77" s="10" t="s">
@@ -38197,11 +38155,11 @@
         <v>1249.5</v>
       </c>
       <c r="G78" s="10">
-        <f>E78-F78</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H78" s="14">
-        <f>(E78-F78)/F78</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I78" s="10" t="s">
@@ -38229,11 +38187,11 @@
         <v>1249.5</v>
       </c>
       <c r="G79" s="10">
-        <f>E79-F79</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H79" s="14">
-        <f>(E79-F79)/F79</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I79" s="10" t="s">
@@ -38261,11 +38219,11 @@
         <v>1249.5</v>
       </c>
       <c r="G80" s="10">
-        <f>E80-F80</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H80" s="14">
-        <f>(E80-F80)/F80</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I80" s="10" t="s">
@@ -38293,11 +38251,11 @@
         <v>1249.5</v>
       </c>
       <c r="G81" s="10">
-        <f>E81-F81</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H81" s="14">
-        <f>(E81-F81)/F81</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I81" s="10" t="s">
@@ -38325,11 +38283,11 @@
         <v>1249.5</v>
       </c>
       <c r="G82" s="10">
-        <f>E82-F82</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H82" s="14">
-        <f>(E82-F82)/F82</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I82" s="10" t="s">
@@ -38357,11 +38315,11 @@
         <v>1249.5</v>
       </c>
       <c r="G83" s="10">
-        <f>E83-F83</f>
+        <f t="shared" si="4"/>
         <v>270.5</v>
       </c>
       <c r="H83" s="14">
-        <f>(E83-F83)/F83</f>
+        <f t="shared" si="5"/>
         <v>0.21648659463785513</v>
       </c>
       <c r="I83" s="10" t="s">
@@ -38389,11 +38347,11 @@
         <v>1178.0999999999999</v>
       </c>
       <c r="G84" s="10">
-        <f>E84-F84</f>
+        <f t="shared" si="4"/>
         <v>341.90000000000009</v>
       </c>
       <c r="H84" s="14">
-        <f>(E84-F84)/F84</f>
+        <f t="shared" si="5"/>
         <v>0.2902130549189374</v>
       </c>
       <c r="I84" s="10" t="s">
@@ -38421,11 +38379,11 @@
         <v>1249.5</v>
       </c>
       <c r="G85" s="10">
-        <f>E85-F85</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H85" s="14">
-        <f>(E85-F85)/F85</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I85" s="10" t="s">
@@ -38453,11 +38411,11 @@
         <v>1249.5</v>
       </c>
       <c r="G86" s="10">
-        <f>E86-F86</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="H86" s="14">
-        <f>(E86-F86)/F86</f>
+        <f t="shared" si="5"/>
         <v>5.6422569027611044E-2</v>
       </c>
       <c r="I86" s="10" t="s">
@@ -38485,11 +38443,11 @@
         <v>1999.2</v>
       </c>
       <c r="G87" s="10">
-        <f>E87-F87</f>
+        <f t="shared" si="4"/>
         <v>40.799999999999955</v>
       </c>
       <c r="H87" s="14">
-        <f>(E87-F87)/F87</f>
+        <f t="shared" si="5"/>
         <v>2.04081632653061E-2</v>
       </c>
       <c r="I87" s="10" t="s">
@@ -38517,11 +38475,11 @@
         <v>1999.2</v>
       </c>
       <c r="G88" s="10">
-        <f>E88-F88</f>
+        <f t="shared" si="4"/>
         <v>40.799999999999955</v>
       </c>
       <c r="H88" s="14">
-        <f>(E88-F88)/F88</f>
+        <f t="shared" si="5"/>
         <v>2.04081632653061E-2</v>
       </c>
       <c r="I88" s="10" t="s">
@@ -38549,11 +38507,11 @@
         <v>1999.2</v>
       </c>
       <c r="G89" s="10">
-        <f>E89-F89</f>
+        <f t="shared" si="4"/>
         <v>40.799999999999955</v>
       </c>
       <c r="H89" s="14">
-        <f>(E89-F89)/F89</f>
+        <f t="shared" si="5"/>
         <v>2.04081632653061E-2</v>
       </c>
       <c r="I89" s="10" t="s">
@@ -38581,11 +38539,11 @@
         <v>1124.55</v>
       </c>
       <c r="G90" s="10">
-        <f>E90-F90</f>
+        <f t="shared" si="4"/>
         <v>85.450000000000045</v>
       </c>
       <c r="H90" s="14">
-        <f>(E90-F90)/F90</f>
+        <f t="shared" si="5"/>
         <v>7.5985949935529817E-2</v>
       </c>
       <c r="I90" s="10" t="s">
@@ -38613,11 +38571,11 @@
         <v>1124.55</v>
       </c>
       <c r="G91" s="10">
-        <f>E91-F91</f>
+        <f t="shared" si="4"/>
         <v>85.450000000000045</v>
       </c>
       <c r="H91" s="14">
-        <f>(E91-F91)/F91</f>
+        <f t="shared" si="5"/>
         <v>7.5985949935529817E-2</v>
       </c>
       <c r="I91" s="10" t="s">
@@ -38643,11 +38601,11 @@
         <v>481.95</v>
       </c>
       <c r="G92" s="10">
-        <f>E92-F92</f>
+        <f t="shared" si="4"/>
         <v>18.050000000000011</v>
       </c>
       <c r="H92" s="14">
-        <f>(E92-F92)/F92</f>
+        <f t="shared" si="5"/>
         <v>3.7452017844174734E-2</v>
       </c>
       <c r="I92" s="10" t="s">
@@ -38675,11 +38633,11 @@
         <v>481.95</v>
       </c>
       <c r="G93" s="10">
-        <f>E93-F93</f>
+        <f t="shared" si="4"/>
         <v>68.050000000000011</v>
       </c>
       <c r="H93" s="14">
-        <f>(E93-F93)/F93</f>
+        <f t="shared" si="5"/>
         <v>0.14119721962859219</v>
       </c>
       <c r="I93" s="10" t="s">
@@ -38707,11 +38665,11 @@
         <v>1249.5</v>
       </c>
       <c r="G94" s="10">
-        <f>E94-F94</f>
+        <f t="shared" si="4"/>
         <v>100.5</v>
       </c>
       <c r="H94" s="14">
-        <f>(E94-F94)/F94</f>
+        <f t="shared" si="5"/>
         <v>8.0432172869147653E-2</v>
       </c>
       <c r="I94" s="10" t="s">
@@ -38739,11 +38697,11 @@
         <v>1249.5</v>
       </c>
       <c r="G95" s="10">
-        <f>E95-F95</f>
+        <f t="shared" si="4"/>
         <v>100.5</v>
       </c>
       <c r="H95" s="14">
-        <f>(E95-F95)/F95</f>
+        <f t="shared" si="5"/>
         <v>8.0432172869147653E-2</v>
       </c>
       <c r="I95" s="10" t="s">
@@ -38769,11 +38727,11 @@
         <v>501.2</v>
       </c>
       <c r="G96" s="10">
-        <f>E96-F96</f>
+        <f t="shared" si="4"/>
         <v>268.8</v>
       </c>
       <c r="H96" s="14">
-        <f>(E96-F96)/F96</f>
+        <f t="shared" si="5"/>
         <v>0.53631284916201116</v>
       </c>
       <c r="I96" s="10" t="s">
@@ -38799,11 +38757,11 @@
         <v>501.2</v>
       </c>
       <c r="G97" s="10">
-        <f>E97-F97</f>
+        <f t="shared" si="4"/>
         <v>268.8</v>
       </c>
       <c r="H97" s="14">
-        <f>(E97-F97)/F97</f>
+        <f t="shared" si="5"/>
         <v>0.53631284916201116</v>
       </c>
       <c r="I97" s="10" t="s">
@@ -38829,11 +38787,11 @@
         <v>143.19999999999999</v>
       </c>
       <c r="G98" s="10">
-        <f>E98-F98</f>
+        <f t="shared" ref="G98:G129" si="6">E98-F98</f>
         <v>206.8</v>
       </c>
       <c r="H98" s="14">
-        <f>(E98-F98)/F98</f>
+        <f t="shared" ref="H98:H129" si="7">(E98-F98)/F98</f>
         <v>1.4441340782122907</v>
       </c>
       <c r="I98" s="10" t="s">
@@ -38861,11 +38819,11 @@
         <v>2534.7199999999998</v>
       </c>
       <c r="G99" s="10">
-        <f>E99-F99</f>
+        <f t="shared" si="6"/>
         <v>385.2800000000002</v>
       </c>
       <c r="H99" s="14">
-        <f>(E99-F99)/F99</f>
+        <f t="shared" si="7"/>
         <v>0.15200100997348828</v>
       </c>
       <c r="I99" s="10" t="s">
@@ -38893,11 +38851,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G100" s="10">
-        <f>E100-F100</f>
+        <f t="shared" si="6"/>
         <v>465.30000000000018</v>
       </c>
       <c r="H100" s="14">
-        <f>(E100-F100)/F100</f>
+        <f t="shared" si="7"/>
         <v>0.18357202035743883</v>
       </c>
       <c r="I100" s="10" t="s">
@@ -38925,11 +38883,11 @@
         <v>2534.7199999999998</v>
       </c>
       <c r="G101" s="10">
-        <f>E101-F101</f>
+        <f t="shared" si="6"/>
         <v>465.2800000000002</v>
       </c>
       <c r="H101" s="14">
-        <f>(E101-F101)/F101</f>
+        <f t="shared" si="7"/>
         <v>0.18356268147961124</v>
       </c>
       <c r="I101" s="10" t="s">
@@ -38957,11 +38915,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G102" s="10">
-        <f>E102-F102</f>
+        <f t="shared" si="6"/>
         <v>385.30000000000018</v>
       </c>
       <c r="H102" s="14">
-        <f>(E102-F102)/F102</f>
+        <f t="shared" si="7"/>
         <v>0.15201009981457381</v>
       </c>
       <c r="I102" s="10" t="s">
@@ -38989,11 +38947,11 @@
         <v>2534.7199999999998</v>
       </c>
       <c r="G103" s="10">
-        <f>E103-F103</f>
+        <f t="shared" si="6"/>
         <v>465.2800000000002</v>
       </c>
       <c r="H103" s="14">
-        <f>(E103-F103)/F103</f>
+        <f t="shared" si="7"/>
         <v>0.18356268147961124</v>
       </c>
       <c r="I103" s="10" t="s">
@@ -39021,11 +38979,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G104" s="10">
-        <f>E104-F104</f>
+        <f t="shared" si="6"/>
         <v>465.30000000000018</v>
       </c>
       <c r="H104" s="14">
-        <f>(E104-F104)/F104</f>
+        <f t="shared" si="7"/>
         <v>0.18357202035743883</v>
       </c>
       <c r="I104" s="10" t="s">
@@ -39053,11 +39011,11 @@
         <v>2534.7199999999998</v>
       </c>
       <c r="G105" s="10">
-        <f>E105-F105</f>
+        <f t="shared" si="6"/>
         <v>385.2800000000002</v>
       </c>
       <c r="H105" s="14">
-        <f>(E105-F105)/F105</f>
+        <f t="shared" si="7"/>
         <v>0.15200100997348828</v>
       </c>
       <c r="I105" s="10" t="s">
@@ -39083,11 +39041,11 @@
         <v>1186.3499999999999</v>
       </c>
       <c r="G106" s="10">
-        <f>E106-F106</f>
+        <f t="shared" si="6"/>
         <v>563.65000000000009</v>
       </c>
       <c r="H106" s="14">
-        <f>(E106-F106)/F106</f>
+        <f t="shared" si="7"/>
         <v>0.47511274075947246</v>
       </c>
       <c r="I106" s="10" t="s">
@@ -39113,11 +39071,11 @@
         <v>1186.3499999999999</v>
       </c>
       <c r="G107" s="10">
-        <f>E107-F107</f>
+        <f t="shared" si="6"/>
         <v>563.65000000000009</v>
       </c>
       <c r="H107" s="14">
-        <f>(E107-F107)/F107</f>
+        <f t="shared" si="7"/>
         <v>0.47511274075947246</v>
       </c>
       <c r="I107" s="10" t="s">
@@ -39143,11 +39101,11 @@
         <v>1213.8</v>
       </c>
       <c r="G108" s="10">
-        <f>E108-F108</f>
+        <f t="shared" si="6"/>
         <v>636.20000000000005</v>
       </c>
       <c r="H108" s="14">
-        <f>(E108-F108)/F108</f>
+        <f t="shared" si="7"/>
         <v>0.52413906739166261</v>
       </c>
       <c r="I108" s="10" t="s">
@@ -39173,11 +39131,11 @@
         <v>1213.8</v>
       </c>
       <c r="G109" s="10">
-        <f>E109-F109</f>
+        <f t="shared" si="6"/>
         <v>486.20000000000005</v>
       </c>
       <c r="H109" s="14">
-        <f>(E109-F109)/F109</f>
+        <f t="shared" si="7"/>
         <v>0.40056022408963593</v>
       </c>
       <c r="I109" s="10" t="s">
@@ -39203,11 +39161,11 @@
         <v>1213.8</v>
       </c>
       <c r="G110" s="10">
-        <f>E110-F110</f>
+        <f t="shared" si="6"/>
         <v>666.2</v>
       </c>
       <c r="H110" s="14">
-        <f>(E110-F110)/F110</f>
+        <f t="shared" si="7"/>
         <v>0.54885483605206797</v>
       </c>
       <c r="I110" s="10" t="s">
@@ -39233,11 +39191,11 @@
         <v>1213.8</v>
       </c>
       <c r="G111" s="10">
-        <f>E111-F111</f>
+        <f t="shared" si="6"/>
         <v>666.2</v>
       </c>
       <c r="H111" s="14">
-        <f>(E111-F111)/F111</f>
+        <f t="shared" si="7"/>
         <v>0.54885483605206797</v>
       </c>
       <c r="I111" s="10" t="s">
@@ -39263,11 +39221,11 @@
         <v>1220.5999999999999</v>
       </c>
       <c r="G112" s="10">
-        <f>E112-F112</f>
+        <f t="shared" si="6"/>
         <v>629.40000000000009</v>
       </c>
       <c r="H112" s="14">
-        <f>(E112-F112)/F112</f>
+        <f t="shared" si="7"/>
         <v>0.51564804194658376</v>
       </c>
       <c r="I112" s="10" t="s">
@@ -39293,11 +39251,11 @@
         <v>1581.76</v>
       </c>
       <c r="G113" s="10">
-        <f>E113-F113</f>
+        <f t="shared" si="6"/>
         <v>348.24</v>
       </c>
       <c r="H113" s="14">
-        <f>(E113-F113)/F113</f>
+        <f t="shared" si="7"/>
         <v>0.2201598219704633</v>
       </c>
       <c r="I113" s="10" t="s">
@@ -39323,11 +39281,11 @@
         <v>1581.76</v>
       </c>
       <c r="G114" s="10">
-        <f>E114-F114</f>
+        <f t="shared" si="6"/>
         <v>348.24</v>
       </c>
       <c r="H114" s="14">
-        <f>(E114-F114)/F114</f>
+        <f t="shared" si="7"/>
         <v>0.2201598219704633</v>
       </c>
       <c r="I114" s="10" t="s">
@@ -39355,11 +39313,11 @@
         <v>135.66</v>
       </c>
       <c r="G115" s="17">
-        <f>E115-F115</f>
+        <f t="shared" si="6"/>
         <v>-5.6599999999999966</v>
       </c>
       <c r="H115" s="19">
-        <f>(E115-F115)/F115</f>
+        <f t="shared" si="7"/>
         <v>-4.1721951938670183E-2</v>
       </c>
       <c r="I115" s="17" t="s">
@@ -39389,11 +39347,11 @@
         <v>135.66</v>
       </c>
       <c r="G116" s="17">
-        <f>E116-F116</f>
+        <f t="shared" si="6"/>
         <v>-5.6599999999999966</v>
       </c>
       <c r="H116" s="19">
-        <f>(E116-F116)/F116</f>
+        <f t="shared" si="7"/>
         <v>-4.1721951938670183E-2</v>
       </c>
       <c r="I116" s="17" t="s">
@@ -39421,11 +39379,11 @@
         <v>1035.3</v>
       </c>
       <c r="G117" s="10">
-        <f>E117-F117</f>
+        <f t="shared" si="6"/>
         <v>164.70000000000005</v>
       </c>
       <c r="H117" s="14">
-        <f>(E117-F117)/F117</f>
+        <f t="shared" si="7"/>
         <v>0.15908432338452627</v>
       </c>
       <c r="I117" s="10" t="s">
@@ -39451,11 +39409,11 @@
         <v>1035.3</v>
       </c>
       <c r="G118" s="10">
-        <f>E118-F118</f>
+        <f t="shared" si="6"/>
         <v>214.70000000000005</v>
       </c>
       <c r="H118" s="14">
-        <f>(E118-F118)/F118</f>
+        <f t="shared" si="7"/>
         <v>0.20737950352554821</v>
       </c>
       <c r="I118" s="10" t="s">
@@ -39481,11 +39439,11 @@
         <v>1035.3</v>
       </c>
       <c r="G119" s="10">
-        <f>E119-F119</f>
+        <f t="shared" si="6"/>
         <v>314.70000000000005</v>
       </c>
       <c r="H119" s="14">
-        <f>(E119-F119)/F119</f>
+        <f t="shared" si="7"/>
         <v>0.30396986380759206</v>
       </c>
       <c r="I119" s="10" t="s">
@@ -39511,11 +39469,11 @@
         <v>1695.75</v>
       </c>
       <c r="G120" s="10">
-        <f>E120-F120</f>
+        <f t="shared" si="6"/>
         <v>304.25</v>
       </c>
       <c r="H120" s="14">
-        <f>(E120-F120)/F120</f>
+        <f t="shared" si="7"/>
         <v>0.17941913607548282</v>
       </c>
       <c r="I120" s="10" t="s">
@@ -39541,11 +39499,11 @@
         <v>1695.75</v>
       </c>
       <c r="G121" s="10">
-        <f>E121-F121</f>
+        <f t="shared" si="6"/>
         <v>204.25</v>
       </c>
       <c r="H121" s="14">
-        <f>(E121-F121)/F121</f>
+        <f t="shared" si="7"/>
         <v>0.12044817927170869</v>
       </c>
       <c r="I121" s="10" t="s">
@@ -39571,11 +39529,11 @@
         <v>1695.75</v>
       </c>
       <c r="G122" s="10">
-        <f>E122-F122</f>
+        <f t="shared" si="6"/>
         <v>204.25</v>
       </c>
       <c r="H122" s="14">
-        <f>(E122-F122)/F122</f>
+        <f t="shared" si="7"/>
         <v>0.12044817927170869</v>
       </c>
       <c r="I122" s="10" t="s">
@@ -39603,11 +39561,11 @@
         <v>3998.4</v>
       </c>
       <c r="G123" s="10">
-        <f>E123-F123</f>
+        <f t="shared" si="6"/>
         <v>251.59999999999991</v>
       </c>
       <c r="H123" s="14">
-        <f>(E123-F123)/F123</f>
+        <f t="shared" si="7"/>
         <v>6.2925170068027184E-2</v>
       </c>
       <c r="I123" s="10" t="s">
@@ -39635,11 +39593,11 @@
         <v>3998.4</v>
       </c>
       <c r="G124" s="10">
-        <f>E124-F124</f>
+        <f t="shared" si="6"/>
         <v>221.59999999999991</v>
       </c>
       <c r="H124" s="14">
-        <f>(E124-F124)/F124</f>
+        <f t="shared" si="7"/>
         <v>5.5422168867546993E-2</v>
       </c>
       <c r="I124" s="10" t="s">
@@ -39667,11 +39625,11 @@
         <v>1677.9</v>
       </c>
       <c r="G125" s="10">
-        <f>E125-F125</f>
+        <f t="shared" si="6"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H125" s="14">
-        <f>(E125-F125)/F125</f>
+        <f t="shared" si="7"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I125" s="10" t="s">
@@ -39699,11 +39657,11 @@
         <v>1677.9</v>
       </c>
       <c r="G126" s="10">
-        <f>E126-F126</f>
+        <f t="shared" si="6"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H126" s="14">
-        <f>(E126-F126)/F126</f>
+        <f t="shared" si="7"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I126" s="10" t="s">
@@ -39731,11 +39689,11 @@
         <v>1677.9</v>
       </c>
       <c r="G127" s="10">
-        <f>E127-F127</f>
+        <f t="shared" si="6"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H127" s="14">
-        <f>(E127-F127)/F127</f>
+        <f t="shared" si="7"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I127" s="10" t="s">
@@ -39763,11 +39721,11 @@
         <v>1677.9</v>
       </c>
       <c r="G128" s="10">
-        <f>E128-F128</f>
+        <f t="shared" si="6"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H128" s="14">
-        <f>(E128-F128)/F128</f>
+        <f t="shared" si="7"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I128" s="10" t="s">
@@ -39795,11 +39753,11 @@
         <v>1677.9</v>
       </c>
       <c r="G129" s="10">
-        <f>E129-F129</f>
+        <f t="shared" si="6"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H129" s="14">
-        <f>(E129-F129)/F129</f>
+        <f t="shared" si="7"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I129" s="10" t="s">
@@ -39827,11 +39785,11 @@
         <v>1677.9</v>
       </c>
       <c r="G130" s="10">
-        <f>E130-F130</f>
+        <f t="shared" ref="G130:G161" si="8">E130-F130</f>
         <v>152.09999999999991</v>
       </c>
       <c r="H130" s="14">
-        <f>(E130-F130)/F130</f>
+        <f t="shared" ref="H130:H159" si="9">(E130-F130)/F130</f>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I130" s="10" t="s">
@@ -39859,11 +39817,11 @@
         <v>1677.9</v>
       </c>
       <c r="G131" s="10">
-        <f>E131-F131</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H131" s="14">
-        <f>(E131-F131)/F131</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I131" s="10" t="s">
@@ -39891,11 +39849,11 @@
         <v>1677.9</v>
       </c>
       <c r="G132" s="10">
-        <f>E132-F132</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H132" s="14">
-        <f>(E132-F132)/F132</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I132" s="10" t="s">
@@ -39923,11 +39881,11 @@
         <v>1677.9</v>
       </c>
       <c r="G133" s="10">
-        <f>E133-F133</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H133" s="14">
-        <f>(E133-F133)/F133</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I133" s="10" t="s">
@@ -39955,11 +39913,11 @@
         <v>1677.9</v>
       </c>
       <c r="G134" s="10">
-        <f>E134-F134</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H134" s="14">
-        <f>(E134-F134)/F134</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I134" s="10" t="s">
@@ -39987,11 +39945,11 @@
         <v>1677.9</v>
       </c>
       <c r="G135" s="10">
-        <f>E135-F135</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H135" s="14">
-        <f>(E135-F135)/F135</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I135" s="10" t="s">
@@ -40019,11 +39977,11 @@
         <v>1677.9</v>
       </c>
       <c r="G136" s="10">
-        <f>E136-F136</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H136" s="14">
-        <f>(E136-F136)/F136</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I136" s="10" t="s">
@@ -40051,11 +40009,11 @@
         <v>1677.9</v>
       </c>
       <c r="G137" s="10">
-        <f>E137-F137</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H137" s="14">
-        <f>(E137-F137)/F137</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I137" s="10" t="s">
@@ -40083,11 +40041,11 @@
         <v>1677.9</v>
       </c>
       <c r="G138" s="10">
-        <f>E138-F138</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H138" s="14">
-        <f>(E138-F138)/F138</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I138" s="10" t="s">
@@ -40115,11 +40073,11 @@
         <v>1677.9</v>
       </c>
       <c r="G139" s="10">
-        <f>E139-F139</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H139" s="14">
-        <f>(E139-F139)/F139</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I139" s="10" t="s">
@@ -40147,11 +40105,11 @@
         <v>1677.9</v>
       </c>
       <c r="G140" s="10">
-        <f>E140-F140</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H140" s="14">
-        <f>(E140-F140)/F140</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I140" s="10" t="s">
@@ -40179,11 +40137,11 @@
         <v>1677.9</v>
       </c>
       <c r="G141" s="10">
-        <f>E141-F141</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H141" s="14">
-        <f>(E141-F141)/F141</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I141" s="10" t="s">
@@ -40211,11 +40169,11 @@
         <v>1677.9</v>
       </c>
       <c r="G142" s="10">
-        <f>E142-F142</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H142" s="14">
-        <f>(E142-F142)/F142</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I142" s="10" t="s">
@@ -40243,11 +40201,11 @@
         <v>1677.9</v>
       </c>
       <c r="G143" s="10">
-        <f>E143-F143</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H143" s="14">
-        <f>(E143-F143)/F143</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I143" s="10" t="s">
@@ -40275,11 +40233,11 @@
         <v>1677.9</v>
       </c>
       <c r="G144" s="10">
-        <f>E144-F144</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H144" s="14">
-        <f>(E144-F144)/F144</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I144" s="10" t="s">
@@ -40307,11 +40265,11 @@
         <v>1677.9</v>
       </c>
       <c r="G145" s="10">
-        <f>E145-F145</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H145" s="14">
-        <f>(E145-F145)/F145</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I145" s="10" t="s">
@@ -40339,11 +40297,11 @@
         <v>1677.9</v>
       </c>
       <c r="G146" s="10">
-        <f>E146-F146</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H146" s="14">
-        <f>(E146-F146)/F146</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I146" s="10" t="s">
@@ -40371,11 +40329,11 @@
         <v>1677.9</v>
       </c>
       <c r="G147" s="10">
-        <f>E147-F147</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H147" s="14">
-        <f>(E147-F147)/F147</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I147" s="10" t="s">
@@ -40403,11 +40361,11 @@
         <v>1677.9</v>
       </c>
       <c r="G148" s="10">
-        <f>E148-F148</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H148" s="14">
-        <f>(E148-F148)/F148</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I148" s="10" t="s">
@@ -40435,11 +40393,11 @@
         <v>1677.9</v>
       </c>
       <c r="G149" s="10">
-        <f>E149-F149</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H149" s="14">
-        <f>(E149-F149)/F149</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I149" s="10" t="s">
@@ -40467,11 +40425,11 @@
         <v>1677.9</v>
       </c>
       <c r="G150" s="10">
-        <f>E150-F150</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H150" s="14">
-        <f>(E150-F150)/F150</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I150" s="10" t="s">
@@ -40499,11 +40457,11 @@
         <v>1677.9</v>
       </c>
       <c r="G151" s="10">
-        <f>E151-F151</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H151" s="14">
-        <f>(E151-F151)/F151</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I151" s="10" t="s">
@@ -40531,11 +40489,11 @@
         <v>1677.9</v>
       </c>
       <c r="G152" s="10">
-        <f>E152-F152</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H152" s="14">
-        <f>(E152-F152)/F152</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I152" s="10" t="s">
@@ -40563,11 +40521,11 @@
         <v>1677.9</v>
       </c>
       <c r="G153" s="10">
-        <f>E153-F153</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H153" s="14">
-        <f>(E153-F153)/F153</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I153" s="10" t="s">
@@ -40595,11 +40553,11 @@
         <v>1677.9</v>
       </c>
       <c r="G154" s="10">
-        <f>E154-F154</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H154" s="14">
-        <f>(E154-F154)/F154</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I154" s="10" t="s">
@@ -40627,11 +40585,11 @@
         <v>1677.9</v>
       </c>
       <c r="G155" s="10">
-        <f>E155-F155</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H155" s="14">
-        <f>(E155-F155)/F155</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I155" s="10" t="s">
@@ -40659,11 +40617,11 @@
         <v>1677.9</v>
       </c>
       <c r="G156" s="10">
-        <f>E156-F156</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H156" s="14">
-        <f>(E156-F156)/F156</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I156" s="10" t="s">
@@ -40691,11 +40649,11 @@
         <v>1677.9</v>
       </c>
       <c r="G157" s="10">
-        <f>E157-F157</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H157" s="14">
-        <f>(E157-F157)/F157</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I157" s="10" t="s">
@@ -40723,11 +40681,11 @@
         <v>1677.9</v>
       </c>
       <c r="G158" s="10">
-        <f>E158-F158</f>
+        <f t="shared" si="8"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H158" s="14">
-        <f>(E158-F158)/F158</f>
+        <f t="shared" si="9"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I158" s="10" t="s">
@@ -40755,11 +40713,11 @@
         <v>1677.9</v>
       </c>
       <c r="G159" s="10">
-        <f>E159-F159</f>
+        <f t="shared" si="8"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H159" s="14">
-        <f>(E159-F159)/F159</f>
+        <f t="shared" si="9"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I159" s="10" t="s">
@@ -40787,11 +40745,11 @@
         <v>1677.9</v>
       </c>
       <c r="G160" s="10">
-        <f t="shared" ref="G160:G223" si="0">E160-F160</f>
+        <f t="shared" ref="G160:G223" si="10">E160-F160</f>
         <v>147.09999999999991</v>
       </c>
       <c r="H160" s="14">
-        <f t="shared" ref="H160:H223" si="1">(E160-F160)/F160</f>
+        <f t="shared" ref="H160:H223" si="11">(E160-F160)/F160</f>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I160" s="10" t="s">
@@ -40819,11 +40777,11 @@
         <v>1677.9</v>
       </c>
       <c r="G161" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H161" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I161" s="10" t="s">
@@ -40851,11 +40809,11 @@
         <v>1677.9</v>
       </c>
       <c r="G162" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H162" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I162" s="10" t="s">
@@ -40883,11 +40841,11 @@
         <v>1677.9</v>
       </c>
       <c r="G163" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H163" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I163" s="10" t="s">
@@ -40915,11 +40873,11 @@
         <v>1677.9</v>
       </c>
       <c r="G164" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H164" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I164" s="10" t="s">
@@ -40947,11 +40905,11 @@
         <v>1677.9</v>
       </c>
       <c r="G165" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H165" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I165" s="10" t="s">
@@ -40979,11 +40937,11 @@
         <v>1677.9</v>
       </c>
       <c r="G166" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H166" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I166" s="10" t="s">
@@ -41011,11 +40969,11 @@
         <v>1677.9</v>
       </c>
       <c r="G167" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H167" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I167" s="10" t="s">
@@ -41043,11 +41001,11 @@
         <v>1677.9</v>
       </c>
       <c r="G168" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H168" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I168" s="10" t="s">
@@ -41075,11 +41033,11 @@
         <v>1677.9</v>
       </c>
       <c r="G169" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H169" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I169" s="10" t="s">
@@ -41107,11 +41065,11 @@
         <v>1677.9</v>
       </c>
       <c r="G170" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H170" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I170" s="10" t="s">
@@ -41139,11 +41097,11 @@
         <v>1677.9</v>
       </c>
       <c r="G171" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H171" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I171" s="10" t="s">
@@ -41171,11 +41129,11 @@
         <v>1677.9</v>
       </c>
       <c r="G172" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H172" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I172" s="10" t="s">
@@ -41203,11 +41161,11 @@
         <v>1677.9</v>
       </c>
       <c r="G173" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H173" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I173" s="10" t="s">
@@ -41235,11 +41193,11 @@
         <v>1677.9</v>
       </c>
       <c r="G174" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H174" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I174" s="10" t="s">
@@ -41267,11 +41225,11 @@
         <v>1677.9</v>
       </c>
       <c r="G175" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H175" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I175" s="10" t="s">
@@ -41299,11 +41257,11 @@
         <v>1677.9</v>
       </c>
       <c r="G176" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H176" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I176" s="10" t="s">
@@ -41331,11 +41289,11 @@
         <v>1677.9</v>
       </c>
       <c r="G177" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H177" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I177" s="10" t="s">
@@ -41363,11 +41321,11 @@
         <v>1677.9</v>
       </c>
       <c r="G178" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H178" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I178" s="10" t="s">
@@ -41395,11 +41353,11 @@
         <v>1677.9</v>
       </c>
       <c r="G179" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H179" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I179" s="10" t="s">
@@ -41427,11 +41385,11 @@
         <v>1677.9</v>
       </c>
       <c r="G180" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H180" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I180" s="10" t="s">
@@ -41459,11 +41417,11 @@
         <v>1677.9</v>
       </c>
       <c r="G181" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H181" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I181" s="10" t="s">
@@ -41491,11 +41449,11 @@
         <v>1677.9</v>
       </c>
       <c r="G182" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H182" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I182" s="10" t="s">
@@ -41523,11 +41481,11 @@
         <v>1677.9</v>
       </c>
       <c r="G183" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H183" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I183" s="10" t="s">
@@ -41555,11 +41513,11 @@
         <v>1677.9</v>
       </c>
       <c r="G184" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H184" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I184" s="10" t="s">
@@ -41587,11 +41545,11 @@
         <v>1677.9</v>
       </c>
       <c r="G185" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H185" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I185" s="10" t="s">
@@ -41619,11 +41577,11 @@
         <v>1677.9</v>
       </c>
       <c r="G186" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H186" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I186" s="10" t="s">
@@ -41651,11 +41609,11 @@
         <v>1677.9</v>
       </c>
       <c r="G187" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H187" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I187" s="10" t="s">
@@ -41683,11 +41641,11 @@
         <v>1677.9</v>
       </c>
       <c r="G188" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H188" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I188" s="10" t="s">
@@ -41715,11 +41673,11 @@
         <v>1677.9</v>
       </c>
       <c r="G189" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H189" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I189" s="10" t="s">
@@ -41747,11 +41705,11 @@
         <v>1677.9</v>
       </c>
       <c r="G190" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H190" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I190" s="10" t="s">
@@ -41779,11 +41737,11 @@
         <v>1677.9</v>
       </c>
       <c r="G191" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H191" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I191" s="10" t="s">
@@ -41811,11 +41769,11 @@
         <v>1677.9</v>
       </c>
       <c r="G192" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H192" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I192" s="10" t="s">
@@ -41843,11 +41801,11 @@
         <v>1677.9</v>
       </c>
       <c r="G193" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H193" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I193" s="10" t="s">
@@ -41875,11 +41833,11 @@
         <v>1677.9</v>
       </c>
       <c r="G194" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H194" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I194" s="10" t="s">
@@ -41907,11 +41865,11 @@
         <v>1677.9</v>
       </c>
       <c r="G195" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H195" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I195" s="10" t="s">
@@ -41939,11 +41897,11 @@
         <v>1677.9</v>
       </c>
       <c r="G196" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H196" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I196" s="10" t="s">
@@ -41971,11 +41929,11 @@
         <v>1677.9</v>
       </c>
       <c r="G197" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H197" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I197" s="10" t="s">
@@ -42003,11 +41961,11 @@
         <v>1677.9</v>
       </c>
       <c r="G198" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H198" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I198" s="10" t="s">
@@ -42035,11 +41993,11 @@
         <v>1677.9</v>
       </c>
       <c r="G199" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H199" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I199" s="10" t="s">
@@ -42067,11 +42025,11 @@
         <v>1677.9</v>
       </c>
       <c r="G200" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H200" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I200" s="10" t="s">
@@ -42099,11 +42057,11 @@
         <v>1677.9</v>
       </c>
       <c r="G201" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H201" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I201" s="10" t="s">
@@ -42131,11 +42089,11 @@
         <v>1677.9</v>
       </c>
       <c r="G202" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H202" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I202" s="10" t="s">
@@ -42163,11 +42121,11 @@
         <v>1677.9</v>
       </c>
       <c r="G203" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H203" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I203" s="10" t="s">
@@ -42195,11 +42153,11 @@
         <v>1677.9</v>
       </c>
       <c r="G204" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H204" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I204" s="10" t="s">
@@ -42227,11 +42185,11 @@
         <v>1677.9</v>
       </c>
       <c r="G205" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H205" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I205" s="10" t="s">
@@ -42259,11 +42217,11 @@
         <v>1677.9</v>
       </c>
       <c r="G206" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H206" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I206" s="10" t="s">
@@ -42291,11 +42249,11 @@
         <v>1677.9</v>
       </c>
       <c r="G207" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H207" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I207" s="10" t="s">
@@ -42323,11 +42281,11 @@
         <v>1677.9</v>
       </c>
       <c r="G208" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H208" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I208" s="10" t="s">
@@ -42355,11 +42313,11 @@
         <v>1677.9</v>
       </c>
       <c r="G209" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H209" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I209" s="10" t="s">
@@ -42387,11 +42345,11 @@
         <v>1677.9</v>
       </c>
       <c r="G210" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H210" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I210" s="10" t="s">
@@ -42419,11 +42377,11 @@
         <v>1677.9</v>
       </c>
       <c r="G211" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>147.09999999999991</v>
       </c>
       <c r="H211" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>8.7669110197270333E-2</v>
       </c>
       <c r="I211" s="10" t="s">
@@ -42451,11 +42409,11 @@
         <v>1677.9</v>
       </c>
       <c r="G212" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>152.09999999999991</v>
       </c>
       <c r="H212" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>9.0649025567673819E-2</v>
       </c>
       <c r="I212" s="10" t="s">
@@ -42483,11 +42441,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G213" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H213" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I213" s="10" t="s">
@@ -42515,11 +42473,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G214" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H214" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I214" s="10" t="s">
@@ -42547,11 +42505,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G215" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H215" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I215" s="10" t="s">
@@ -42579,11 +42537,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G216" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H216" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I216" s="10" t="s">
@@ -42611,11 +42569,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G217" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H217" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I217" s="10" t="s">
@@ -42643,11 +42601,11 @@
         <v>12495</v>
       </c>
       <c r="G218" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>1455</v>
       </c>
       <c r="H218" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.11644657863145258</v>
       </c>
       <c r="I218" s="10" t="s">
@@ -42675,11 +42633,11 @@
         <v>1106.7</v>
       </c>
       <c r="G219" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>413.29999999999995</v>
       </c>
       <c r="H219" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.37345260684919124</v>
       </c>
       <c r="I219" s="10" t="s">
@@ -42707,11 +42665,11 @@
         <v>1106.7</v>
       </c>
       <c r="G220" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>413.29999999999995</v>
       </c>
       <c r="H220" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.37345260684919124</v>
       </c>
       <c r="I220" s="10" t="s">
@@ -42739,11 +42697,11 @@
         <v>1106.7</v>
       </c>
       <c r="G221" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>203.29999999999995</v>
       </c>
       <c r="H221" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.18369928616607928</v>
       </c>
       <c r="I221" s="10" t="s">
@@ -42771,11 +42729,11 @@
         <v>1106.7</v>
       </c>
       <c r="G222" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>203.29999999999995</v>
       </c>
       <c r="H222" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.18369928616607928</v>
       </c>
       <c r="I222" s="10" t="s">
@@ -42803,11 +42761,11 @@
         <v>1106.7</v>
       </c>
       <c r="G223" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="10"/>
         <v>413.29999999999995</v>
       </c>
       <c r="H223" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>0.37345260684919124</v>
       </c>
       <c r="I223" s="10" t="s">
@@ -42835,11 +42793,11 @@
         <v>1106.7</v>
       </c>
       <c r="G224" s="10">
-        <f>E224-F224</f>
+        <f t="shared" ref="G224:G260" si="12">E224-F224</f>
         <v>413.29999999999995</v>
       </c>
       <c r="H224" s="14">
-        <f>(E224-F224)/F224</f>
+        <f t="shared" ref="H224:H260" si="13">(E224-F224)/F224</f>
         <v>0.37345260684919124</v>
       </c>
       <c r="I224" s="10" t="s">
@@ -42867,11 +42825,11 @@
         <v>1106.7</v>
       </c>
       <c r="G225" s="10">
-        <f>E225-F225</f>
+        <f t="shared" si="12"/>
         <v>413.29999999999995</v>
       </c>
       <c r="H225" s="14">
-        <f>(E225-F225)/F225</f>
+        <f t="shared" si="13"/>
         <v>0.37345260684919124</v>
       </c>
       <c r="I225" s="10" t="s">
@@ -42899,11 +42857,11 @@
         <v>1106.7</v>
       </c>
       <c r="G226" s="10">
-        <f>E226-F226</f>
+        <f t="shared" si="12"/>
         <v>203.29999999999995</v>
       </c>
       <c r="H226" s="14">
-        <f>(E226-F226)/F226</f>
+        <f t="shared" si="13"/>
         <v>0.18369928616607928</v>
       </c>
       <c r="I226" s="10" t="s">
@@ -42929,11 +42887,11 @@
         <v>4738.8</v>
       </c>
       <c r="G227" s="17">
-        <f>E227-F227</f>
+        <f t="shared" si="12"/>
         <v>-138.80000000000018</v>
       </c>
       <c r="H227" s="19">
-        <f>(E227-F227)/F227</f>
+        <f t="shared" si="13"/>
         <v>-2.929011564109061E-2</v>
       </c>
       <c r="I227" s="17" t="s">
@@ -42961,11 +42919,11 @@
         <v>4498.2</v>
       </c>
       <c r="G228" s="10">
-        <f>E228-F228</f>
+        <f t="shared" si="12"/>
         <v>101.80000000000018</v>
       </c>
       <c r="H228" s="14">
-        <f>(E228-F228)/F228</f>
+        <f t="shared" si="13"/>
         <v>2.2631274732115108E-2</v>
       </c>
       <c r="I228" s="10" t="s">
@@ -42991,11 +42949,11 @@
         <v>4045.4</v>
       </c>
       <c r="G229" s="10">
-        <f>E229-F229</f>
+        <f t="shared" si="12"/>
         <v>554.59999999999991</v>
       </c>
       <c r="H229" s="14">
-        <f>(E229-F229)/F229</f>
+        <f t="shared" si="13"/>
         <v>0.1370939832896623</v>
       </c>
       <c r="I229" s="10" t="s">
@@ -43021,11 +42979,11 @@
         <v>4738.8</v>
       </c>
       <c r="G230" s="17">
-        <f>E230-F230</f>
+        <f t="shared" si="12"/>
         <v>-338.80000000000018</v>
       </c>
       <c r="H230" s="19">
-        <f>(E230-F230)/F230</f>
+        <f t="shared" si="13"/>
         <v>-7.1494893221912756E-2</v>
       </c>
       <c r="I230" s="17" t="s">
@@ -43055,11 +43013,11 @@
         <v>3284.4</v>
       </c>
       <c r="G231" s="10">
-        <f>E231-F231</f>
+        <f t="shared" si="12"/>
         <v>815.59999999999991</v>
       </c>
       <c r="H231" s="14">
-        <f>(E231-F231)/F231</f>
+        <f t="shared" si="13"/>
         <v>0.24832541712337106</v>
       </c>
       <c r="I231" s="10" t="s">
@@ -43087,11 +43045,11 @@
         <v>2320.5</v>
       </c>
       <c r="G232" s="17">
-        <f>E232-F232</f>
+        <f t="shared" si="12"/>
         <v>-90.5</v>
       </c>
       <c r="H232" s="19">
-        <f>(E232-F232)/F232</f>
+        <f t="shared" si="13"/>
         <v>-3.9000215470803706E-2</v>
       </c>
       <c r="I232" s="17" t="s">
@@ -43121,11 +43079,11 @@
         <v>2320.5</v>
       </c>
       <c r="G233" s="17">
-        <f>E233-F233</f>
+        <f t="shared" si="12"/>
         <v>-90.5</v>
       </c>
       <c r="H233" s="19">
-        <f>(E233-F233)/F233</f>
+        <f t="shared" si="13"/>
         <v>-3.9000215470803706E-2</v>
       </c>
       <c r="I233" s="17" t="s">
@@ -43155,11 +43113,11 @@
         <v>6604.5</v>
       </c>
       <c r="G234" s="10">
-        <f>E234-F234</f>
+        <f t="shared" si="12"/>
         <v>645.5</v>
       </c>
       <c r="H234" s="14">
-        <f>(E234-F234)/F234</f>
+        <f t="shared" si="13"/>
         <v>9.7736391854038915E-2</v>
       </c>
       <c r="I234" s="10" t="s">
@@ -43187,11 +43145,11 @@
         <v>6604.5</v>
       </c>
       <c r="G235" s="10">
-        <f>E235-F235</f>
+        <f t="shared" si="12"/>
         <v>645.5</v>
       </c>
       <c r="H235" s="14">
-        <f>(E235-F235)/F235</f>
+        <f t="shared" si="13"/>
         <v>9.7736391854038915E-2</v>
       </c>
       <c r="I235" s="10" t="s">
@@ -43219,11 +43177,11 @@
         <v>6247.5</v>
       </c>
       <c r="G236" s="10">
-        <f>E236-F236</f>
+        <f t="shared" si="12"/>
         <v>552.5</v>
       </c>
       <c r="H236" s="14">
-        <f>(E236-F236)/F236</f>
+        <f t="shared" si="13"/>
         <v>8.8435374149659865E-2</v>
       </c>
       <c r="I236" s="10" t="s">
@@ -43251,11 +43209,11 @@
         <v>12495</v>
       </c>
       <c r="G237" s="10">
-        <f>E237-F237</f>
+        <f t="shared" si="12"/>
         <v>1505</v>
       </c>
       <c r="H237" s="14">
-        <f>(E237-F237)/F237</f>
+        <f t="shared" si="13"/>
         <v>0.12044817927170869</v>
       </c>
       <c r="I237" s="10" t="s">
@@ -43283,11 +43241,11 @@
         <v>3927</v>
       </c>
       <c r="G238" s="10">
-        <f>E238-F238</f>
+        <f t="shared" si="12"/>
         <v>73</v>
       </c>
       <c r="H238" s="14">
-        <f>(E238-F238)/F238</f>
+        <f t="shared" si="13"/>
         <v>1.8589253883371529E-2</v>
       </c>
       <c r="I238" s="10" t="s">
@@ -43315,11 +43273,11 @@
         <v>3927</v>
       </c>
       <c r="G239" s="17">
-        <f>E239-F239</f>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="H239" s="19">
-        <f>(E239-F239)/F239</f>
+        <f t="shared" si="13"/>
         <v>-1.7825311942959001E-3</v>
       </c>
       <c r="I239" s="17" t="s">
@@ -43349,11 +43307,11 @@
         <v>3927</v>
       </c>
       <c r="G240" s="17">
-        <f>E240-F240</f>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="H240" s="19">
-        <f>(E240-F240)/F240</f>
+        <f t="shared" si="13"/>
         <v>-1.7825311942959001E-3</v>
       </c>
       <c r="I240" s="17" t="s">
@@ -43383,11 +43341,11 @@
         <v>3927</v>
       </c>
       <c r="G241" s="17">
-        <f>E241-F241</f>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="H241" s="19">
-        <f>(E241-F241)/F241</f>
+        <f t="shared" si="13"/>
         <v>-1.7825311942959001E-3</v>
       </c>
       <c r="I241" s="17" t="s">
@@ -43417,11 +43375,11 @@
         <v>3927</v>
       </c>
       <c r="G242" s="17">
-        <f>E242-F242</f>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="H242" s="19">
-        <f>(E242-F242)/F242</f>
+        <f t="shared" si="13"/>
         <v>-1.7825311942959001E-3</v>
       </c>
       <c r="I242" s="17" t="s">
@@ -43451,11 +43409,11 @@
         <v>3927</v>
       </c>
       <c r="G243" s="10">
-        <f>E243-F243</f>
+        <f t="shared" si="12"/>
         <v>73</v>
       </c>
       <c r="H243" s="14">
-        <f>(E243-F243)/F243</f>
+        <f t="shared" si="13"/>
         <v>1.8589253883371529E-2</v>
       </c>
       <c r="I243" s="10" t="s">
@@ -43483,11 +43441,11 @@
         <v>3927</v>
       </c>
       <c r="G244" s="17">
-        <f>E244-F244</f>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="H244" s="19">
-        <f>(E244-F244)/F244</f>
+        <f t="shared" si="13"/>
         <v>-1.7825311942959001E-3</v>
       </c>
       <c r="I244" s="17" t="s">
@@ -43517,11 +43475,11 @@
         <v>3927</v>
       </c>
       <c r="G245" s="10">
-        <f>E245-F245</f>
+        <f t="shared" si="12"/>
         <v>73</v>
       </c>
       <c r="H245" s="14">
-        <f>(E245-F245)/F245</f>
+        <f t="shared" si="13"/>
         <v>1.8589253883371529E-2</v>
       </c>
       <c r="I245" s="10" t="s">
@@ -43549,11 +43507,11 @@
         <v>1017.45</v>
       </c>
       <c r="G246" s="10">
-        <f>E246-F246</f>
+        <f t="shared" si="12"/>
         <v>102.54999999999995</v>
       </c>
       <c r="H246" s="14">
-        <f>(E246-F246)/F246</f>
+        <f t="shared" si="13"/>
         <v>0.10079119367045059</v>
       </c>
       <c r="I246" s="10" t="s">
@@ -43581,11 +43539,11 @@
         <v>1071</v>
       </c>
       <c r="G247" s="10">
-        <f>E247-F247</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H247" s="14">
-        <f>(E247-F247)/F247</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I247" s="10" t="s">
@@ -43613,11 +43571,11 @@
         <v>1071</v>
       </c>
       <c r="G248" s="10">
-        <f>E248-F248</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H248" s="14">
-        <f>(E248-F248)/F248</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I248" s="10" t="s">
@@ -43645,11 +43603,11 @@
         <v>1071</v>
       </c>
       <c r="G249" s="10">
-        <f>E249-F249</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H249" s="14">
-        <f>(E249-F249)/F249</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I249" s="10" t="s">
@@ -43677,11 +43635,11 @@
         <v>1071</v>
       </c>
       <c r="G250" s="10">
-        <f>E250-F250</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H250" s="14">
-        <f>(E250-F250)/F250</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I250" s="10" t="s">
@@ -43709,11 +43667,11 @@
         <v>1071</v>
       </c>
       <c r="G251" s="10">
-        <f>E251-F251</f>
+        <f t="shared" si="12"/>
         <v>369</v>
       </c>
       <c r="H251" s="14">
-        <f>(E251-F251)/F251</f>
+        <f t="shared" si="13"/>
         <v>0.34453781512605042</v>
       </c>
       <c r="I251" s="10" t="s">
@@ -43741,11 +43699,11 @@
         <v>1071</v>
       </c>
       <c r="G252" s="10">
-        <f>E252-F252</f>
+        <f t="shared" si="12"/>
         <v>369</v>
       </c>
       <c r="H252" s="14">
-        <f>(E252-F252)/F252</f>
+        <f t="shared" si="13"/>
         <v>0.34453781512605042</v>
       </c>
       <c r="I252" s="10" t="s">
@@ -43773,11 +43731,11 @@
         <v>1071</v>
       </c>
       <c r="G253" s="10">
-        <f>E253-F253</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H253" s="14">
-        <f>(E253-F253)/F253</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I253" s="10" t="s">
@@ -43805,11 +43763,11 @@
         <v>1071</v>
       </c>
       <c r="G254" s="10">
-        <f>E254-F254</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H254" s="14">
-        <f>(E254-F254)/F254</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I254" s="10" t="s">
@@ -43837,11 +43795,11 @@
         <v>1071</v>
       </c>
       <c r="G255" s="10">
-        <f>E255-F255</f>
+        <f t="shared" si="12"/>
         <v>174</v>
       </c>
       <c r="H255" s="14">
-        <f>(E255-F255)/F255</f>
+        <f t="shared" si="13"/>
         <v>0.16246498599439776</v>
       </c>
       <c r="I255" s="10" t="s">
@@ -43869,11 +43827,11 @@
         <v>1071</v>
       </c>
       <c r="G256" s="10">
-        <f>E256-F256</f>
+        <f t="shared" si="12"/>
         <v>369</v>
       </c>
       <c r="H256" s="14">
-        <f>(E256-F256)/F256</f>
+        <f t="shared" si="13"/>
         <v>0.34453781512605042</v>
       </c>
       <c r="I256" s="10" t="s">
@@ -43901,11 +43859,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G257" s="10">
-        <f>E257-F257</f>
+        <f t="shared" si="12"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H257" s="14">
-        <f>(E257-F257)/F257</f>
+        <f t="shared" si="13"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I257" s="10" t="s">
@@ -43933,11 +43891,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G258" s="10">
-        <f>E258-F258</f>
+        <f t="shared" si="12"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H258" s="14">
-        <f>(E258-F258)/F258</f>
+        <f t="shared" si="13"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I258" s="10" t="s">
@@ -43965,11 +43923,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G259" s="10">
-        <f>E259-F259</f>
+        <f t="shared" si="12"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H259" s="14">
-        <f>(E259-F259)/F259</f>
+        <f t="shared" si="13"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I259" s="10" t="s">
@@ -43997,11 +43955,11 @@
         <v>2534.6999999999998</v>
       </c>
       <c r="G260" s="10">
-        <f>E260-F260</f>
+        <f t="shared" si="12"/>
         <v>445.30000000000018</v>
       </c>
       <c r="H260" s="14">
-        <f>(E260-F260)/F260</f>
+        <f t="shared" si="13"/>
         <v>0.17568154022172258</v>
       </c>
       <c r="I260" s="10" t="s">
@@ -44270,11 +44228,11 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J260">
     <sortCondition ref="I2:I260"/>
   </sortState>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C260">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44403,11 +44361,11 @@
         <v>2750</v>
       </c>
       <c r="G4" s="10">
-        <f>E4-F4</f>
+        <f t="shared" ref="G4:G45" si="0">E4-F4</f>
         <v>313.28999999999996</v>
       </c>
       <c r="H4" s="14">
-        <f>(E4-F4)/F4</f>
+        <f t="shared" ref="H4:H45" si="1">(E4-F4)/F4</f>
         <v>0.11392363636363635</v>
       </c>
       <c r="I4" s="10" t="s">
@@ -44435,11 +44393,11 @@
         <v>3050</v>
       </c>
       <c r="G5" s="10">
-        <f>E5-F5</f>
+        <f t="shared" si="0"/>
         <v>317.07999999999993</v>
       </c>
       <c r="H5" s="14">
-        <f>(E5-F5)/F5</f>
+        <f t="shared" si="1"/>
         <v>0.1039606557377049</v>
       </c>
       <c r="I5" s="10" t="s">
@@ -44467,11 +44425,11 @@
         <v>2600</v>
       </c>
       <c r="G6" s="10">
-        <f>E6-F6</f>
+        <f t="shared" si="0"/>
         <v>387.34000000000015</v>
       </c>
       <c r="H6" s="14">
-        <f>(E6-F6)/F6</f>
+        <f t="shared" si="1"/>
         <v>0.14897692307692315</v>
       </c>
       <c r="I6" s="10" t="s">
@@ -44499,11 +44457,11 @@
         <v>3000</v>
       </c>
       <c r="G7" s="10">
-        <f>E7-F7</f>
+        <f t="shared" si="0"/>
         <v>455.69000000000005</v>
       </c>
       <c r="H7" s="14">
-        <f>(E7-F7)/F7</f>
+        <f t="shared" si="1"/>
         <v>0.15189666666666668</v>
       </c>
       <c r="I7" s="10" t="s">
@@ -44531,11 +44489,11 @@
         <v>3200</v>
       </c>
       <c r="G8" s="10">
-        <f>E8-F8</f>
+        <f t="shared" si="0"/>
         <v>534.17000000000007</v>
       </c>
       <c r="H8" s="14">
-        <f>(E8-F8)/F8</f>
+        <f t="shared" si="1"/>
         <v>0.16692812500000001</v>
       </c>
       <c r="I8" s="10" t="s">
@@ -44563,11 +44521,11 @@
         <v>2600</v>
       </c>
       <c r="G9" s="10">
-        <f>E9-F9</f>
+        <f t="shared" si="0"/>
         <v>425.30999999999995</v>
       </c>
       <c r="H9" s="14">
-        <f>(E9-F9)/F9</f>
+        <f t="shared" si="1"/>
         <v>0.1635807692307692</v>
       </c>
       <c r="I9" s="10" t="s">
@@ -44595,11 +44553,11 @@
         <v>2600</v>
       </c>
       <c r="G10" s="10">
-        <f>E10-F10</f>
+        <f t="shared" si="0"/>
         <v>412.65000000000009</v>
       </c>
       <c r="H10" s="14">
-        <f>(E10-F10)/F10</f>
+        <f t="shared" si="1"/>
         <v>0.15871153846153849</v>
       </c>
       <c r="I10" s="10" t="s">
@@ -44625,11 +44583,11 @@
         <v>2050</v>
       </c>
       <c r="G11" s="17">
-        <f>E11-F11</f>
+        <f t="shared" si="0"/>
         <v>-252.53999999999996</v>
       </c>
       <c r="H11" s="19">
-        <f>(E11-F11)/F11</f>
+        <f t="shared" si="1"/>
         <v>-0.123190243902439</v>
       </c>
       <c r="I11" s="17" t="s">
@@ -44659,11 +44617,11 @@
         <v>2000</v>
       </c>
       <c r="G12" s="17">
-        <f>E12-F12</f>
+        <f t="shared" si="0"/>
         <v>-202.53999999999996</v>
       </c>
       <c r="H12" s="19">
-        <f>(E12-F12)/F12</f>
+        <f t="shared" si="1"/>
         <v>-0.10126999999999999</v>
       </c>
       <c r="I12" s="17" t="s">
@@ -44693,11 +44651,11 @@
         <v>3000</v>
       </c>
       <c r="G13" s="10">
-        <f>E13-F13</f>
+        <f t="shared" si="0"/>
         <v>367.07999999999993</v>
       </c>
       <c r="H13" s="14">
-        <f>(E13-F13)/F13</f>
+        <f t="shared" si="1"/>
         <v>0.12235999999999998</v>
       </c>
       <c r="I13" s="10" t="s">
@@ -44725,11 +44683,11 @@
         <v>2700</v>
       </c>
       <c r="G14" s="10">
-        <f>E14-F14</f>
+        <f t="shared" si="0"/>
         <v>553.15999999999985</v>
       </c>
       <c r="H14" s="14">
-        <f>(E14-F14)/F14</f>
+        <f t="shared" si="1"/>
         <v>0.20487407407407401</v>
       </c>
       <c r="I14" s="10" t="s">
@@ -44757,11 +44715,11 @@
         <v>3200</v>
       </c>
       <c r="G15" s="10">
-        <f>E15-F15</f>
+        <f t="shared" si="0"/>
         <v>318.98</v>
       </c>
       <c r="H15" s="14">
-        <f>(E15-F15)/F15</f>
+        <f t="shared" si="1"/>
         <v>9.9681249999999999E-2</v>
       </c>
       <c r="I15" s="10" t="s">
@@ -44789,11 +44747,11 @@
         <v>2713.2</v>
       </c>
       <c r="G16" s="10">
-        <f>E16-F16</f>
+        <f t="shared" si="0"/>
         <v>729.83000000000038</v>
       </c>
       <c r="H16" s="14">
-        <f>(E16-F16)/F16</f>
+        <f t="shared" si="1"/>
         <v>0.26899233377561566</v>
       </c>
       <c r="I16" s="10" t="s">
@@ -44821,11 +44779,11 @@
         <v>3213</v>
       </c>
       <c r="G17" s="10">
-        <f>E17-F17</f>
+        <f t="shared" si="0"/>
         <v>230.0300000000002</v>
       </c>
       <c r="H17" s="14">
-        <f>(E17-F17)/F17</f>
+        <f t="shared" si="1"/>
         <v>7.1593526299408711E-2</v>
       </c>
       <c r="I17" s="10" t="s">
@@ -44853,11 +44811,11 @@
         <v>3659.25</v>
       </c>
       <c r="G18" s="17">
-        <f>E18-F18</f>
+        <f t="shared" si="0"/>
         <v>-89.25</v>
       </c>
       <c r="H18" s="19">
-        <f>(E18-F18)/F18</f>
+        <f t="shared" si="1"/>
         <v>-2.4390243902439025E-2</v>
       </c>
       <c r="I18" s="17" t="s">
@@ -44887,11 +44845,11 @@
         <v>3659.25</v>
       </c>
       <c r="G19" s="17">
-        <f>E19-F19</f>
+        <f t="shared" si="0"/>
         <v>-89.25</v>
       </c>
       <c r="H19" s="19">
-        <f>(E19-F19)/F19</f>
+        <f t="shared" si="1"/>
         <v>-2.4390243902439025E-2</v>
       </c>
       <c r="I19" s="17" t="s">
@@ -44921,11 +44879,11 @@
         <v>3659.25</v>
       </c>
       <c r="G20" s="17">
-        <f>E20-F20</f>
+        <f t="shared" si="0"/>
         <v>-89.25</v>
       </c>
       <c r="H20" s="19">
-        <f>(E20-F20)/F20</f>
+        <f t="shared" si="1"/>
         <v>-2.4390243902439025E-2</v>
       </c>
       <c r="I20" s="17" t="s">
@@ -44955,11 +44913,11 @@
         <v>3677.1</v>
       </c>
       <c r="G21" s="17">
-        <f>E21-F21</f>
+        <f t="shared" si="0"/>
         <v>-107.09999999999991</v>
       </c>
       <c r="H21" s="19">
-        <f>(E21-F21)/F21</f>
+        <f t="shared" si="1"/>
         <v>-2.9126213592232986E-2</v>
       </c>
       <c r="I21" s="17" t="s">
@@ -44989,11 +44947,11 @@
         <v>999.6</v>
       </c>
       <c r="G22" s="10">
-        <f>E22-F22</f>
+        <f t="shared" si="0"/>
         <v>494.07000000000005</v>
       </c>
       <c r="H22" s="14">
-        <f>(E22-F22)/F22</f>
+        <f t="shared" si="1"/>
         <v>0.49426770708283319</v>
       </c>
       <c r="I22" s="10" t="s">
@@ -45021,11 +44979,11 @@
         <v>2748.9</v>
       </c>
       <c r="G23" s="10">
-        <f>E23-F23</f>
+        <f t="shared" si="0"/>
         <v>567.54999999999973</v>
       </c>
       <c r="H23" s="14">
-        <f>(E23-F23)/F23</f>
+        <f t="shared" si="1"/>
         <v>0.20646440394339544</v>
       </c>
       <c r="I23" s="10" t="s">
@@ -45053,11 +45011,11 @@
         <v>2677.5</v>
       </c>
       <c r="G24" s="10">
-        <f>E24-F24</f>
+        <f t="shared" si="0"/>
         <v>461.73999999999978</v>
       </c>
       <c r="H24" s="14">
-        <f>(E24-F24)/F24</f>
+        <f t="shared" si="1"/>
         <v>0.17245191409897284</v>
       </c>
       <c r="I24" s="10" t="s">
@@ -45085,11 +45043,11 @@
         <v>2998.8</v>
       </c>
       <c r="G25" s="10">
-        <f>E25-F25</f>
+        <f t="shared" si="0"/>
         <v>292.32999999999993</v>
       </c>
       <c r="H25" s="14">
-        <f>(E25-F25)/F25</f>
+        <f t="shared" si="1"/>
         <v>9.7482326263838834E-2</v>
       </c>
       <c r="I25" s="10" t="s">
@@ -45117,11 +45075,11 @@
         <v>3248.7</v>
       </c>
       <c r="G26" s="10">
-        <f>E26-F26</f>
+        <f t="shared" si="0"/>
         <v>143.70000000000027</v>
       </c>
       <c r="H26" s="14">
-        <f>(E26-F26)/F26</f>
+        <f t="shared" si="1"/>
         <v>4.4233077846523312E-2</v>
       </c>
       <c r="I26" s="10" t="s">
@@ -45149,11 +45107,11 @@
         <v>3177.3</v>
       </c>
       <c r="G27" s="10">
-        <f>E27-F27</f>
+        <f t="shared" si="0"/>
         <v>177.12999999999965</v>
       </c>
       <c r="H27" s="14">
-        <f>(E27-F27)/F27</f>
+        <f t="shared" si="1"/>
         <v>5.5748591571459935E-2</v>
       </c>
       <c r="I27" s="10" t="s">
@@ -45181,11 +45139,11 @@
         <v>999.6</v>
       </c>
       <c r="G28" s="10">
-        <f>E28-F28</f>
+        <f t="shared" si="0"/>
         <v>494.07000000000005</v>
       </c>
       <c r="H28" s="14">
-        <f>(E28-F28)/F28</f>
+        <f t="shared" si="1"/>
         <v>0.49426770708283319</v>
       </c>
       <c r="I28" s="10" t="s">
@@ -45213,11 +45171,11 @@
         <v>2677.5</v>
       </c>
       <c r="G29" s="10">
-        <f>E29-F29</f>
+        <f t="shared" si="0"/>
         <v>423.76000000000022</v>
       </c>
       <c r="H29" s="14">
-        <f>(E29-F29)/F29</f>
+        <f t="shared" si="1"/>
         <v>0.15826704014939316</v>
       </c>
       <c r="I29" s="10" t="s">
@@ -45245,11 +45203,11 @@
         <v>2677.5</v>
       </c>
       <c r="G30" s="10">
-        <f>E30-F30</f>
+        <f t="shared" si="0"/>
         <v>385.78999999999996</v>
       </c>
       <c r="H30" s="14">
-        <f>(E30-F30)/F30</f>
+        <f t="shared" si="1"/>
         <v>0.1440859010270775</v>
       </c>
       <c r="I30" s="10" t="s">
@@ -45277,11 +45235,11 @@
         <v>3034.5</v>
       </c>
       <c r="G31" s="10">
-        <f>E31-F31</f>
+        <f t="shared" si="0"/>
         <v>408.5300000000002</v>
       </c>
       <c r="H31" s="14">
-        <f>(E31-F31)/F31</f>
+        <f t="shared" si="1"/>
         <v>0.13462843961113863</v>
       </c>
       <c r="I31" s="10" t="s">
@@ -45309,11 +45267,11 @@
         <v>3034.5</v>
       </c>
       <c r="G32" s="10">
-        <f>E32-F32</f>
+        <f t="shared" si="0"/>
         <v>408.5300000000002</v>
       </c>
       <c r="H32" s="14">
-        <f>(E32-F32)/F32</f>
+        <f t="shared" si="1"/>
         <v>0.13462843961113863</v>
       </c>
       <c r="I32" s="10" t="s">
@@ -45341,11 +45299,11 @@
         <v>3034.5</v>
       </c>
       <c r="G33" s="10">
-        <f>E33-F33</f>
+        <f t="shared" si="0"/>
         <v>408.5300000000002</v>
       </c>
       <c r="H33" s="14">
-        <f>(E33-F33)/F33</f>
+        <f t="shared" si="1"/>
         <v>0.13462843961113863</v>
       </c>
       <c r="I33" s="10" t="s">
@@ -45373,11 +45331,11 @@
         <v>1892.1</v>
       </c>
       <c r="G34" s="10">
-        <f>E34-F34</f>
+        <f t="shared" si="0"/>
         <v>373.72000000000025</v>
       </c>
       <c r="H34" s="14">
-        <f>(E34-F34)/F34</f>
+        <f t="shared" si="1"/>
         <v>0.19751598752708646</v>
       </c>
       <c r="I34" s="10" t="s">
@@ -45405,11 +45363,11 @@
         <v>2106.3000000000002</v>
       </c>
       <c r="G35" s="10">
-        <f>E35-F35</f>
+        <f t="shared" si="0"/>
         <v>349.38999999999987</v>
       </c>
       <c r="H35" s="14">
-        <f>(E35-F35)/F35</f>
+        <f t="shared" si="1"/>
         <v>0.16587855481175515</v>
       </c>
       <c r="I35" s="10" t="s">
@@ -45437,11 +45395,11 @@
         <v>2677.5</v>
       </c>
       <c r="G36" s="10">
-        <f>E36-F36</f>
+        <f t="shared" si="0"/>
         <v>550.34000000000015</v>
       </c>
       <c r="H36" s="14">
-        <f>(E36-F36)/F36</f>
+        <f t="shared" si="1"/>
         <v>0.20554248366013078</v>
       </c>
       <c r="I36" s="10" t="s">
@@ -45467,11 +45425,11 @@
         <v>3257.8</v>
       </c>
       <c r="G37" s="10">
-        <f>E37-F37</f>
+        <f t="shared" si="0"/>
         <v>134.59999999999991</v>
       </c>
       <c r="H37" s="14">
-        <f>(E37-F37)/F37</f>
+        <f t="shared" si="1"/>
         <v>4.131622567376754E-2</v>
       </c>
       <c r="I37" s="10" t="s">
@@ -45499,11 +45457,11 @@
         <v>3034.5</v>
       </c>
       <c r="G38" s="10">
-        <f>E38-F38</f>
+        <f t="shared" si="0"/>
         <v>383.2199999999998</v>
       </c>
       <c r="H38" s="14">
-        <f>(E38-F38)/F38</f>
+        <f t="shared" si="1"/>
         <v>0.12628769154720706</v>
       </c>
       <c r="I38" s="10" t="s">
@@ -45531,11 +45489,11 @@
         <v>2891.7</v>
       </c>
       <c r="G39" s="10">
-        <f>E39-F39</f>
+        <f t="shared" si="0"/>
         <v>108.30000000000018</v>
       </c>
       <c r="H39" s="14">
-        <f>(E39-F39)/F39</f>
+        <f t="shared" si="1"/>
         <v>3.7452017844174769E-2</v>
       </c>
       <c r="I39" s="10" t="s">
@@ -45563,11 +45521,11 @@
         <v>2677.5</v>
       </c>
       <c r="G40" s="10">
-        <f>E40-F40</f>
+        <f t="shared" si="0"/>
         <v>385.78999999999996</v>
       </c>
       <c r="H40" s="14">
-        <f>(E40-F40)/F40</f>
+        <f t="shared" si="1"/>
         <v>0.1440859010270775</v>
       </c>
       <c r="I40" s="10" t="s">
@@ -45595,11 +45553,11 @@
         <v>1700.5</v>
       </c>
       <c r="G41" s="10">
-        <f>E41-F41</f>
+        <f t="shared" si="0"/>
         <v>324.80999999999995</v>
       </c>
       <c r="H41" s="14">
-        <f>(E41-F41)/F41</f>
+        <f t="shared" si="1"/>
         <v>0.19100852690385178</v>
       </c>
       <c r="I41" s="10" t="s">
@@ -45627,11 +45585,11 @@
         <v>1356.6</v>
       </c>
       <c r="G42" s="10">
-        <f>E42-F42</f>
+        <f t="shared" si="0"/>
         <v>668.71</v>
       </c>
       <c r="H42" s="14">
-        <f>(E42-F42)/F42</f>
+        <f t="shared" si="1"/>
         <v>0.49293085655314761</v>
       </c>
       <c r="I42" s="10" t="s">
@@ -45659,11 +45617,11 @@
         <v>714</v>
       </c>
       <c r="G43" s="10">
-        <f>E43-F43</f>
+        <f t="shared" si="0"/>
         <v>20.169999999999959</v>
       </c>
       <c r="H43" s="14">
-        <f>(E43-F43)/F43</f>
+        <f t="shared" si="1"/>
         <v>2.8249299719887898E-2</v>
       </c>
       <c r="I43" s="10" t="s">
@@ -45691,11 +45649,11 @@
         <v>3105.9</v>
       </c>
       <c r="G44" s="10">
-        <f>E44-F44</f>
+        <f t="shared" si="0"/>
         <v>413.07999999999993</v>
       </c>
       <c r="H44" s="14">
-        <f>(E44-F44)/F44</f>
+        <f t="shared" si="1"/>
         <v>0.13299848675102222</v>
       </c>
       <c r="I44" s="10" t="s">
@@ -45723,11 +45681,11 @@
         <v>4676.7909090909097</v>
       </c>
       <c r="G45" s="13">
-        <f>E45-F45</f>
+        <f t="shared" si="0"/>
         <v>108.01909090909066</v>
       </c>
       <c r="H45" s="14">
-        <f>(E45-F45)/F45</f>
+        <f t="shared" si="1"/>
         <v>2.3096839907706668E-2</v>
       </c>
       <c r="I45" s="10" t="s">
@@ -45753,15 +45711,15 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E47" s="7">
-        <f t="shared" ref="E47:G47" si="0">SUM(E2:E46)</f>
+        <f t="shared" ref="E47:G47" si="2">SUM(E2:E46)</f>
         <v>132444.34999999998</v>
       </c>
       <c r="F47" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>119693.16090909092</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12751.189090909093</v>
       </c>
       <c r="H47" s="40">
@@ -45949,116 +45907,82 @@
       <c r="C103" s="33"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C1:C44 C46:C1048576">
+    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C103">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C44 C46:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219AAD04-B4E6-427C-9FEF-ED731BA8819D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B091008-6629-447F-AAC9-C0A18E7BDA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4801" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4826" uniqueCount="608">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1840,7 +1840,37 @@
     <t>408 Shop Exp</t>
   </si>
   <si>
-    <t>Karachi Office Exp</t>
+    <t>Karachi Office Exp 7677/3 =2559</t>
+  </si>
+  <si>
+    <t>ST Usa Business Exp in June-2026</t>
+  </si>
+  <si>
+    <t>21.32 US$ @3.674 Claude AI Charges</t>
+  </si>
+  <si>
+    <t>36.27 US$ @3.674 AWS Charges</t>
+  </si>
+  <si>
+    <t>2-june label 17328 1833.25 US$ @3.674 ST</t>
+  </si>
+  <si>
+    <t>22-june label 17424 &amp; 17511 1833.25 US$ @3.674 ST</t>
+  </si>
+  <si>
+    <t>11-june label 57726 89.69 US$ @3.674 ST</t>
+  </si>
+  <si>
+    <t>Total Profit in ST USA</t>
+  </si>
+  <si>
+    <t>Total Profit in USA</t>
+  </si>
+  <si>
+    <t>Total Profit in Karachi</t>
+  </si>
+  <si>
+    <t>Total Profit in NewZealand</t>
   </si>
 </sst>
 </file>
@@ -1990,7 +2020,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2068,27 +2098,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7AF396E0-14CD-4B92-AB27-039AE1E776EB}"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="51">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -21784,7 +21853,7 @@
   </sheetData>
   <autoFilter ref="A6:I655" xr:uid="{9BB2F6C6-EF2F-424D-9FFF-ECB06C81F028}"/>
   <conditionalFormatting sqref="C1:C655">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21792,7 +21861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6BDDCE-7628-4239-A22E-AFC54CBF13AA}">
-  <dimension ref="A1:L231"/>
+  <dimension ref="A1:L232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -30113,7 +30182,7 @@
       <c r="L209" s="10"/>
     </row>
     <row r="213" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B213" s="43" t="s">
+      <c r="B213" s="41" t="s">
         <v>583</v>
       </c>
       <c r="C213" s="21">
@@ -30121,7 +30190,7 @@
       </c>
     </row>
     <row r="214" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B214" s="44" t="s">
+      <c r="B214" s="42" t="s">
         <v>584</v>
       </c>
       <c r="C214" s="21">
@@ -30129,7 +30198,7 @@
       </c>
     </row>
     <row r="215" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B215" s="44" t="s">
+      <c r="B215" s="42" t="s">
         <v>585</v>
       </c>
       <c r="C215" s="21">
@@ -30137,7 +30206,7 @@
       </c>
     </row>
     <row r="216" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B216" s="44" t="s">
+      <c r="B216" s="42" t="s">
         <v>590</v>
       </c>
       <c r="C216" s="21">
@@ -30145,132 +30214,142 @@
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B217" s="44" t="s">
+      <c r="B217" s="42" t="s">
         <v>586</v>
       </c>
       <c r="C217" s="21">
         <v>15154.99</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B218" s="45" t="s">
+    <row r="218" spans="2:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="47" t="s">
+        <v>597</v>
+      </c>
+      <c r="C218" s="48">
+        <v>2559</v>
+      </c>
+      <c r="G218" s="3"/>
+      <c r="J218" s="4"/>
+    </row>
+    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B219" s="50" t="s">
         <v>594</v>
       </c>
-      <c r="C218" s="21">
+      <c r="C219" s="21">
         <v>7045.14</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B219" s="44" t="s">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B220" s="42" t="s">
         <v>576</v>
       </c>
-      <c r="C219" s="21">
+      <c r="C220" s="21">
         <v>10140</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B220" s="44" t="s">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B221" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="C220" s="32">
+      <c r="C221" s="32">
         <v>12303.19</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B221" s="44" t="s">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B222" s="42" t="s">
         <v>577</v>
       </c>
-      <c r="C221" s="21">
+      <c r="C222" s="21">
         <v>6337.5</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B222" s="44" t="s">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B223" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="C222" s="21">
+      <c r="C223" s="21">
         <v>3727.36</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B223" s="44" t="s">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B224" s="42" t="s">
         <v>579</v>
       </c>
-      <c r="C223" s="21">
+      <c r="C224" s="21">
         <v>3727.37</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B224" s="44" t="s">
+    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B225" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="C224" s="21">
+      <c r="C225" s="21">
         <v>1013.5</v>
       </c>
     </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="44" t="s">
+    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B226" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="C225" s="21">
+      <c r="C226" s="21">
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="44" t="s">
+    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B227" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="C226" s="21">
+      <c r="C227" s="21">
         <v>256</v>
       </c>
     </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="10" t="s">
+    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B228" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="C227" s="21">
+      <c r="C228" s="21">
         <v>4984.16</v>
       </c>
     </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="10"/>
-      <c r="C228" s="21"/>
-    </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="10"/>
+      <c r="C229" s="21"/>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B230" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="C229" s="5">
-        <f>SUM(C213:C228)</f>
-        <v>106520.26</v>
-      </c>
-    </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B230" s="10"/>
-      <c r="C230" s="21"/>
-    </row>
-    <row r="231" spans="2:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="B231" s="46" t="s">
+      <c r="C230" s="5">
+        <f>SUM(C213:C229)</f>
+        <v>109079.26000000001</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B231" s="10"/>
+      <c r="C231" s="21"/>
+    </row>
+    <row r="232" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B232" s="43" t="s">
         <v>589</v>
       </c>
-      <c r="C231" s="47">
-        <f>I209-C229</f>
-        <v>39869.875454545559</v>
+      <c r="C232" s="44">
+        <f>I209-C230</f>
+        <v>37310.875454545545</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C207">
-    <cfRule type="duplicateValues" dxfId="47" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C219:C223">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+  <conditionalFormatting sqref="C220:C224">
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C220">
-    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="4"/>
+  <conditionalFormatting sqref="C221">
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C230 C1:C228 C232:C1048576">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+  <conditionalFormatting sqref="C231 C1:C229 C233:C1048576">
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30278,7 +30357,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B5EA52-4A09-4771-8155-97F59FDF1D1A}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="22" customWidth="1"/>
@@ -33654,48 +33733,82 @@
       <c r="K87" s="10"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="44" t="s">
+      <c r="B94" s="42" t="s">
         <v>590</v>
       </c>
-      <c r="C94" s="22">
+      <c r="C94" s="48">
         <v>3273.66</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B95" s="41" t="s">
+      <c r="B95" s="42" t="s">
         <v>591</v>
       </c>
-      <c r="C95" s="22">
+      <c r="C95" s="48">
         <v>5662.62</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B96" s="41" t="s">
+      <c r="B96" s="42" t="s">
         <v>592</v>
       </c>
-      <c r="C96" s="22">
+      <c r="C96" s="48">
         <v>5613.5</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
+      <c r="B97" s="47" t="s">
         <v>593</v>
       </c>
-      <c r="C97" s="22">
+      <c r="C97" s="48">
         <v>4984.16</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="45" t="s">
+      <c r="B98" s="50" t="s">
         <v>594</v>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="48">
         <v>7045.14</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="47" t="s">
+        <v>597</v>
+      </c>
+      <c r="C99" s="48">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="47"/>
+      <c r="C100" s="48"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C101" s="5">
+        <f>SUM(C94:C100)</f>
+        <v>29138.079999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="47"/>
+      <c r="C102" s="48"/>
+    </row>
+    <row r="103" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B103" s="43" t="s">
+        <v>607</v>
+      </c>
+      <c r="C103" s="44">
+        <f>I87-C101</f>
+        <v>107473.27015200008</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C85">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33707,7 +33820,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="21.7109375" style="22" customWidth="1"/>
     <col min="4" max="4" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
@@ -35455,72 +35568,127 @@
       <c r="C60" s="33"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="44" t="s">
+      <c r="B61" s="51" t="s">
         <v>590</v>
       </c>
-      <c r="C61" s="33"/>
+      <c r="C61" s="54">
+        <v>1636.83</v>
+      </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
+      <c r="B62" s="52" t="s">
         <v>593</v>
       </c>
-      <c r="C62" s="33"/>
+      <c r="C62" s="54">
+        <v>2492.08</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="45" t="s">
+      <c r="B63" s="53" t="s">
         <v>594</v>
       </c>
-      <c r="C63" s="34"/>
+      <c r="C63" s="48">
+        <v>3522.57</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C64" s="33"/>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="33"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="33"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="33"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="33"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="33"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="33"/>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="33"/>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="34"/>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="33"/>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="33"/>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="C64" s="46">
+        <v>3367.68</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="C65" s="46">
+        <v>4542.62</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="C66" s="46">
+        <v>164.76</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="52" t="s">
+        <v>597</v>
+      </c>
+      <c r="C67" s="54">
+        <v>1279.5</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="C68" s="54">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="51" t="s">
+        <v>600</v>
+      </c>
+      <c r="C69" s="54">
+        <v>66.62</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="51" t="s">
+        <v>599</v>
+      </c>
+      <c r="C70" s="54">
+        <v>39.159999999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="47"/>
+      <c r="C71" s="49"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C72" s="5">
+        <f>SUM(C61:C71)</f>
+        <v>22622.82</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="47"/>
+      <c r="C73" s="49"/>
+    </row>
+    <row r="74" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B74" s="43" t="s">
+        <v>604</v>
+      </c>
+      <c r="C74" s="43">
+        <f>G55-C72</f>
+        <v>2746.2499999999563</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C75" s="33"/>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C76" s="33"/>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C77" s="33"/>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C78" s="33"/>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C79" s="34"/>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C80" s="33"/>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.25">
@@ -35623,14 +35791,14 @@
       <c r="C113" s="33"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
+  <conditionalFormatting sqref="C1:C71 C73 C75:C1048576">
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C53">
-    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C60:C113">
-    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+  <conditionalFormatting sqref="C60:C71 C73 C75:C113">
+    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44004,75 +44172,146 @@
       <c r="J262" s="10"/>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B268" s="44" t="s">
+      <c r="B268" s="51" t="s">
         <v>590</v>
       </c>
+      <c r="C268" s="54">
+        <v>1636.83</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B269" s="52" t="s">
+        <v>593</v>
+      </c>
+      <c r="C269" s="54">
+        <v>2492.08</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B270" s="53" t="s">
+        <v>594</v>
+      </c>
+      <c r="C270" s="48">
+        <v>3522.57</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B271" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="C271" s="46">
+        <v>3367.68</v>
+      </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C272" s="33"/>
+      <c r="B272" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="C272" s="46">
+        <v>4542.62</v>
+      </c>
       <c r="D272" s="35"/>
     </row>
-    <row r="273" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C273" s="33"/>
+    <row r="273" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B273" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="C273" s="46">
+        <v>164.76</v>
+      </c>
       <c r="D273" s="35"/>
     </row>
-    <row r="274" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C274" s="33"/>
+    <row r="274" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B274" s="52" t="s">
+        <v>597</v>
+      </c>
+      <c r="C274" s="54">
+        <v>1279.5</v>
+      </c>
       <c r="D274" s="35"/>
     </row>
-    <row r="275" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C275" s="36"/>
+    <row r="275" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B275" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="C275" s="54">
+        <v>5511</v>
+      </c>
       <c r="D275" s="37"/>
     </row>
-    <row r="276" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C276" s="33"/>
+    <row r="276" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B276" s="51" t="s">
+        <v>600</v>
+      </c>
+      <c r="C276" s="54">
+        <v>66.62</v>
+      </c>
       <c r="D276" s="35"/>
     </row>
-    <row r="277" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C277" s="33"/>
+    <row r="277" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B277" s="51" t="s">
+        <v>599</v>
+      </c>
+      <c r="C277" s="54">
+        <v>39.159999999999997</v>
+      </c>
       <c r="D277" s="35"/>
     </row>
-    <row r="278" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C278" s="33"/>
+    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B278" s="47"/>
+      <c r="C278" s="49"/>
       <c r="D278" s="35"/>
     </row>
-    <row r="279" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C279" s="33"/>
+    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B279" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C279" s="5">
+        <f>SUM(C268:C278)</f>
+        <v>22622.82</v>
+      </c>
       <c r="D279" s="35"/>
     </row>
-    <row r="280" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C280" s="33"/>
+    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B280" s="47"/>
+      <c r="C280" s="49"/>
       <c r="D280" s="35"/>
     </row>
-    <row r="281" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C281" s="33"/>
+    <row r="281" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B281" s="43" t="s">
+        <v>605</v>
+      </c>
+      <c r="C281" s="43">
+        <f>G262-C279</f>
+        <v>26030.559999999925</v>
+      </c>
       <c r="D281" s="35"/>
     </row>
-    <row r="282" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C282" s="33"/>
       <c r="D282" s="35"/>
     </row>
-    <row r="283" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C283" s="33"/>
       <c r="D283" s="35"/>
     </row>
-    <row r="284" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C284" s="36"/>
       <c r="D284" s="37"/>
     </row>
-    <row r="285" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C285" s="33"/>
       <c r="D285" s="35"/>
     </row>
-    <row r="286" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C286" s="33"/>
       <c r="D286" s="35"/>
     </row>
-    <row r="287" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C287" s="33"/>
       <c r="D287" s="35"/>
     </row>
-    <row r="288" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C288" s="33"/>
       <c r="D288" s="35"/>
     </row>
@@ -44228,11 +44467,17 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J260">
     <sortCondition ref="I2:I260"/>
   </sortState>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+  <conditionalFormatting sqref="C1:C267 C278 C280 C282:C1048576">
+    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C260">
-    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C268:C277">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C268:C277">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45739,37 +45984,46 @@
       <c r="C52" s="33"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
+      <c r="B53" s="47" t="s">
         <v>595</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="48">
         <v>8151.89</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
+      <c r="B54" s="47" t="s">
         <v>596</v>
       </c>
-      <c r="C54" s="42">
+      <c r="C54" s="32">
         <v>1062.01</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>597</v>
-      </c>
-      <c r="C55" s="42">
-        <v>7677</v>
-      </c>
+      <c r="B55" s="47"/>
+      <c r="C55" s="32"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="33"/>
+      <c r="B56" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C56" s="5">
+        <f>SUM(C53:C55)</f>
+        <v>9213.9</v>
+      </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="33"/>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="33"/>
+      <c r="B57" s="47"/>
+      <c r="C57" s="49"/>
+    </row>
+    <row r="58" spans="2:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="B58" s="43" t="s">
+        <v>606</v>
+      </c>
+      <c r="C58" s="44">
+        <f>G47-C56</f>
+        <v>3537.2890909090929</v>
+      </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C59" s="33"/>
@@ -45907,82 +46161,82 @@
       <c r="C103" s="33"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C44 C46:C1048576">
-    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+  <conditionalFormatting sqref="C1:C44 C46:C55 C57 C59:C1048576">
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C50:C103">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="C50:C55 C57 C59:C103">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B091008-6629-447F-AAC9-C0A18E7BDA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672B048E-6022-425F-9881-1DAAE43AC894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4826" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4832" uniqueCount="609">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1871,6 +1871,9 @@
   </si>
   <si>
     <t>Total Profit in NewZealand</t>
+  </si>
+  <si>
+    <t>Overall Profit in June-2026</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2131,6 +2134,15 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -21861,15 +21873,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6BDDCE-7628-4239-A22E-AFC54CBF13AA}">
-  <dimension ref="A1:L232"/>
+  <dimension ref="A1:L247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="55.140625" customWidth="1"/>
     <col min="3" max="3" width="32" style="22" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="5" max="6" width="28.5703125" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" style="3" customWidth="1"/>
     <col min="8" max="8" width="18.140625" customWidth="1"/>
     <col min="9" max="9" width="16.140625" customWidth="1"/>
@@ -30335,6 +30346,68 @@
       <c r="C232" s="44">
         <f>I209-C230</f>
         <v>37310.875454545545</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C238" s="55"/>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C239" s="55"/>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C240" s="55"/>
+    </row>
+    <row r="241" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E241" s="47" t="s">
+        <v>589</v>
+      </c>
+      <c r="F241" s="56">
+        <v>37310.875454545545</v>
+      </c>
+    </row>
+    <row r="242" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E242" s="47" t="s">
+        <v>607</v>
+      </c>
+      <c r="F242" s="56">
+        <v>107473.27015200008</v>
+      </c>
+    </row>
+    <row r="243" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E243" s="47" t="s">
+        <v>604</v>
+      </c>
+      <c r="F243" s="56">
+        <v>2746.2499999999563</v>
+      </c>
+    </row>
+    <row r="244" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E244" s="47" t="s">
+        <v>605</v>
+      </c>
+      <c r="F244" s="56">
+        <v>26030.559999999925</v>
+      </c>
+    </row>
+    <row r="245" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E245" s="47" t="s">
+        <v>606</v>
+      </c>
+      <c r="F245" s="56">
+        <v>2904.3890909090915</v>
+      </c>
+    </row>
+    <row r="246" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E246" s="47"/>
+      <c r="F246" s="48"/>
+    </row>
+    <row r="247" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E247" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="F247" s="57">
+        <f>SUM(F241:F246)</f>
+        <v>176465.3446974546</v>
       </c>
     </row>
   </sheetData>
@@ -30348,7 +30421,7 @@
     <cfRule type="duplicateValues" dxfId="47" priority="3"/>
     <cfRule type="duplicateValues" dxfId="46" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C231 C1:C229 C233:C1048576">
+  <conditionalFormatting sqref="C231 C1:C229 C233:C240 C248:C1048576 F241:F247">
     <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44474,10 +44547,10 @@
     <cfRule type="duplicateValues" dxfId="39" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C268:C277">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C268:C277">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45996,7 +46069,7 @@
         <v>596</v>
       </c>
       <c r="C54" s="32">
-        <v>1062.01</v>
+        <v>1694.91</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
@@ -46009,7 +46082,7 @@
       </c>
       <c r="C56" s="5">
         <f>SUM(C53:C55)</f>
-        <v>9213.9</v>
+        <v>9846.8000000000011</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
@@ -46022,7 +46095,7 @@
       </c>
       <c r="C58" s="44">
         <f>G47-C56</f>
-        <v>3537.2890909090929</v>
+        <v>2904.3890909090915</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
@@ -46162,81 +46235,81 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C44 C46:C55 C57 C59:C1048576">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C55 C57 C59:C103">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report June-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672B048E-6022-425F-9881-1DAAE43AC894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D095BAD-6420-4240-8FB9-6EE291985660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{B6D4EC9A-6888-49F7-BC98-088E7BD35AE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="ST USA" sheetId="4" r:id="rId4"/>
     <sheet name="USA " sheetId="5" r:id="rId5"/>
     <sheet name="Karachi " sheetId="6" r:id="rId6"/>
+    <sheet name="All Expanses" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$6:$I$655</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4832" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4861" uniqueCount="619">
   <si>
     <t>Sale-wise Profit Report</t>
   </si>
@@ -1874,6 +1875,36 @@
   </si>
   <si>
     <t>Overall Profit in June-2026</t>
+  </si>
+  <si>
+    <t>Expanse Description</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Local Charges in june Turbo &amp; Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karachi Office Exp </t>
+  </si>
+  <si>
+    <t>4000 AU$ @2.5350 Aus Office Rent</t>
+  </si>
+  <si>
+    <t>Fuel Exp Melbourne</t>
+  </si>
+  <si>
+    <t>Dubai Office Exp in june</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary Exp in june </t>
+  </si>
+  <si>
+    <t>22-june label 17424 &amp; 17511 2472.85 US$ @3.674 ST</t>
+  </si>
+  <si>
+    <t>Total Expanses in June-2026</t>
   </si>
 </sst>
 </file>
@@ -1938,7 +1969,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1965,6 +1996,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2023,7 +2060,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2144,12 +2181,139 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7AF396E0-14CD-4B92-AB27-039AE1E776EB}"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="63">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -21865,7 +22029,7 @@
   </sheetData>
   <autoFilter ref="A6:I655" xr:uid="{9BB2F6C6-EF2F-424D-9FFF-ECB06C81F028}"/>
   <conditionalFormatting sqref="C1:C655">
-    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24482,15 +24646,15 @@
         <v>928.34</v>
       </c>
       <c r="G66" s="13">
-        <f t="shared" ref="G66:G97" si="8">F66/11</f>
+        <f t="shared" ref="G66" si="8">F66/11</f>
         <v>84.394545454545451</v>
       </c>
       <c r="H66" s="13">
-        <f t="shared" ref="H66:H97" si="9">F66-G66</f>
+        <f t="shared" ref="H66" si="9">F66-G66</f>
         <v>843.9454545454546</v>
       </c>
       <c r="I66" s="13">
-        <f t="shared" ref="I66:I97" si="10">E66-H66</f>
+        <f t="shared" ref="I66" si="10">E66-H66</f>
         <v>491.0545454545454</v>
       </c>
       <c r="J66" s="14">
@@ -30412,17 +30576,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C207">
-    <cfRule type="duplicateValues" dxfId="49" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C220:C224">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C221">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C231 C1:C229 C233:C240 C248:C1048576 F241:F247">
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33881,7 +34045,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C85">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35865,13 +36029,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C71 C73 C75:C1048576">
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C53">
-    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C71 C73 C75:C113">
-    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40026,7 +40190,7 @@
         <v>1677.9</v>
       </c>
       <c r="G130" s="10">
-        <f t="shared" ref="G130:G161" si="8">E130-F130</f>
+        <f t="shared" ref="G130:G159" si="8">E130-F130</f>
         <v>152.09999999999991</v>
       </c>
       <c r="H130" s="14">
@@ -44541,16 +44705,14 @@
     <sortCondition ref="I2:I260"/>
   </sortState>
   <conditionalFormatting sqref="C1:C267 C278 C280 C282:C1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C260">
-    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C268:C277">
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C268:C277">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46235,81 +46397,355 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C44 C46:C55 C57 C59:C1048576">
-    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C5">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C9">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C15">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C27">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:C38">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:C42">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C50:C55 C57 C59:C103">
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44D69AA-569C-4DB0-8CAD-9847626DA14A}">
+  <dimension ref="B3:C31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="60" t="s">
+        <v>609</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="C4" s="48">
+        <v>10691.07</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="C5" s="48">
+        <v>15682.45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="C6" s="48">
+        <v>11863.87</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="42" t="s">
+        <v>611</v>
+      </c>
+      <c r="C7" s="48">
+        <v>9821</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="42" t="s">
+        <v>586</v>
+      </c>
+      <c r="C8" s="48">
+        <v>15154.99</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="47" t="s">
+        <v>612</v>
+      </c>
+      <c r="C9" s="48">
+        <v>7677</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="42" t="s">
+        <v>613</v>
+      </c>
+      <c r="C10" s="48">
+        <v>10140</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="C11" s="32">
+        <v>12303.19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="C12" s="48">
+        <v>6337.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="42" t="s">
+        <v>578</v>
+      </c>
+      <c r="C13" s="48">
+        <v>3727.36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="42" t="s">
+        <v>579</v>
+      </c>
+      <c r="C14" s="48">
+        <v>3727.37</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="42" t="s">
+        <v>614</v>
+      </c>
+      <c r="C15" s="48">
+        <v>1013.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="C16" s="48">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="C17" s="48">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="C18" s="58">
+        <v>14952.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="50" t="s">
+        <v>616</v>
+      </c>
+      <c r="C19" s="58">
+        <v>21135.439999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="42" t="s">
+        <v>591</v>
+      </c>
+      <c r="C20" s="48">
+        <v>5662.62</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="C21" s="48">
+        <v>5613.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="C22" s="58">
+        <v>6735.36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="C23" s="58">
+        <v>9085.25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="C24" s="58">
+        <v>329.52</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="C25" s="58">
+        <v>11022</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="51" t="s">
+        <v>600</v>
+      </c>
+      <c r="C26" s="58">
+        <v>133.25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="51" t="s">
+        <v>599</v>
+      </c>
+      <c r="C27" s="58">
+        <v>78.319999999999993</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="47" t="s">
+        <v>595</v>
+      </c>
+      <c r="C28" s="48">
+        <v>8151.89</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="47" t="s">
+        <v>596</v>
+      </c>
+      <c r="C29" s="32">
+        <v>1694.91</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="59" t="s">
+        <v>618</v>
+      </c>
+      <c r="C31" s="60">
+        <f>SUM(C4:C30)</f>
+        <v>193309.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C4:C5">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C14">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
     <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="C11:C19 C22:C27">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C50:C55 C57 C59:C103">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="C28:C29">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28:C29">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
